--- a/thesis-final/Results_Comparison.xlsx
+++ b/thesis-final/Results_Comparison.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="422">
   <si>
     <t xml:space="preserve">Results comparison — v8-Chain thesis</t>
   </si>
@@ -172,45 +172,45 @@
     <t xml:space="preserve">v5_backup_int15</t>
   </si>
   <si>
+    <t xml:space="preserve">v5b_energy_aware_repair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v5x_backup_repair_int10</t>
+  </si>
+  <si>
     <t xml:space="preserve">v5x_backup_repair_int5</t>
   </si>
   <si>
-    <t xml:space="preserve">v5x_backup_repair_int10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v5b_energy_aware_repair</t>
-  </si>
-  <si>
     <t xml:space="preserve">v6_chain_center</t>
   </si>
   <si>
     <t xml:space="preserve">v6_chain_farBS</t>
   </si>
   <si>
+    <t xml:space="preserve">v7_1_multihop_int5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v7_2_multihop_int10</t>
+  </si>
+  <si>
     <t xml:space="preserve">v7_chain_backup_center</t>
   </si>
   <si>
     <t xml:space="preserve">v7_chain_backup_farBS</t>
   </si>
   <si>
-    <t xml:space="preserve">v7_1_multihop_int5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v7_2_multihop_int10</t>
-  </si>
-  <si>
     <t xml:space="preserve">v8_center</t>
   </si>
   <si>
+    <t xml:space="preserve">v8_chain_center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v8_chain_farBS</t>
+  </si>
+  <si>
     <t xml:space="preserve">v8_farBS</t>
   </si>
   <si>
-    <t xml:space="preserve">v8_chain_center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v8_chain_farBS</t>
-  </si>
-  <si>
     <t xml:space="preserve">4_PROPOSED/side_experiments</t>
   </si>
   <si>
@@ -331,6 +331,30 @@
     <t xml:space="preserve">v8_chain_center_seed99</t>
   </si>
   <si>
+    <t xml:space="preserve">v8_chain_farBS_seed1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v8_chain_farBS_seed12345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v8_chain_farBS_seed2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v8_chain_farBS_seed31337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v8_chain_farBS_seed42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v8_chain_farBS_seed555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v8_chain_farBS_seed7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v8_chain_farBS_seed99</t>
+  </si>
+  <si>
     <t xml:space="preserve">v8_farBS_seed1</t>
   </si>
   <si>
@@ -355,28 +379,385 @@
     <t xml:space="preserve">v8_farBS_seed99</t>
   </si>
   <si>
-    <t xml:space="preserve">v8_chain_farBS_seed1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v8_chain_farBS_seed12345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v8_chain_farBS_seed2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v8_chain_farBS_seed31337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v8_chain_farBS_seed42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v8_chain_farBS_seed555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v8_chain_farBS_seed7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v8_chain_farBS_seed99</t>
+    <t xml:space="preserve">security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v8_chain_mic104_aes5nJ_center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v8_chain_mic104_aes5nJ_ecc20mJ_center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v8_chain_mic104_aes5nJ_ecc20mJ_far</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v8_chain_mic104_aes5nJ_far</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v8_chain_mic104_center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v8_chain_mic104_ecc20mJ_center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v8_chain_mic104_ecc20mJ_far</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v8_chain_mic104_far</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v8_chain_none_center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v8_chain_none_far</t>
+  </si>
+  <si>
+    <t xml:space="preserve">far_bs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eechheed_EDITED_farBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eechheed_IMPROVED_farBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heed_EDITED_farBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heed_fairness_EDITED_farBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hleach_EDITED_farBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hleach_IMPROVED_farBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leach_EDITED_farBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pegasis_EDITED_farBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shleach_EDITED_farBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shleach_IMPROVED_farBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v3_single_pass_reuse_int5_farBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v5b_energy_aware_repair_farBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">security_proposal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_center_s0_none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_center_s10_ecc160_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_center_s11_p256_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_center_s12_ecc160_ecdsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_center_s13_ecc160_swaes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_center_s14_x25519_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_center_s15_rsa3072_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_center_s16_rsa1024_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_center_s1_aes_only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_center_s2_hybrid_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_center_s3_hybrid_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_center_s4_full_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_center_s5_full_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_center_s6_once_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_center_s7_once_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_center_s8_bs_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_center_s9_bs_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_far_s0_none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_far_s10_ecc160_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_far_s11_p256_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_far_s12_ecc160_ecdsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_far_s13_ecc160_swaes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_far_s14_x25519_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_far_s15_rsa3072_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_far_s16_rsa1024_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_far_s1_aes_only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_far_s2_hybrid_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_far_s3_hybrid_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_far_s4_full_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_far_s5_full_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_far_s6_once_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_far_s7_once_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_far_s8_bs_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_leach_far_s9_bs_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_center_s0_none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_center_s10_ecc160_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_center_s11_p256_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_center_s12_ecc160_ecdsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_center_s13_ecc160_swaes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_center_s14_x25519_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_center_s15_rsa3072_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_center_s16_rsa1024_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_center_s1_aes_only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_center_s2_hybrid_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_center_s3_hybrid_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_center_s4_full_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_center_s5_full_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_center_s6_once_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_center_s7_once_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_center_s8_bs_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_center_s9_bs_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_far_s0_none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_far_s10_ecc160_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_far_s11_p256_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_far_s12_ecc160_ecdsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_far_s13_ecc160_swaes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_far_s14_x25519_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_far_s15_rsa3072_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_far_s16_rsa1024_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_far_s1_aes_only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_far_s2_hybrid_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_far_s3_hybrid_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_far_s4_full_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_far_s5_full_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_far_s6_once_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_far_s7_once_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_far_s8_bs_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_pegasis_far_s9_bs_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8_center_s0_none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8_center_s10_ecc160_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8_center_s11_p256_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8_center_s12_ecc160_ecdsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8_center_s13_ecc160_swaes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8_center_s14_x25519_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8_center_s15_rsa3072_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8_center_s16_rsa1024_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8_center_s1_aes_only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8_center_s2_hybrid_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8_center_s3_hybrid_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8_center_s4_full_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8_center_s5_full_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8_center_s6_once_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8_center_s7_once_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8_center_s8_bs_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8_center_s9_bs_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8chain_far_s0_none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8chain_far_s10_ecc160_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8chain_far_s11_p256_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8chain_far_s12_ecc160_ecdsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8chain_far_s13_ecc160_swaes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8chain_far_s14_x25519_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8chain_far_s15_rsa3072_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8chain_far_s16_rsa1024_aes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8chain_far_s1_aes_only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8chain_far_s2_hybrid_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8chain_far_s3_hybrid_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8chain_far_s4_full_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8chain_far_s5_full_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8chain_far_s6_once_rsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8chain_far_s7_once_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8chain_far_s8_bs_ecc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sec_v8chain_far_s9_bs_rsa</t>
   </si>
   <si>
     <t xml:space="preserve">Best version of every family — unified environment, BS at the centre</t>
@@ -1533,10 +1914,10 @@
                   <c:v>1383</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>634</c:v>
+                  <c:v>658</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>743</c:v>
+                  <c:v>738</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1324</c:v>
@@ -1554,13 +1935,13 @@
                   <c:v>1473</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1311</c:v>
+                  <c:v>1277</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1368</c:v>
+                  <c:v>1335</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2501</c:v>
+                  <c:v>2446</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1667,10 +2048,10 @@
                   <c:v>1586</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1216</c:v>
+                  <c:v>1197</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1154</c:v>
+                  <c:v>1157</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>2352</c:v>
@@ -1688,13 +2069,13 @@
                   <c:v>1509</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1382</c:v>
+                  <c:v>1384</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1385</c:v>
+                  <c:v>1384</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2589</c:v>
+                  <c:v>2536</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1801,10 +2182,10 @@
                   <c:v>1842</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1883</c:v>
+                  <c:v>1875</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1960</c:v>
+                  <c:v>1969</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>3504</c:v>
@@ -1822,13 +2203,13 @@
                   <c:v>1525</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1545</c:v>
+                  <c:v>1543</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1767</c:v>
+                  <c:v>1766</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2631</c:v>
+                  <c:v>2566</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1836,11 +2217,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="89229517"/>
-        <c:axId val="83126491"/>
+        <c:axId val="32135223"/>
+        <c:axId val="33015798"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="89229517"/>
+        <c:axId val="32135223"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1872,7 +2253,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83126491"/>
+        <c:crossAx val="33015798"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1880,7 +2261,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83126491"/>
+        <c:axId val="33015798"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1956,7 +2337,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89229517"/>
+        <c:crossAx val="32135223"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2172,19 +2553,19 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>322</c:v>
+                  <c:v>320</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>338</c:v>
+                  <c:v>334</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1645</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1438</c:v>
+                  <c:v>1513</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1438</c:v>
+                  <c:v>1513</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>1645</c:v>
@@ -2196,34 +2577,34 @@
                   <c:v>1645</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1415</c:v>
+                  <c:v>1521</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1409</c:v>
+                  <c:v>1481</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1415</c:v>
+                  <c:v>1521</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1409</c:v>
+                  <c:v>1481</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1471</c:v>
+                  <c:v>1466</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1421</c:v>
+                  <c:v>1431</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2501</c:v>
+                  <c:v>2446</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1441</c:v>
+                  <c:v>1406</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2501</c:v>
+                  <c:v>2446</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1671</c:v>
+                  <c:v>1626</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2348,58 +2729,58 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>530</c:v>
+                  <c:v>529</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>528</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2011</c:v>
+                  <c:v>2001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2206</c:v>
+                  <c:v>2158</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2131</c:v>
+                  <c:v>2116</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2006</c:v>
+                  <c:v>1996</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2091</c:v>
+                  <c:v>2090</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2011</c:v>
+                  <c:v>1996</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1916</c:v>
+                  <c:v>1913</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1824</c:v>
+                  <c:v>1816</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1911</c:v>
+                  <c:v>1906</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1801</c:v>
+                  <c:v>1796</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1916</c:v>
+                  <c:v>1896</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1991</c:v>
+                  <c:v>1996</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2589</c:v>
+                  <c:v>2536</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1596</c:v>
+                  <c:v>1551</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2589</c:v>
+                  <c:v>2536</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1851</c:v>
+                  <c:v>1821</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2524,58 +2905,58 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>1217</c:v>
+                  <c:v>1218</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1276</c:v>
+                  <c:v>1285</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2205</c:v>
+                  <c:v>2203</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2476</c:v>
+                  <c:v>2416</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2401</c:v>
+                  <c:v>2356</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2101</c:v>
+                  <c:v>2081</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2251</c:v>
+                  <c:v>2259</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2106</c:v>
+                  <c:v>2116</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2016</c:v>
+                  <c:v>2025</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1936</c:v>
+                  <c:v>1961</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2001</c:v>
+                  <c:v>2011</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1906</c:v>
+                  <c:v>1911</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2006</c:v>
+                  <c:v>2011</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2193</c:v>
+                  <c:v>2181</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2636</c:v>
+                  <c:v>2566</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1646</c:v>
+                  <c:v>1606</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2631</c:v>
+                  <c:v>2566</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1906</c:v>
+                  <c:v>1881</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2583,11 +2964,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="5656242"/>
-        <c:axId val="41057891"/>
+        <c:axId val="6505993"/>
+        <c:axId val="39638910"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="5656242"/>
+        <c:axId val="6505993"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2619,7 +3000,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41057891"/>
+        <c:crossAx val="39638910"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2627,7 +3008,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="41057891"/>
+        <c:axId val="39638910"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2703,7 +3084,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5656242"/>
+        <c:crossAx val="6505993"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2883,22 +3264,22 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2501</c:v>
+                  <c:v>2446</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2501</c:v>
+                  <c:v>2451</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2496</c:v>
+                  <c:v>2430</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2501</c:v>
+                  <c:v>2446</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>1766</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2106</c:v>
+                  <c:v>2171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2987,22 +3368,22 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2589</c:v>
+                  <c:v>2536</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2589</c:v>
+                  <c:v>2541</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2581</c:v>
+                  <c:v>2535</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2586</c:v>
+                  <c:v>2536</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1946</c:v>
+                  <c:v>1916</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2516</c:v>
+                  <c:v>2481</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3091,22 +3472,22 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2636</c:v>
+                  <c:v>2566</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2636</c:v>
+                  <c:v>2581</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2641</c:v>
+                  <c:v>2581</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2626</c:v>
+                  <c:v>2566</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2021</c:v>
+                  <c:v>1981</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2616</c:v>
+                  <c:v>2551</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3114,11 +3495,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="94970449"/>
-        <c:axId val="37593461"/>
+        <c:axId val="89937507"/>
+        <c:axId val="29399870"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="94970449"/>
+        <c:axId val="89937507"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3150,7 +3531,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37593461"/>
+        <c:crossAx val="29399870"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3158,7 +3539,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37593461"/>
+        <c:axId val="29399870"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3234,7 +3615,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94970449"/>
+        <c:crossAx val="89937507"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3672,151 +4053,151 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>259</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>260</v>
+        <v>387</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>261</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>262</v>
+        <v>389</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>263</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>264</v>
+        <v>391</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>265</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>266</v>
+        <v>393</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>267</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>268</v>
+        <v>395</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>269</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>270</v>
+        <v>397</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>271</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>272</v>
+        <v>399</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>273</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>274</v>
+        <v>401</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>275</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>276</v>
+        <v>403</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>277</v>
+        <v>404</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>278</v>
+        <v>405</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>279</v>
+        <v>406</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>280</v>
+        <v>407</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>281</v>
+        <v>408</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>282</v>
+        <v>409</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>283</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>284</v>
+        <v>411</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>285</v>
+        <v>412</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>286</v>
+        <v>413</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>287</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>288</v>
+        <v>415</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>289</v>
+        <v>416</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>290</v>
+        <v>417</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>291</v>
+        <v>418</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>242</v>
+        <v>369</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>292</v>
+        <v>419</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>293</v>
+        <v>420</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>294</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -3835,7 +4216,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F214"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -4001,16 +4382,16 @@
         <v>30</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1311</v>
+        <v>1277</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>0.9974</v>
+        <v>0.994936</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4021,16 +4402,16 @@
         <v>31</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>634</v>
+        <v>658</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1216</v>
+        <v>1197</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1883</v>
+        <v>1875</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>0.996845</v>
+        <v>0.996512</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4041,16 +4422,16 @@
         <v>32</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>1960</v>
+        <v>1969</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>0.997395</v>
+        <v>0.996732</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4141,16 +4522,16 @@
         <v>38</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1368</v>
+        <v>1335</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>0.995064</v>
+        <v>0.996207</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4201,16 +4582,16 @@
         <v>42</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>0.997502</v>
+        <v>0.997623</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4221,16 +4602,16 @@
         <v>43</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>528</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>1276</v>
+        <v>1285</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>0.996435</v>
+        <v>0.997665</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4244,13 +4625,13 @@
         <v>1645</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>2011</v>
+        <v>2001</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>0.982072</v>
+        <v>0.983494</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4261,16 +4642,16 @@
         <v>45</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>1438</v>
+        <v>1513</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>2206</v>
+        <v>2158</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2476</v>
+        <v>2416</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0.959074</v>
+        <v>0.970722</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4281,16 +4662,16 @@
         <v>46</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>1438</v>
+        <v>1513</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>2131</v>
+        <v>2116</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>2401</v>
+        <v>2356</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>0.984413</v>
+        <v>0.984351</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4304,13 +4685,13 @@
         <v>1645</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>2006</v>
+        <v>1996</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>2101</v>
+        <v>2116</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>0.98822</v>
+        <v>0.986194</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4324,13 +4705,13 @@
         <v>1540</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>2251</v>
+        <v>2259</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>0.986576</v>
+        <v>0.987008</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4344,13 +4725,13 @@
         <v>1645</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>2011</v>
+        <v>1996</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>2106</v>
+        <v>2081</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>0.985626</v>
+        <v>0.989505</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4361,16 +4742,16 @@
         <v>50</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>1415</v>
+        <v>1521</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>1916</v>
+        <v>1913</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0.987496</v>
+        <v>0.985123</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4381,16 +4762,16 @@
         <v>51</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>1409</v>
+        <v>1481</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>1824</v>
+        <v>1816</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>1936</v>
+        <v>1961</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>0.977653</v>
+        <v>0.979452</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4401,16 +4782,16 @@
         <v>52</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>1415</v>
+        <v>1466</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>1911</v>
+        <v>1896</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>0.991026</v>
+        <v>0.990826</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4421,16 +4802,16 @@
         <v>53</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>1409</v>
+        <v>1431</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>1801</v>
+        <v>1996</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>1906</v>
+        <v>2181</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0.989727</v>
+        <v>0.984303</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4441,16 +4822,16 @@
         <v>54</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>1471</v>
+        <v>1521</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>1916</v>
+        <v>1906</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>2006</v>
+        <v>2011</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>0.990728</v>
+        <v>0.989135</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4461,16 +4842,16 @@
         <v>55</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>1421</v>
+        <v>1481</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>1991</v>
+        <v>1796</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>2193</v>
+        <v>1911</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>0.982688</v>
+        <v>0.98804</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4481,16 +4862,16 @@
         <v>56</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>2501</v>
+        <v>2446</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>2589</v>
+        <v>2536</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>2636</v>
+        <v>2566</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>0.996527</v>
+        <v>0.997208</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4501,16 +4882,16 @@
         <v>57</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1441</v>
+        <v>2446</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>1596</v>
+        <v>2536</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>1646</v>
+        <v>2566</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0.994649</v>
+        <v>0.997168</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4521,16 +4902,16 @@
         <v>58</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>2501</v>
+        <v>1626</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>2589</v>
+        <v>1821</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>2631</v>
+        <v>1881</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>0.996392</v>
+        <v>0.995637</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4541,16 +4922,16 @@
         <v>59</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1671</v>
+        <v>1406</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>1851</v>
+        <v>1551</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>1906</v>
+        <v>1606</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>0.993581</v>
+        <v>0.993787</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4581,16 +4962,16 @@
         <v>63</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>2501</v>
+        <v>2451</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>2589</v>
+        <v>2541</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>2636</v>
+        <v>2581</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0.996527</v>
+        <v>0.997409</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4601,16 +4982,16 @@
         <v>64</v>
       </c>
       <c r="C41" s="8" t="n">
-        <v>2496</v>
+        <v>2430</v>
       </c>
       <c r="D41" s="8" t="n">
+        <v>2535</v>
+      </c>
+      <c r="E41" s="8" t="n">
         <v>2581</v>
       </c>
-      <c r="E41" s="8" t="n">
-        <v>2641</v>
-      </c>
       <c r="F41" s="9" t="n">
-        <v>0.996573</v>
+        <v>0.996309</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4621,16 +5002,16 @@
         <v>65</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>2501</v>
+        <v>2446</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>2586</v>
+        <v>2536</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>2626</v>
+        <v>2566</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>0.997107</v>
+        <v>0.997105</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4644,13 +5025,13 @@
         <v>1766</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>1946</v>
+        <v>1916</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>2021</v>
+        <v>1981</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>0.994142</v>
+        <v>0.995359</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4661,16 +5042,16 @@
         <v>67</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>2106</v>
+        <v>2171</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>2516</v>
+        <v>2481</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>2616</v>
+        <v>2551</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>0.997063</v>
+        <v>0.997721</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4681,16 +5062,16 @@
         <v>69</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>2501</v>
+        <v>2446</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>2589</v>
+        <v>2536</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>2636</v>
+        <v>2566</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>0.996527</v>
+        <v>0.997208</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4701,16 +5082,16 @@
         <v>70</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>2436</v>
+        <v>2381</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>2531</v>
+        <v>2486</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>2561</v>
+        <v>2521</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>0.996404</v>
+        <v>0.996779</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4721,16 +5102,16 @@
         <v>71</v>
       </c>
       <c r="C47" s="8" t="n">
-        <v>2501</v>
+        <v>2446</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>2589</v>
+        <v>2536</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>2631</v>
+        <v>2566</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>0.996392</v>
+        <v>0.997168</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4741,16 +5122,16 @@
         <v>72</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1441</v>
+        <v>1406</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1596</v>
+        <v>1551</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1646</v>
+        <v>1606</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>0.994649</v>
+        <v>0.993787</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4761,16 +5142,16 @@
         <v>73</v>
       </c>
       <c r="C49" s="8" t="n">
-        <v>1636</v>
+        <v>1586</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>1846</v>
+        <v>1801</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>1891</v>
+        <v>1866</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>0.994479</v>
+        <v>0.995802</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4781,16 +5162,16 @@
         <v>74</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1671</v>
+        <v>1626</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>1851</v>
+        <v>1821</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1906</v>
+        <v>1881</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>0.993581</v>
+        <v>0.995637</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4801,16 +5182,16 @@
         <v>76</v>
       </c>
       <c r="C51" s="8" t="n">
-        <v>1602</v>
+        <v>1743</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>2040</v>
+        <v>2031</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>2126</v>
+        <v>2121</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>0.984329</v>
+        <v>0.986778</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4824,13 +5205,13 @@
         <v>1645</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>2011</v>
+        <v>1996</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>2106</v>
+        <v>2116</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>0.985626</v>
+        <v>0.986194</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4841,16 +5222,16 @@
         <v>78</v>
       </c>
       <c r="C53" s="8" t="n">
-        <v>1611</v>
+        <v>1606</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>2201</v>
+        <v>2116</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>0.980777</v>
+        <v>0.98646</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4861,16 +5242,16 @@
         <v>79</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>1431</v>
+        <v>1410</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>2046</v>
+        <v>2041</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>2211</v>
+        <v>2141</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>0.983414</v>
+        <v>0.987119</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4881,16 +5262,16 @@
         <v>80</v>
       </c>
       <c r="C55" s="8" t="n">
-        <v>1666</v>
+        <v>1551</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>2061</v>
+        <v>2051</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>2302</v>
+        <v>2401</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>0.980665</v>
+        <v>0.982669</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4901,16 +5282,16 @@
         <v>81</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>1625</v>
+        <v>1486</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>2036</v>
+        <v>2041</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>2121</v>
+        <v>2502</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>0.981109</v>
+        <v>0.982345</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4927,10 +5308,10 @@
         <v>2066</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>2701</v>
+        <v>2303</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>0.973292</v>
+        <v>0.976919</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4941,16 +5322,16 @@
         <v>83</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>1639</v>
+        <v>1681</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>2045</v>
+        <v>2051</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>2146</v>
+        <v>2201</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>0.979466</v>
+        <v>0.981511</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4961,16 +5342,16 @@
         <v>84</v>
       </c>
       <c r="C59" s="8" t="n">
-        <v>2511</v>
+        <v>2481</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>2601</v>
+        <v>2551</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>2646</v>
+        <v>2596</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>0.996431</v>
+        <v>0.99752</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4981,16 +5362,16 @@
         <v>85</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>2501</v>
+        <v>2446</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>2589</v>
+        <v>2536</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>2636</v>
+        <v>2566</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>0.996527</v>
+        <v>0.997208</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5001,16 +5382,16 @@
         <v>86</v>
       </c>
       <c r="C61" s="8" t="n">
-        <v>2491</v>
+        <v>2401</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>2568</v>
+        <v>2507</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>2606</v>
+        <v>2541</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>0.996691</v>
+        <v>0.997033</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5021,16 +5402,16 @@
         <v>87</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>2506</v>
+        <v>2466</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>2603</v>
+        <v>2567</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>2651</v>
+        <v>2611</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>0.996986</v>
+        <v>0.997024</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5041,16 +5422,16 @@
         <v>88</v>
       </c>
       <c r="C63" s="8" t="n">
-        <v>2496</v>
+        <v>2416</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>2578</v>
+        <v>2546</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>2621</v>
+        <v>2581</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>0.996601</v>
+        <v>0.997119</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5061,16 +5442,16 @@
         <v>89</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>2491</v>
+        <v>2451</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>2581</v>
+        <v>2526</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>2621</v>
+        <v>2561</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>0.995811</v>
+        <v>0.997042</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5081,16 +5462,16 @@
         <v>90</v>
       </c>
       <c r="C65" s="8" t="n">
-        <v>2531</v>
+        <v>2476</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>2634</v>
+        <v>2581</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>2671</v>
+        <v>2621</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>0.996847</v>
+        <v>0.997118</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5101,16 +5482,16 @@
         <v>91</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>2471</v>
+        <v>2446</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>2606</v>
+        <v>2541</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>2636</v>
+        <v>2571</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0.996435</v>
+        <v>0.996922</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5121,16 +5502,16 @@
         <v>92</v>
       </c>
       <c r="C67" s="8" t="n">
-        <v>2511</v>
+        <v>2481</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>2601</v>
+        <v>2551</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>2646</v>
+        <v>2596</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>0.996428</v>
+        <v>0.997438</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5141,16 +5522,16 @@
         <v>93</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>2501</v>
+        <v>2446</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>2589</v>
+        <v>2536</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>2631</v>
+        <v>2566</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>0.996392</v>
+        <v>0.997168</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5161,16 +5542,16 @@
         <v>94</v>
       </c>
       <c r="C69" s="8" t="n">
-        <v>2491</v>
+        <v>2401</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>2568</v>
+        <v>2507</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>2601</v>
+        <v>2541</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>0.996703</v>
+        <v>0.997081</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5181,16 +5562,16 @@
         <v>95</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>2506</v>
+        <v>2466</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>2603</v>
+        <v>2567</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>2646</v>
+        <v>2611</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>0.997105</v>
+        <v>0.997048</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5201,16 +5582,16 @@
         <v>96</v>
       </c>
       <c r="C71" s="8" t="n">
-        <v>2496</v>
+        <v>2416</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>2578</v>
+        <v>2546</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>2626</v>
+        <v>2581</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>0.996407</v>
+        <v>0.99721</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5221,16 +5602,16 @@
         <v>97</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>2491</v>
+        <v>2451</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>2581</v>
+        <v>2526</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>2641</v>
+        <v>2566</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>0.995049</v>
+        <v>0.996856</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5241,16 +5622,16 @@
         <v>98</v>
       </c>
       <c r="C73" s="8" t="n">
-        <v>2531</v>
+        <v>2476</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>2634</v>
+        <v>2581</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>2676</v>
+        <v>2621</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>0.996544</v>
+        <v>0.996897</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5261,16 +5642,16 @@
         <v>99</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>2471</v>
+        <v>2446</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>2606</v>
+        <v>2541</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2641</v>
+        <v>2571</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>0.996132</v>
+        <v>0.997079</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5281,16 +5662,16 @@
         <v>100</v>
       </c>
       <c r="C75" s="8" t="n">
-        <v>1466</v>
+        <v>1636</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>1651</v>
+        <v>1866</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>1696</v>
+        <v>1911</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>0.993332</v>
+        <v>0.994081</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5301,16 +5682,16 @@
         <v>101</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>1441</v>
+        <v>1626</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>1596</v>
+        <v>1821</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1646</v>
+        <v>1881</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>0.994649</v>
+        <v>0.995637</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5321,16 +5702,16 @@
         <v>102</v>
       </c>
       <c r="C77" s="8" t="n">
-        <v>1421</v>
+        <v>1596</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>1606</v>
+        <v>1826</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>1651</v>
+        <v>1876</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>0.994033</v>
+        <v>0.995765</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5341,16 +5722,16 @@
         <v>103</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>1446</v>
+        <v>1681</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>1641</v>
+        <v>1861</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>1691</v>
+        <v>1901</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>0.994139</v>
+        <v>0.992752</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5361,16 +5742,16 @@
         <v>104</v>
       </c>
       <c r="C79" s="8" t="n">
-        <v>1451</v>
+        <v>1681</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>1636</v>
+        <v>1871</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>1696</v>
+        <v>1921</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>0.992346</v>
+        <v>0.993602</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5381,16 +5762,16 @@
         <v>105</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>1391</v>
+        <v>1671</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>1596</v>
+        <v>1831</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1651</v>
+        <v>1876</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>0.993827</v>
+        <v>0.995833</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5401,16 +5782,16 @@
         <v>106</v>
       </c>
       <c r="C81" s="8" t="n">
-        <v>1481</v>
+        <v>1646</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>1646</v>
+        <v>1871</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>1701</v>
+        <v>1916</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>0.992082</v>
+        <v>0.994856</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5421,16 +5802,16 @@
         <v>107</v>
       </c>
       <c r="C82" s="11" t="n">
-        <v>1446</v>
+        <v>1676</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>1646</v>
+        <v>1851</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>1701</v>
+        <v>1901</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>0.99434</v>
+        <v>0.994335</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5441,16 +5822,16 @@
         <v>108</v>
       </c>
       <c r="C83" s="8" t="n">
-        <v>1661</v>
+        <v>1386</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>1891</v>
+        <v>1636</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>1951</v>
+        <v>1671</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>0.994434</v>
+        <v>0.993522</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5461,16 +5842,16 @@
         <v>109</v>
       </c>
       <c r="C84" s="11" t="n">
-        <v>1671</v>
+        <v>1406</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>1851</v>
+        <v>1551</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>1906</v>
+        <v>1606</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>0.993581</v>
+        <v>0.993787</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5481,16 +5862,16 @@
         <v>110</v>
       </c>
       <c r="C85" s="8" t="n">
-        <v>1646</v>
+        <v>1346</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>1851</v>
+        <v>1571</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>1921</v>
+        <v>1631</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>0.994472</v>
+        <v>0.994742</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5501,16 +5882,16 @@
         <v>111</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>1716</v>
+        <v>1436</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>1881</v>
+        <v>1626</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>1941</v>
+        <v>1676</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>0.993319</v>
+        <v>0.992915</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5521,16 +5902,16 @@
         <v>112</v>
       </c>
       <c r="C87" s="8" t="n">
-        <v>1716</v>
+        <v>1436</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>1891</v>
+        <v>1631</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>1951</v>
+        <v>1666</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>0.993293</v>
+        <v>0.993628</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5541,16 +5922,16 @@
         <v>113</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>1641</v>
+        <v>1396</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>1856</v>
+        <v>1566</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>1916</v>
+        <v>1616</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>0.994133</v>
+        <v>0.993724</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5561,16 +5942,16 @@
         <v>114</v>
       </c>
       <c r="C89" s="8" t="n">
-        <v>1681</v>
+        <v>1476</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>1881</v>
+        <v>1621</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>1956</v>
+        <v>1671</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>0.993912</v>
+        <v>0.994442</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5581,16 +5962,2496 @@
         <v>115</v>
       </c>
       <c r="C90" s="11" t="n">
+        <v>1416</v>
+      </c>
+      <c r="D90" s="11" t="n">
+        <v>1626</v>
+      </c>
+      <c r="E90" s="11" t="n">
+        <v>1666</v>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>0.993002</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C91" s="8" t="n">
+        <v>2061</v>
+      </c>
+      <c r="D91" s="8" t="n">
+        <v>2141</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>2176</v>
+      </c>
+      <c r="F91" s="9" t="n">
+        <v>0.997941</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C92" s="11" t="n">
+        <v>1971</v>
+      </c>
+      <c r="D92" s="11" t="n">
+        <v>2062</v>
+      </c>
+      <c r="E92" s="11" t="n">
+        <v>2091</v>
+      </c>
+      <c r="F92" s="12" t="n">
+        <v>0.997036</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C93" s="8" t="n">
+        <v>1336</v>
+      </c>
+      <c r="D93" s="8" t="n">
+        <v>1506</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>1546</v>
+      </c>
+      <c r="F93" s="9" t="n">
+        <v>0.99502</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C94" s="11" t="n">
+        <v>1361</v>
+      </c>
+      <c r="D94" s="11" t="n">
+        <v>1566</v>
+      </c>
+      <c r="E94" s="11" t="n">
+        <v>1616</v>
+      </c>
+      <c r="F94" s="12" t="n">
+        <v>0.99394</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C95" s="8" t="n">
+        <v>2246</v>
+      </c>
+      <c r="D95" s="8" t="n">
+        <v>2321</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>2351</v>
+      </c>
+      <c r="F95" s="9" t="n">
+        <v>0.997584</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B96" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C96" s="11" t="n">
+        <v>2156</v>
+      </c>
+      <c r="D96" s="11" t="n">
+        <v>2231</v>
+      </c>
+      <c r="E96" s="11" t="n">
+        <v>2261</v>
+      </c>
+      <c r="F96" s="12" t="n">
+        <v>0.997196</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C97" s="8" t="n">
+        <v>1426</v>
+      </c>
+      <c r="D97" s="8" t="n">
+        <v>1611</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>1661</v>
+      </c>
+      <c r="F97" s="9" t="n">
+        <v>0.995774</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B98" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C98" s="11" t="n">
+        <v>1491</v>
+      </c>
+      <c r="D98" s="11" t="n">
+        <v>1686</v>
+      </c>
+      <c r="E98" s="11" t="n">
         <v>1721</v>
       </c>
-      <c r="D90" s="11" t="n">
-        <v>1876</v>
-      </c>
-      <c r="E90" s="11" t="n">
-        <v>1926</v>
-      </c>
-      <c r="F90" s="12" t="n">
-        <v>0.995348</v>
+      <c r="F98" s="12" t="n">
+        <v>0.99558</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C99" s="8" t="n">
+        <v>2446</v>
+      </c>
+      <c r="D99" s="8" t="n">
+        <v>2536</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>2566</v>
+      </c>
+      <c r="F99" s="9" t="n">
+        <v>0.997168</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B100" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C100" s="11" t="n">
+        <v>1626</v>
+      </c>
+      <c r="D100" s="11" t="n">
+        <v>1821</v>
+      </c>
+      <c r="E100" s="11" t="n">
+        <v>1881</v>
+      </c>
+      <c r="F100" s="12" t="n">
+        <v>0.995637</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C101" s="8" t="n">
+        <v>970</v>
+      </c>
+      <c r="D101" s="8" t="n">
+        <v>1377</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F101" s="9" t="n">
+        <v>0.99521</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B102" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C102" s="11" t="n">
+        <v>1410</v>
+      </c>
+      <c r="D102" s="11" t="n">
+        <v>1437</v>
+      </c>
+      <c r="E102" s="11" t="n">
+        <v>1457</v>
+      </c>
+      <c r="F102" s="12" t="n">
+        <v>0.991819</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C103" s="8" t="n">
+        <v>350</v>
+      </c>
+      <c r="D103" s="8" t="n">
+        <v>765</v>
+      </c>
+      <c r="E103" s="8" t="n">
+        <v>1375</v>
+      </c>
+      <c r="F103" s="9" t="n">
+        <v>0.995336</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B104" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C104" s="11" t="n">
+        <v>407</v>
+      </c>
+      <c r="D104" s="11" t="n">
+        <v>756</v>
+      </c>
+      <c r="E104" s="11" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>0.994919</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C105" s="8" t="n">
+        <v>1121</v>
+      </c>
+      <c r="D105" s="8" t="n">
+        <v>1156</v>
+      </c>
+      <c r="E105" s="8" t="n">
+        <v>1174</v>
+      </c>
+      <c r="F105" s="9" t="n">
+        <v>0.980272</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B106" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C106" s="11" t="n">
+        <v>1219</v>
+      </c>
+      <c r="D106" s="11" t="n">
+        <v>1262</v>
+      </c>
+      <c r="E106" s="11" t="n">
+        <v>1278</v>
+      </c>
+      <c r="F106" s="12" t="n">
+        <v>0.991184</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C107" s="8" t="n">
+        <v>988</v>
+      </c>
+      <c r="D107" s="8" t="n">
+        <v>1230</v>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>1652</v>
+      </c>
+      <c r="F107" s="9" t="n">
+        <v>0.994295</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B108" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C108" s="11" t="n">
+        <v>1374</v>
+      </c>
+      <c r="D108" s="11" t="n">
+        <v>2176</v>
+      </c>
+      <c r="E108" s="11" t="n">
+        <v>2713</v>
+      </c>
+      <c r="F108" s="12" t="n">
+        <v>0.990811</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C109" s="8" t="n">
+        <v>390</v>
+      </c>
+      <c r="D109" s="8" t="n">
+        <v>601</v>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>861</v>
+      </c>
+      <c r="F109" s="9" t="n">
+        <v>0.996734</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B110" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C110" s="11" t="n">
+        <v>1388</v>
+      </c>
+      <c r="D110" s="11" t="n">
+        <v>1435</v>
+      </c>
+      <c r="E110" s="11" t="n">
+        <v>1455</v>
+      </c>
+      <c r="F110" s="12" t="n">
+        <v>0.988878</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C111" s="8" t="n">
+        <v>1161</v>
+      </c>
+      <c r="D111" s="8" t="n">
+        <v>1546</v>
+      </c>
+      <c r="E111" s="8" t="n">
+        <v>2902</v>
+      </c>
+      <c r="F111" s="9" t="n">
+        <v>0.980928</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B112" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C112" s="11" t="n">
+        <v>1161</v>
+      </c>
+      <c r="D112" s="11" t="n">
+        <v>1536</v>
+      </c>
+      <c r="E112" s="11" t="n">
+        <v>1905</v>
+      </c>
+      <c r="F112" s="12" t="n">
+        <v>0.987968</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C113" s="8" t="n">
+        <v>1383</v>
+      </c>
+      <c r="D113" s="8" t="n">
+        <v>1586</v>
+      </c>
+      <c r="E113" s="8" t="n">
+        <v>1842</v>
+      </c>
+      <c r="F113" s="9" t="n">
+        <v>0.994</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C114" s="11" t="n">
+        <v>971</v>
+      </c>
+      <c r="D114" s="11" t="n">
+        <v>1141</v>
+      </c>
+      <c r="E114" s="11" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F114" s="12" t="n">
+        <v>0.9931</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C115" s="8" t="n">
+        <v>845</v>
+      </c>
+      <c r="D115" s="8" t="n">
+        <v>986</v>
+      </c>
+      <c r="E115" s="8" t="n">
+        <v>1118</v>
+      </c>
+      <c r="F115" s="9" t="n">
+        <v>0.9887</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B116" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C116" s="11" t="n">
+        <v>281</v>
+      </c>
+      <c r="D116" s="11" t="n">
+        <v>306</v>
+      </c>
+      <c r="E116" s="11" t="n">
+        <v>320</v>
+      </c>
+      <c r="F116" s="12" t="n">
+        <v>0.9887</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C117" s="8" t="n">
+        <v>557</v>
+      </c>
+      <c r="D117" s="8" t="n">
+        <v>666</v>
+      </c>
+      <c r="E117" s="8" t="n">
+        <v>779</v>
+      </c>
+      <c r="F117" s="9" t="n">
+        <v>0.987</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B118" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C118" s="11" t="n">
+        <v>932</v>
+      </c>
+      <c r="D118" s="11" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E118" s="11" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F118" s="12" t="n">
+        <v>0.9896</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C119" s="8" t="n">
+        <v>728</v>
+      </c>
+      <c r="D119" s="8" t="n">
+        <v>870</v>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>1029</v>
+      </c>
+      <c r="F119" s="9" t="n">
+        <v>0.9879</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B120" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C120" s="11" t="n">
+        <v>990</v>
+      </c>
+      <c r="D120" s="11" t="n">
+        <v>1158</v>
+      </c>
+      <c r="E120" s="11" t="n">
+        <v>1321</v>
+      </c>
+      <c r="F120" s="12" t="n">
+        <v>0.9943</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C121" s="8" t="n">
+        <v>1037</v>
+      </c>
+      <c r="D121" s="8" t="n">
+        <v>1240</v>
+      </c>
+      <c r="E121" s="8" t="n">
+        <v>1435</v>
+      </c>
+      <c r="F121" s="9" t="n">
+        <v>0.9913</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B122" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C122" s="11" t="n">
+        <v>395</v>
+      </c>
+      <c r="D122" s="11" t="n">
+        <v>429</v>
+      </c>
+      <c r="E122" s="11" t="n">
+        <v>450</v>
+      </c>
+      <c r="F122" s="12" t="n">
+        <v>0.9908</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C123" s="8" t="n">
+        <v>302</v>
+      </c>
+      <c r="D123" s="8" t="n">
+        <v>328</v>
+      </c>
+      <c r="E123" s="8" t="n">
+        <v>347</v>
+      </c>
+      <c r="F123" s="9" t="n">
+        <v>0.9806</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B124" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C124" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="E124" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="F124" s="12" t="n">
+        <v>0.2382</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C125" s="8" t="n">
+        <v>182</v>
+      </c>
+      <c r="D125" s="8" t="n">
+        <v>194</v>
+      </c>
+      <c r="E125" s="8" t="n">
+        <v>201</v>
+      </c>
+      <c r="F125" s="9" t="n">
+        <v>0.0547</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B126" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C126" s="11" t="n">
+        <v>1019</v>
+      </c>
+      <c r="D126" s="11" t="n">
+        <v>1210</v>
+      </c>
+      <c r="E126" s="11" t="n">
+        <v>1410</v>
+      </c>
+      <c r="F126" s="12" t="n">
+        <v>0.992</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C127" s="8" t="n">
+        <v>1017</v>
+      </c>
+      <c r="D127" s="8" t="n">
+        <v>1194</v>
+      </c>
+      <c r="E127" s="8" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F127" s="9" t="n">
+        <v>0.9912</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B128" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C128" s="11" t="n">
+        <v>284</v>
+      </c>
+      <c r="D128" s="11" t="n">
+        <v>314</v>
+      </c>
+      <c r="E128" s="11" t="n">
+        <v>321</v>
+      </c>
+      <c r="F128" s="12" t="n">
+        <v>0.9698</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C129" s="8" t="n">
+        <v>201</v>
+      </c>
+      <c r="D129" s="8" t="n">
+        <v>209</v>
+      </c>
+      <c r="E129" s="8" t="n">
+        <v>220</v>
+      </c>
+      <c r="F129" s="9" t="n">
+        <v>0.9532</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B130" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C130" s="11" t="n">
+        <v>988</v>
+      </c>
+      <c r="D130" s="11" t="n">
+        <v>1230</v>
+      </c>
+      <c r="E130" s="11" t="n">
+        <v>1652</v>
+      </c>
+      <c r="F130" s="12" t="n">
+        <v>0.9943</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C131" s="8" t="n">
+        <v>764</v>
+      </c>
+      <c r="D131" s="8" t="n">
+        <v>913</v>
+      </c>
+      <c r="E131" s="8" t="n">
+        <v>1207</v>
+      </c>
+      <c r="F131" s="9" t="n">
+        <v>0.9917</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B132" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C132" s="11" t="n">
+        <v>648</v>
+      </c>
+      <c r="D132" s="11" t="n">
+        <v>771</v>
+      </c>
+      <c r="E132" s="11" t="n">
+        <v>1046</v>
+      </c>
+      <c r="F132" s="12" t="n">
+        <v>0.9894</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C133" s="8" t="n">
+        <v>262</v>
+      </c>
+      <c r="D133" s="8" t="n">
+        <v>285</v>
+      </c>
+      <c r="E133" s="8" t="n">
+        <v>311</v>
+      </c>
+      <c r="F133" s="9" t="n">
+        <v>0.9926</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B134" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C134" s="11" t="n">
+        <v>504</v>
+      </c>
+      <c r="D134" s="11" t="n">
+        <v>566</v>
+      </c>
+      <c r="E134" s="11" t="n">
+        <v>752</v>
+      </c>
+      <c r="F134" s="12" t="n">
+        <v>0.9841</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C135" s="8" t="n">
+        <v>720</v>
+      </c>
+      <c r="D135" s="8" t="n">
+        <v>867</v>
+      </c>
+      <c r="E135" s="8" t="n">
+        <v>1158</v>
+      </c>
+      <c r="F135" s="9" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B136" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C136" s="11" t="n">
+        <v>572</v>
+      </c>
+      <c r="D136" s="11" t="n">
+        <v>675</v>
+      </c>
+      <c r="E136" s="11" t="n">
+        <v>913</v>
+      </c>
+      <c r="F136" s="12" t="n">
+        <v>0.9901</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C137" s="8" t="n">
+        <v>765</v>
+      </c>
+      <c r="D137" s="8" t="n">
+        <v>920</v>
+      </c>
+      <c r="E137" s="8" t="n">
+        <v>1252</v>
+      </c>
+      <c r="F137" s="9" t="n">
+        <v>0.9896</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B138" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C138" s="11" t="n">
+        <v>821</v>
+      </c>
+      <c r="D138" s="11" t="n">
+        <v>986</v>
+      </c>
+      <c r="E138" s="11" t="n">
+        <v>1334</v>
+      </c>
+      <c r="F138" s="12" t="n">
+        <v>0.9884</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C139" s="8" t="n">
+        <v>351</v>
+      </c>
+      <c r="D139" s="8" t="n">
+        <v>390</v>
+      </c>
+      <c r="E139" s="8" t="n">
+        <v>434</v>
+      </c>
+      <c r="F139" s="9" t="n">
+        <v>0.9884</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B140" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C140" s="11" t="n">
+        <v>281</v>
+      </c>
+      <c r="D140" s="11" t="n">
+        <v>304</v>
+      </c>
+      <c r="E140" s="11" t="n">
+        <v>336</v>
+      </c>
+      <c r="F140" s="12" t="n">
+        <v>0.9883</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E141" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="F141" s="9" t="n">
+        <v>0.2185</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B142" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="C142" s="11" t="n">
+        <v>161</v>
+      </c>
+      <c r="D142" s="11" t="n">
+        <v>186</v>
+      </c>
+      <c r="E142" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="F142" s="12" t="n">
+        <v>0.0528</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C143" s="8" t="n">
+        <v>798</v>
+      </c>
+      <c r="D143" s="8" t="n">
+        <v>954</v>
+      </c>
+      <c r="E143" s="8" t="n">
+        <v>1283</v>
+      </c>
+      <c r="F143" s="9" t="n">
+        <v>0.991</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B144" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C144" s="11" t="n">
+        <v>786</v>
+      </c>
+      <c r="D144" s="11" t="n">
+        <v>930</v>
+      </c>
+      <c r="E144" s="11" t="n">
+        <v>1266</v>
+      </c>
+      <c r="F144" s="12" t="n">
+        <v>0.9916</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C145" s="8" t="n">
+        <v>264</v>
+      </c>
+      <c r="D145" s="8" t="n">
+        <v>295</v>
+      </c>
+      <c r="E145" s="8" t="n">
+        <v>320</v>
+      </c>
+      <c r="F145" s="9" t="n">
+        <v>0.9584</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B146" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C146" s="11" t="n">
+        <v>181</v>
+      </c>
+      <c r="D146" s="11" t="n">
+        <v>203</v>
+      </c>
+      <c r="E146" s="11" t="n">
+        <v>220</v>
+      </c>
+      <c r="F146" s="12" t="n">
+        <v>0.9415</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C147" s="8" t="n">
+        <v>1324</v>
+      </c>
+      <c r="D147" s="8" t="n">
+        <v>2352</v>
+      </c>
+      <c r="E147" s="8" t="n">
+        <v>3504</v>
+      </c>
+      <c r="F147" s="9" t="n">
+        <v>0.9942</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B148" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="C148" s="11" t="n">
+        <v>1141</v>
+      </c>
+      <c r="D148" s="11" t="n">
+        <v>1953</v>
+      </c>
+      <c r="E148" s="11" t="n">
+        <v>2938</v>
+      </c>
+      <c r="F148" s="12" t="n">
+        <v>0.9932</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C149" s="8" t="n">
+        <v>981</v>
+      </c>
+      <c r="D149" s="8" t="n">
+        <v>1676</v>
+      </c>
+      <c r="E149" s="8" t="n">
+        <v>2514</v>
+      </c>
+      <c r="F149" s="9" t="n">
+        <v>0.992</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C150" s="11" t="n">
+        <v>760</v>
+      </c>
+      <c r="D150" s="11" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E150" s="11" t="n">
+        <v>1665</v>
+      </c>
+      <c r="F150" s="12" t="n">
+        <v>0.9801</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C151" s="8" t="n">
+        <v>785</v>
+      </c>
+      <c r="D151" s="8" t="n">
+        <v>1099</v>
+      </c>
+      <c r="E151" s="8" t="n">
+        <v>1682</v>
+      </c>
+      <c r="F151" s="9" t="n">
+        <v>0.9919</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B152" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C152" s="11" t="n">
+        <v>1081</v>
+      </c>
+      <c r="D152" s="11" t="n">
+        <v>1847</v>
+      </c>
+      <c r="E152" s="11" t="n">
+        <v>2776</v>
+      </c>
+      <c r="F152" s="12" t="n">
+        <v>0.9937</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C153" s="8" t="n">
+        <v>863</v>
+      </c>
+      <c r="D153" s="8" t="n">
+        <v>1475</v>
+      </c>
+      <c r="E153" s="8" t="n">
+        <v>2226</v>
+      </c>
+      <c r="F153" s="9" t="n">
+        <v>0.9926</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B154" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C154" s="11" t="n">
+        <v>1158</v>
+      </c>
+      <c r="D154" s="11" t="n">
+        <v>1980</v>
+      </c>
+      <c r="E154" s="11" t="n">
+        <v>2982</v>
+      </c>
+      <c r="F154" s="12" t="n">
+        <v>0.9935</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C155" s="8" t="n">
+        <v>1196</v>
+      </c>
+      <c r="D155" s="8" t="n">
+        <v>2043</v>
+      </c>
+      <c r="E155" s="8" t="n">
+        <v>3077</v>
+      </c>
+      <c r="F155" s="9" t="n">
+        <v>0.9942</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B156" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C156" s="11" t="n">
+        <v>874</v>
+      </c>
+      <c r="D156" s="11" t="n">
+        <v>1245</v>
+      </c>
+      <c r="E156" s="11" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F156" s="12" t="n">
+        <v>0.9772</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B157" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C157" s="8" t="n">
+        <v>774</v>
+      </c>
+      <c r="D157" s="8" t="n">
+        <v>1047</v>
+      </c>
+      <c r="E157" s="8" t="n">
+        <v>1705</v>
+      </c>
+      <c r="F157" s="9" t="n">
+        <v>0.9768</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B158" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C158" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D158" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="E158" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="F158" s="12" t="n">
+        <v>0.8329</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B159" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C159" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="F159" s="9" t="n">
+        <v>0.0288</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B160" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C160" s="11" t="n">
+        <v>1158</v>
+      </c>
+      <c r="D160" s="11" t="n">
+        <v>1980</v>
+      </c>
+      <c r="E160" s="11" t="n">
+        <v>2982</v>
+      </c>
+      <c r="F160" s="12" t="n">
+        <v>0.9935</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B161" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="C161" s="8" t="n">
+        <v>1141</v>
+      </c>
+      <c r="D161" s="8" t="n">
+        <v>1953</v>
+      </c>
+      <c r="E161" s="8" t="n">
+        <v>2938</v>
+      </c>
+      <c r="F161" s="9" t="n">
+        <v>0.9932</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B162" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C162" s="11" t="n">
+        <v>774</v>
+      </c>
+      <c r="D162" s="11" t="n">
+        <v>1047</v>
+      </c>
+      <c r="E162" s="11" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F162" s="12" t="n">
+        <v>0.9768</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B163" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C163" s="8" t="n">
+        <v>674</v>
+      </c>
+      <c r="D163" s="8" t="n">
+        <v>848</v>
+      </c>
+      <c r="E163" s="8" t="n">
+        <v>1229</v>
+      </c>
+      <c r="F163" s="9" t="n">
+        <v>0.9446</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B164" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="C164" s="11" t="n">
+        <v>1374</v>
+      </c>
+      <c r="D164" s="11" t="n">
+        <v>2176</v>
+      </c>
+      <c r="E164" s="11" t="n">
+        <v>2713</v>
+      </c>
+      <c r="F164" s="12" t="n">
+        <v>0.9908</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B165" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C165" s="8" t="n">
+        <v>1182</v>
+      </c>
+      <c r="D165" s="8" t="n">
+        <v>1814</v>
+      </c>
+      <c r="E165" s="8" t="n">
+        <v>2272</v>
+      </c>
+      <c r="F165" s="9" t="n">
+        <v>0.9911</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B166" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C166" s="11" t="n">
+        <v>1014</v>
+      </c>
+      <c r="D166" s="11" t="n">
+        <v>1560</v>
+      </c>
+      <c r="E166" s="11" t="n">
+        <v>1952</v>
+      </c>
+      <c r="F166" s="12" t="n">
+        <v>0.9884</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B167" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C167" s="8" t="n">
+        <v>774</v>
+      </c>
+      <c r="D167" s="8" t="n">
+        <v>974</v>
+      </c>
+      <c r="E167" s="8" t="n">
+        <v>1016</v>
+      </c>
+      <c r="F167" s="9" t="n">
+        <v>0.9649</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B168" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C168" s="11" t="n">
+        <v>804</v>
+      </c>
+      <c r="D168" s="11" t="n">
+        <v>1057</v>
+      </c>
+      <c r="E168" s="11" t="n">
+        <v>1397</v>
+      </c>
+      <c r="F168" s="12" t="n">
+        <v>0.9858</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B169" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C169" s="8" t="n">
+        <v>1118</v>
+      </c>
+      <c r="D169" s="8" t="n">
+        <v>1716</v>
+      </c>
+      <c r="E169" s="8" t="n">
+        <v>2149</v>
+      </c>
+      <c r="F169" s="9" t="n">
+        <v>0.9887</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B170" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="C170" s="11" t="n">
+        <v>893</v>
+      </c>
+      <c r="D170" s="11" t="n">
+        <v>1374</v>
+      </c>
+      <c r="E170" s="11" t="n">
+        <v>1721</v>
+      </c>
+      <c r="F170" s="12" t="n">
+        <v>0.9886</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B171" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C171" s="8" t="n">
+        <v>1199</v>
+      </c>
+      <c r="D171" s="8" t="n">
+        <v>1843</v>
+      </c>
+      <c r="E171" s="8" t="n">
+        <v>2302</v>
+      </c>
+      <c r="F171" s="9" t="n">
+        <v>0.9897</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B172" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C172" s="11" t="n">
+        <v>1237</v>
+      </c>
+      <c r="D172" s="11" t="n">
+        <v>1900</v>
+      </c>
+      <c r="E172" s="11" t="n">
+        <v>2384</v>
+      </c>
+      <c r="F172" s="12" t="n">
+        <v>0.9911</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C173" s="8" t="n">
+        <v>894</v>
+      </c>
+      <c r="D173" s="8" t="n">
+        <v>1195</v>
+      </c>
+      <c r="E173" s="8" t="n">
+        <v>1259</v>
+      </c>
+      <c r="F173" s="9" t="n">
+        <v>0.9735</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B174" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="C174" s="11" t="n">
+        <v>796</v>
+      </c>
+      <c r="D174" s="11" t="n">
+        <v>1021</v>
+      </c>
+      <c r="E174" s="11" t="n">
+        <v>1076</v>
+      </c>
+      <c r="F174" s="12" t="n">
+        <v>0.9681</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B175" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C175" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D175" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E175" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="F175" s="9" t="n">
+        <v>0.8314</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B176" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="C176" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D176" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E176" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F176" s="12" t="n">
+        <v>0.0338</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B177" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C177" s="8" t="n">
+        <v>1199</v>
+      </c>
+      <c r="D177" s="8" t="n">
+        <v>1843</v>
+      </c>
+      <c r="E177" s="8" t="n">
+        <v>2302</v>
+      </c>
+      <c r="F177" s="9" t="n">
+        <v>0.9897</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B178" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C178" s="11" t="n">
+        <v>1182</v>
+      </c>
+      <c r="D178" s="11" t="n">
+        <v>1814</v>
+      </c>
+      <c r="E178" s="11" t="n">
+        <v>2272</v>
+      </c>
+      <c r="F178" s="12" t="n">
+        <v>0.9911</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B179" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C179" s="8" t="n">
+        <v>796</v>
+      </c>
+      <c r="D179" s="8" t="n">
+        <v>1021</v>
+      </c>
+      <c r="E179" s="8" t="n">
+        <v>1075</v>
+      </c>
+      <c r="F179" s="9" t="n">
+        <v>0.9681</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B180" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="C180" s="11" t="n">
+        <v>674</v>
+      </c>
+      <c r="D180" s="11" t="n">
+        <v>806</v>
+      </c>
+      <c r="E180" s="11" t="n">
+        <v>855</v>
+      </c>
+      <c r="F180" s="12" t="n">
+        <v>0.9594</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B181" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C181" s="8" t="n">
+        <v>2446</v>
+      </c>
+      <c r="D181" s="8" t="n">
+        <v>2536</v>
+      </c>
+      <c r="E181" s="8" t="n">
+        <v>2566</v>
+      </c>
+      <c r="F181" s="9" t="n">
+        <v>0.9972</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B182" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C182" s="11" t="n">
+        <v>1931</v>
+      </c>
+      <c r="D182" s="11" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E182" s="11" t="n">
+        <v>2046</v>
+      </c>
+      <c r="F182" s="12" t="n">
+        <v>0.9975</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B183" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C183" s="8" t="n">
+        <v>1651</v>
+      </c>
+      <c r="D183" s="8" t="n">
+        <v>1741</v>
+      </c>
+      <c r="E183" s="8" t="n">
+        <v>1771</v>
+      </c>
+      <c r="F183" s="9" t="n">
+        <v>0.9974</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B184" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C184" s="11" t="n">
+        <v>991</v>
+      </c>
+      <c r="D184" s="11" t="n">
+        <v>1096</v>
+      </c>
+      <c r="E184" s="11" t="n">
+        <v>1136</v>
+      </c>
+      <c r="F184" s="12" t="n">
+        <v>0.9937</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C185" s="8" t="n">
+        <v>1061</v>
+      </c>
+      <c r="D185" s="8" t="n">
+        <v>1181</v>
+      </c>
+      <c r="E185" s="8" t="n">
+        <v>1211</v>
+      </c>
+      <c r="F185" s="9" t="n">
+        <v>0.996</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B186" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C186" s="11" t="n">
+        <v>1831</v>
+      </c>
+      <c r="D186" s="11" t="n">
+        <v>1916</v>
+      </c>
+      <c r="E186" s="11" t="n">
+        <v>1941</v>
+      </c>
+      <c r="F186" s="12" t="n">
+        <v>0.9971</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B187" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C187" s="8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="D187" s="8" t="n">
+        <v>1551</v>
+      </c>
+      <c r="E187" s="8" t="n">
+        <v>1591</v>
+      </c>
+      <c r="F187" s="9" t="n">
+        <v>0.9971</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B188" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="C188" s="11" t="n">
+        <v>1961</v>
+      </c>
+      <c r="D188" s="11" t="n">
+        <v>2046</v>
+      </c>
+      <c r="E188" s="11" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F188" s="12" t="n">
+        <v>0.9976</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B189" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C189" s="8" t="n">
+        <v>2061</v>
+      </c>
+      <c r="D189" s="8" t="n">
+        <v>2141</v>
+      </c>
+      <c r="E189" s="8" t="n">
+        <v>2176</v>
+      </c>
+      <c r="F189" s="9" t="n">
+        <v>0.9979</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B190" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="C190" s="11" t="n">
+        <v>1286</v>
+      </c>
+      <c r="D190" s="11" t="n">
+        <v>1351</v>
+      </c>
+      <c r="E190" s="11" t="n">
+        <v>1391</v>
+      </c>
+      <c r="F190" s="12" t="n">
+        <v>0.9906</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C191" s="8" t="n">
+        <v>1101</v>
+      </c>
+      <c r="D191" s="8" t="n">
+        <v>1191</v>
+      </c>
+      <c r="E191" s="8" t="n">
+        <v>1241</v>
+      </c>
+      <c r="F191" s="9" t="n">
+        <v>0.9903</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B192" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="C192" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D192" s="11" t="n">
+        <v>96</v>
+      </c>
+      <c r="E192" s="11" t="n">
+        <v>201</v>
+      </c>
+      <c r="F192" s="12" t="n">
+        <v>0.1687</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B193" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="C193" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="D193" s="8" t="n">
+        <v>216</v>
+      </c>
+      <c r="E193" s="8" t="n">
+        <v>331</v>
+      </c>
+      <c r="F193" s="9" t="n">
+        <v>0.0591</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B194" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="C194" s="11" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D194" s="11" t="n">
+        <v>2086</v>
+      </c>
+      <c r="E194" s="11" t="n">
+        <v>2116</v>
+      </c>
+      <c r="F194" s="12" t="n">
+        <v>0.9975</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B195" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C195" s="8" t="n">
+        <v>1966</v>
+      </c>
+      <c r="D195" s="8" t="n">
+        <v>2050</v>
+      </c>
+      <c r="E195" s="8" t="n">
+        <v>2076</v>
+      </c>
+      <c r="F195" s="9" t="n">
+        <v>0.997</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B196" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="C196" s="11" t="n">
+        <v>706</v>
+      </c>
+      <c r="D196" s="11" t="n">
+        <v>936</v>
+      </c>
+      <c r="E196" s="11" t="n">
+        <v>1026</v>
+      </c>
+      <c r="F196" s="12" t="n">
+        <v>0.9666</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B197" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C197" s="8" t="n">
+        <v>411</v>
+      </c>
+      <c r="D197" s="8" t="n">
+        <v>746</v>
+      </c>
+      <c r="E197" s="8" t="n">
+        <v>851</v>
+      </c>
+      <c r="F197" s="9" t="n">
+        <v>0.9535</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B198" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="C198" s="11" t="n">
+        <v>1626</v>
+      </c>
+      <c r="D198" s="11" t="n">
+        <v>1821</v>
+      </c>
+      <c r="E198" s="11" t="n">
+        <v>1881</v>
+      </c>
+      <c r="F198" s="12" t="n">
+        <v>0.9956</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B199" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="C199" s="8" t="n">
+        <v>1281</v>
+      </c>
+      <c r="D199" s="8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="E199" s="8" t="n">
+        <v>1536</v>
+      </c>
+      <c r="F199" s="9" t="n">
+        <v>0.9944</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B200" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C200" s="11" t="n">
+        <v>1051</v>
+      </c>
+      <c r="D200" s="11" t="n">
+        <v>1276</v>
+      </c>
+      <c r="E200" s="11" t="n">
+        <v>1316</v>
+      </c>
+      <c r="F200" s="12" t="n">
+        <v>0.9946</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B201" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C201" s="8" t="n">
+        <v>796</v>
+      </c>
+      <c r="D201" s="8" t="n">
+        <v>911</v>
+      </c>
+      <c r="E201" s="8" t="n">
+        <v>986</v>
+      </c>
+      <c r="F201" s="9" t="n">
+        <v>0.972</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B202" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="C202" s="11" t="n">
+        <v>661</v>
+      </c>
+      <c r="D202" s="11" t="n">
+        <v>901</v>
+      </c>
+      <c r="E202" s="11" t="n">
+        <v>936</v>
+      </c>
+      <c r="F202" s="12" t="n">
+        <v>0.9932</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B203" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C203" s="8" t="n">
+        <v>1226</v>
+      </c>
+      <c r="D203" s="8" t="n">
+        <v>1386</v>
+      </c>
+      <c r="E203" s="8" t="n">
+        <v>1436</v>
+      </c>
+      <c r="F203" s="9" t="n">
+        <v>0.9958</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B204" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="C204" s="11" t="n">
+        <v>911</v>
+      </c>
+      <c r="D204" s="11" t="n">
+        <v>1111</v>
+      </c>
+      <c r="E204" s="11" t="n">
+        <v>1171</v>
+      </c>
+      <c r="F204" s="12" t="n">
+        <v>0.9935</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B205" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="C205" s="8" t="n">
+        <v>1336</v>
+      </c>
+      <c r="D205" s="8" t="n">
+        <v>1491</v>
+      </c>
+      <c r="E205" s="8" t="n">
+        <v>1551</v>
+      </c>
+      <c r="F205" s="9" t="n">
+        <v>0.9952</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B206" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="C206" s="11" t="n">
+        <v>1361</v>
+      </c>
+      <c r="D206" s="11" t="n">
+        <v>1566</v>
+      </c>
+      <c r="E206" s="11" t="n">
+        <v>1616</v>
+      </c>
+      <c r="F206" s="12" t="n">
+        <v>0.9939</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B207" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="C207" s="8" t="n">
+        <v>946</v>
+      </c>
+      <c r="D207" s="8" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E207" s="8" t="n">
+        <v>1186</v>
+      </c>
+      <c r="F207" s="9" t="n">
+        <v>0.9802</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B208" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="C208" s="11" t="n">
+        <v>841</v>
+      </c>
+      <c r="D208" s="11" t="n">
+        <v>981</v>
+      </c>
+      <c r="E208" s="11" t="n">
+        <v>1061</v>
+      </c>
+      <c r="F208" s="12" t="n">
+        <v>0.9606</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B209" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="C209" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D209" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="E209" s="8" t="n">
+        <v>181</v>
+      </c>
+      <c r="F209" s="9" t="n">
+        <v>0.1491</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B210" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C210" s="11" t="n">
+        <v>199</v>
+      </c>
+      <c r="D210" s="11" t="n">
+        <v>281</v>
+      </c>
+      <c r="E210" s="11" t="n">
+        <v>386</v>
+      </c>
+      <c r="F210" s="12" t="n">
+        <v>0.0405</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B211" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="C211" s="8" t="n">
+        <v>1316</v>
+      </c>
+      <c r="D211" s="8" t="n">
+        <v>1521</v>
+      </c>
+      <c r="E211" s="8" t="n">
+        <v>1561</v>
+      </c>
+      <c r="F211" s="9" t="n">
+        <v>0.9955</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B212" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="C212" s="11" t="n">
+        <v>1286</v>
+      </c>
+      <c r="D212" s="11" t="n">
+        <v>1496</v>
+      </c>
+      <c r="E212" s="11" t="n">
+        <v>1551</v>
+      </c>
+      <c r="F212" s="12" t="n">
+        <v>0.9957</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B213" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C213" s="8" t="n">
+        <v>661</v>
+      </c>
+      <c r="D213" s="8" t="n">
+        <v>921</v>
+      </c>
+      <c r="E213" s="8" t="n">
+        <v>996</v>
+      </c>
+      <c r="F213" s="9" t="n">
+        <v>0.9606</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B214" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="C214" s="11" t="n">
+        <v>346</v>
+      </c>
+      <c r="D214" s="11" t="n">
+        <v>746</v>
+      </c>
+      <c r="E214" s="11" t="n">
+        <v>846</v>
+      </c>
+      <c r="F214" s="12" t="n">
+        <v>0.9488</v>
       </c>
     </row>
   </sheetData>
@@ -5622,23 +8483,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>117</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>118</v>
+        <v>245</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>120</v>
+        <v>247</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
@@ -5653,21 +8514,21 @@
         <v>21</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>121</v>
+        <v>248</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>122</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>123</v>
+        <v>250</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>34</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>124</v>
+        <v>251</v>
       </c>
       <c r="D5" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B5,'All runs'!$B:$B,0))</f>
@@ -5687,92 +8548,92 @@
       </c>
       <c r="H5" s="16" t="n">
         <f aca="false">IF(D5=0,"",$D$15/D5-1)</f>
-        <v>0.808387563268257</v>
+        <v>0.768618944323934</v>
       </c>
       <c r="I5" s="17" t="n">
         <f aca="false">($G$15-G5)*100</f>
-        <v>0.244000000000011</v>
+        <v>0.321600000000011</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>125</v>
+        <v>252</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>31</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>124</v>
+        <v>251</v>
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B6,'All runs'!$B:$B,0))</f>
-        <v>634</v>
+        <v>658</v>
       </c>
       <c r="E6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B6,'All runs'!$B:$B,0))</f>
-        <v>1216</v>
+        <v>1197</v>
       </c>
       <c r="F6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B6,'All runs'!$B:$B,0))</f>
-        <v>1883</v>
+        <v>1875</v>
       </c>
       <c r="G6" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B6,'All runs'!$B:$B,0))</f>
-        <v>0.996845</v>
+        <v>0.996512</v>
       </c>
       <c r="H6" s="21" t="n">
         <f aca="false">IF(D6=0,"",$D$15/D6-1)</f>
-        <v>2.94479495268139</v>
+        <v>2.71732522796353</v>
       </c>
       <c r="I6" s="22" t="n">
         <f aca="false">($G$15-G6)*100</f>
-        <v>-0.0452999999999926</v>
+        <v>0.0656000000000101</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>126</v>
+        <v>253</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>127</v>
+        <v>254</v>
       </c>
       <c r="D7" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B7,'All runs'!$B:$B,0))</f>
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="E7" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B7,'All runs'!$B:$B,0))</f>
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="F7" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B7,'All runs'!$B:$B,0))</f>
-        <v>1960</v>
+        <v>1969</v>
       </c>
       <c r="G7" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B7,'All runs'!$B:$B,0))</f>
-        <v>0.997395</v>
+        <v>0.996732</v>
       </c>
       <c r="H7" s="16" t="n">
         <f aca="false">IF(D7=0,"",$D$15/D7-1)</f>
-        <v>2.36608344549125</v>
+        <v>2.31436314363144</v>
       </c>
       <c r="I7" s="17" t="n">
         <f aca="false">($G$15-G7)*100</f>
-        <v>-0.100299999999998</v>
+        <v>0.0436000000000103</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>128</v>
+        <v>255</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>35</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>124</v>
+        <v>251</v>
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B8,'All runs'!$B:$B,0))</f>
@@ -5792,22 +8653,22 @@
       </c>
       <c r="H8" s="21" t="n">
         <f aca="false">IF(D8=0,"",$D$15/D8-1)</f>
-        <v>0.888972809667674</v>
+        <v>0.847432024169184</v>
       </c>
       <c r="I8" s="22" t="n">
         <f aca="false">($G$15-G8)*100</f>
-        <v>0.220600000000004</v>
+        <v>0.298200000000004</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>129</v>
+        <v>256</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>130</v>
+        <v>257</v>
       </c>
       <c r="D9" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B9,'All runs'!$B:$B,0))</f>
@@ -5827,22 +8688,22 @@
       </c>
       <c r="H9" s="16" t="n">
         <f aca="false">IF(D9=0,"",$D$15/D9-1)</f>
-        <v>2.86553323029366</v>
+        <v>2.78052550231839</v>
       </c>
       <c r="I9" s="17" t="n">
         <f aca="false">($G$15-G9)*100</f>
-        <v>1.0548</v>
+        <v>1.1324</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>131</v>
+        <v>258</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>40</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>132</v>
+        <v>259</v>
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B10,'All runs'!$B:$B,0))</f>
@@ -5862,22 +8723,22 @@
       </c>
       <c r="H10" s="21" t="n">
         <f aca="false">IF(D10=0,"",$D$15/D10-1)</f>
-        <v>0.689864864864865</v>
+        <v>0.652702702702703</v>
       </c>
       <c r="I10" s="22" t="n">
         <f aca="false">($G$15-G10)*100</f>
-        <v>0.432900000000003</v>
+        <v>0.510500000000003</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>133</v>
+        <v>260</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>130</v>
+        <v>257</v>
       </c>
       <c r="D11" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B11,'All runs'!$B:$B,0))</f>
@@ -5897,22 +8758,22 @@
       </c>
       <c r="H11" s="16" t="n">
         <f aca="false">IF(D11=0,"",$D$15/D11-1)</f>
-        <v>0.807080924855491</v>
+        <v>0.767341040462428</v>
       </c>
       <c r="I11" s="17" t="n">
         <f aca="false">($G$15-G11)*100</f>
-        <v>0.342400000000009</v>
+        <v>0.420000000000009</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>39</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>132</v>
+        <v>259</v>
       </c>
       <c r="D12" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B12,'All runs'!$B:$B,0))</f>
@@ -5932,108 +8793,108 @@
       </c>
       <c r="H12" s="21" t="n">
         <f aca="false">IF(D12=0,"",$D$15/D12-1)</f>
-        <v>0.697895451459606</v>
+        <v>0.660556687033266</v>
       </c>
       <c r="I12" s="22" t="n">
         <f aca="false">($G$15-G12)*100</f>
-        <v>0.277500000000008</v>
+        <v>0.355100000000008</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>135</v>
+        <v>262</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>136</v>
+        <v>263</v>
       </c>
       <c r="D13" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B13,'All runs'!$B:$B,0))</f>
-        <v>1311</v>
+        <v>1277</v>
       </c>
       <c r="E13" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B13,'All runs'!$B:$B,0))</f>
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="F13" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B13,'All runs'!$B:$B,0))</f>
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="G13" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B13,'All runs'!$B:$B,0))</f>
-        <v>0.9974</v>
+        <v>0.994936</v>
       </c>
       <c r="H13" s="16" t="n">
         <f aca="false">IF(D13=0,"",$D$15/D13-1)</f>
-        <v>0.907704042715484</v>
+        <v>0.915426781519186</v>
       </c>
       <c r="I13" s="17" t="n">
         <f aca="false">($G$15-G13)*100</f>
-        <v>-0.10079999999999</v>
+        <v>0.223200000000001</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="B14" s="18" t="s">
         <v>38</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>138</v>
+        <v>265</v>
       </c>
       <c r="D14" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B14,'All runs'!$B:$B,0))</f>
-        <v>1368</v>
+        <v>1335</v>
       </c>
       <c r="E14" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B14,'All runs'!$B:$B,0))</f>
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F14" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B14,'All runs'!$B:$B,0))</f>
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="G14" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B14,'All runs'!$B:$B,0))</f>
-        <v>0.995064</v>
+        <v>0.996207</v>
       </c>
       <c r="H14" s="21" t="n">
         <f aca="false">IF(D14=0,"",$D$15/D14-1)</f>
-        <v>0.828216374269006</v>
+        <v>0.832209737827715</v>
       </c>
       <c r="I14" s="22" t="n">
         <f aca="false">($G$15-G14)*100</f>
-        <v>0.132800000000011</v>
+        <v>0.0961000000000101</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>139</v>
+        <v>266</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>140</v>
+        <v>267</v>
       </c>
       <c r="D15" s="24" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B15,'All runs'!$B:$B,0))</f>
-        <v>2501</v>
+        <v>2446</v>
       </c>
       <c r="E15" s="24" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B15,'All runs'!$B:$B,0))</f>
-        <v>2589</v>
+        <v>2536</v>
       </c>
       <c r="F15" s="24" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B15,'All runs'!$B:$B,0))</f>
-        <v>2631</v>
+        <v>2566</v>
       </c>
       <c r="G15" s="25" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B15,'All runs'!$B:$B,0))</f>
-        <v>0.996392</v>
+        <v>0.997168</v>
       </c>
       <c r="H15" s="26" t="n">
         <f aca="false">IF(D15=0,"",$D$15/D15-1)</f>
@@ -6072,67 +8933,67 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>142</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>118</v>
+        <v>245</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>143</v>
+        <v>270</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>144</v>
+        <v>271</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>145</v>
+        <v>272</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>146</v>
+        <v>273</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>147</v>
+        <v>274</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>148</v>
+        <v>275</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>149</v>
+        <v>276</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>150</v>
+        <v>277</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>151</v>
+        <v>278</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>152</v>
+        <v>279</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>153</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>123</v>
+        <v>250</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>154</v>
+        <v>281</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>154</v>
+        <v>281</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>1312</v>
@@ -6166,24 +9027,24 @@
         <v>0.0114329268292683</v>
       </c>
       <c r="M5" s="30" t="s">
-        <v>155</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>125</v>
+        <v>252</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>154</v>
+        <v>281</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>154</v>
+        <v>281</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>154</v>
+        <v>281</v>
       </c>
       <c r="F6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B6,'All runs'!$B:$B,0))</f>
@@ -6214,12 +9075,12 @@
         <v/>
       </c>
       <c r="M6" s="33" t="s">
-        <v>156</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>128</v>
+        <v>255</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>27</v>
@@ -6262,24 +9123,24 @@
         <v>0.00273722627737226</v>
       </c>
       <c r="M7" s="30" t="s">
-        <v>157</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>129</v>
+        <v>256</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>154</v>
+        <v>281</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>154</v>
+        <v>281</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>154</v>
+        <v>281</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B8,'All runs'!$B:$B,0))</f>
@@ -6310,21 +9171,21 @@
         <v/>
       </c>
       <c r="M8" s="33" t="s">
-        <v>158</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>133</v>
+        <v>260</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>154</v>
+        <v>281</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>154</v>
+        <v>281</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>4312</v>
@@ -6358,12 +9219,12 @@
         <v>0.720083487940631</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>159</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>135</v>
+        <v>262</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>23</v>
@@ -6406,12 +9267,12 @@
         <v>0.719545454545455</v>
       </c>
       <c r="M10" s="33" t="s">
-        <v>160</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="34" t="s">
-        <v>161</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -6443,23 +9304,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>162</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>163</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>118</v>
+        <v>245</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>164</v>
+        <v>291</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
@@ -6474,15 +9335,15 @@
         <v>21</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>165</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>129</v>
+        <v>256</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>166</v>
+        <v>293</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>28</v>
@@ -6504,15 +9365,15 @@
         <v>0.996585</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>167</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>129</v>
+        <v>256</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>168</v>
+        <v>295</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>36</v>
@@ -6534,15 +9395,15 @@
         <v>0.985844</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>169</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>129</v>
+        <v>256</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>170</v>
+        <v>297</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>40</v>
@@ -6564,15 +9425,15 @@
         <v>0.992063</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>171</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>133</v>
+        <v>260</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>166</v>
+        <v>293</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>25</v>
@@ -6594,15 +9455,15 @@
         <v>0.950353</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>172</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>133</v>
+        <v>260</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>168</v>
+        <v>295</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>33</v>
@@ -6624,15 +9485,15 @@
         <v>0.992968</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>169</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>133</v>
+        <v>260</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>170</v>
+        <v>297</v>
       </c>
       <c r="C10" s="23" t="s">
         <v>39</v>
@@ -6654,15 +9515,15 @@
         <v>0.993617</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>173</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>135</v>
+        <v>262</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>166</v>
+        <v>293</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>23</v>
@@ -6684,91 +9545,91 @@
         <v>0.997831</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>174</v>
+        <v>301</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>135</v>
+        <v>262</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>168</v>
+        <v>295</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C12,'All runs'!$B:$B,0))</f>
-        <v>1311</v>
+        <v>1277</v>
       </c>
       <c r="E12" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C12,'All runs'!$B:$B,0))</f>
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="F12" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C12,'All runs'!$B:$B,0))</f>
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="G12" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C12,'All runs'!$B:$B,0))</f>
-        <v>0.9974</v>
+        <v>0.994936</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>175</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>135</v>
+        <v>262</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>170</v>
+        <v>297</v>
       </c>
       <c r="C13" s="23" t="s">
         <v>38</v>
       </c>
       <c r="D13" s="24" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C13,'All runs'!$B:$B,0))</f>
-        <v>1368</v>
+        <v>1335</v>
       </c>
       <c r="E13" s="24" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C13,'All runs'!$B:$B,0))</f>
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F13" s="24" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C13,'All runs'!$B:$B,0))</f>
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="G13" s="25" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C13,'All runs'!$B:$B,0))</f>
-        <v>0.995064</v>
+        <v>0.996207</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>176</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>118</v>
+        <v>245</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6" t="s">
-        <v>177</v>
+        <v>304</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>178</v>
+        <v>305</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>179</v>
+        <v>306</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>180</v>
+        <v>307</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>129</v>
+        <v>256</v>
       </c>
       <c r="D16" s="21" t="n">
         <f aca="false">D7/D6-1</f>
@@ -6789,7 +9650,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>133</v>
+        <v>260</v>
       </c>
       <c r="D17" s="16" t="n">
         <f aca="false">D10/D9-1</f>
@@ -6810,23 +9671,23 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>135</v>
+        <v>262</v>
       </c>
       <c r="D18" s="21" t="n">
         <f aca="false">D13/D12-1</f>
-        <v>0.0434782608695652</v>
+        <v>0.0454189506656226</v>
       </c>
       <c r="E18" s="21" t="n">
         <f aca="false">E13/E12-1</f>
-        <v>0.0021707670043416</v>
+        <v>0</v>
       </c>
       <c r="F18" s="21" t="n">
         <f aca="false">F13/F12-1</f>
-        <v>0.14368932038835</v>
+        <v>0.14452365521711</v>
       </c>
       <c r="G18" s="35" t="n">
         <f aca="false">(G13-G12)*100</f>
-        <v>-0.2336</v>
+        <v>0.127099999999991</v>
       </c>
     </row>
   </sheetData>
@@ -6858,23 +9719,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>182</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>183</v>
+        <v>310</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>184</v>
+        <v>311</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
@@ -6889,34 +9750,34 @@
         <v>21</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>185</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>186</v>
+        <v>313</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>42</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>187</v>
+        <v>314</v>
       </c>
       <c r="D5" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B5,'All runs'!$B:$B,0))</f>
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E5" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B5,'All runs'!$B:$B,0))</f>
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F5" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B5,'All runs'!$B:$B,0))</f>
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="G5" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B5,'All runs'!$B:$B,0))</f>
-        <v>0.997502</v>
+        <v>0.997623</v>
       </c>
       <c r="H5" s="16" t="n">
         <f aca="false">D5/$D$5-1</f>
@@ -6925,17 +9786,17 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>188</v>
+        <v>315</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>43</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>189</v>
+        <v>316</v>
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B6,'All runs'!$B:$B,0))</f>
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B6,'All runs'!$B:$B,0))</f>
@@ -6943,26 +9804,26 @@
       </c>
       <c r="F6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B6,'All runs'!$B:$B,0))</f>
-        <v>1276</v>
+        <v>1285</v>
       </c>
       <c r="G6" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B6,'All runs'!$B:$B,0))</f>
-        <v>0.996435</v>
+        <v>0.997665</v>
       </c>
       <c r="H6" s="21" t="n">
         <f aca="false">D6/$D$5-1</f>
-        <v>0.0496894409937889</v>
+        <v>0.04375</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>190</v>
+        <v>317</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>44</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>191</v>
+        <v>318</v>
       </c>
       <c r="D7" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B7,'All runs'!$B:$B,0))</f>
@@ -6970,92 +9831,92 @@
       </c>
       <c r="E7" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B7,'All runs'!$B:$B,0))</f>
-        <v>2011</v>
+        <v>2001</v>
       </c>
       <c r="F7" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B7,'All runs'!$B:$B,0))</f>
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="G7" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B7,'All runs'!$B:$B,0))</f>
-        <v>0.982072</v>
+        <v>0.983494</v>
       </c>
       <c r="H7" s="16" t="n">
         <f aca="false">D7/$D$5-1</f>
-        <v>4.10869565217391</v>
+        <v>4.140625</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>192</v>
+        <v>319</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>45</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>193</v>
+        <v>320</v>
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B8,'All runs'!$B:$B,0))</f>
-        <v>1438</v>
+        <v>1513</v>
       </c>
       <c r="E8" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B8,'All runs'!$B:$B,0))</f>
-        <v>2206</v>
+        <v>2158</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B8,'All runs'!$B:$B,0))</f>
-        <v>2476</v>
+        <v>2416</v>
       </c>
       <c r="G8" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B8,'All runs'!$B:$B,0))</f>
-        <v>0.959074</v>
+        <v>0.970722</v>
       </c>
       <c r="H8" s="21" t="n">
         <f aca="false">D8/$D$5-1</f>
-        <v>3.46583850931677</v>
+        <v>3.728125</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>194</v>
+        <v>321</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>46</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>195</v>
+        <v>322</v>
       </c>
       <c r="D9" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B9,'All runs'!$B:$B,0))</f>
-        <v>1438</v>
+        <v>1513</v>
       </c>
       <c r="E9" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B9,'All runs'!$B:$B,0))</f>
-        <v>2131</v>
+        <v>2116</v>
       </c>
       <c r="F9" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B9,'All runs'!$B:$B,0))</f>
-        <v>2401</v>
+        <v>2356</v>
       </c>
       <c r="G9" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B9,'All runs'!$B:$B,0))</f>
-        <v>0.984413</v>
+        <v>0.984351</v>
       </c>
       <c r="H9" s="16" t="n">
         <f aca="false">D9/$D$5-1</f>
-        <v>3.46583850931677</v>
+        <v>3.728125</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>196</v>
+        <v>323</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>197</v>
+        <v>324</v>
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B10,'All runs'!$B:$B,0))</f>
@@ -7063,30 +9924,30 @@
       </c>
       <c r="E10" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B10,'All runs'!$B:$B,0))</f>
-        <v>2006</v>
+        <v>1996</v>
       </c>
       <c r="F10" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B10,'All runs'!$B:$B,0))</f>
-        <v>2101</v>
+        <v>2081</v>
       </c>
       <c r="G10" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B10,'All runs'!$B:$B,0))</f>
-        <v>0.98822</v>
+        <v>0.989505</v>
       </c>
       <c r="H10" s="21" t="n">
         <f aca="false">D10/$D$5-1</f>
-        <v>4.10869565217391</v>
+        <v>4.140625</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>198</v>
+        <v>325</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>199</v>
+        <v>326</v>
       </c>
       <c r="D11" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B11,'All runs'!$B:$B,0))</f>
@@ -7094,30 +9955,30 @@
       </c>
       <c r="E11" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B11,'All runs'!$B:$B,0))</f>
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="F11" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B11,'All runs'!$B:$B,0))</f>
-        <v>2251</v>
+        <v>2259</v>
       </c>
       <c r="G11" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B11,'All runs'!$B:$B,0))</f>
-        <v>0.986576</v>
+        <v>0.987008</v>
       </c>
       <c r="H11" s="16" t="n">
         <f aca="false">D11/$D$5-1</f>
-        <v>3.78260869565217</v>
+        <v>3.8125</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>200</v>
+        <v>327</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>201</v>
+        <v>328</v>
       </c>
       <c r="D12" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B12,'All runs'!$B:$B,0))</f>
@@ -7125,329 +9986,329 @@
       </c>
       <c r="E12" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B12,'All runs'!$B:$B,0))</f>
-        <v>2011</v>
+        <v>1996</v>
       </c>
       <c r="F12" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B12,'All runs'!$B:$B,0))</f>
-        <v>2106</v>
+        <v>2116</v>
       </c>
       <c r="G12" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B12,'All runs'!$B:$B,0))</f>
-        <v>0.985626</v>
+        <v>0.986194</v>
       </c>
       <c r="H12" s="21" t="n">
         <f aca="false">D12/$D$5-1</f>
-        <v>4.10869565217391</v>
+        <v>4.140625</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>202</v>
+        <v>329</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>50</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>203</v>
+        <v>330</v>
       </c>
       <c r="D13" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B13,'All runs'!$B:$B,0))</f>
-        <v>1415</v>
+        <v>1521</v>
       </c>
       <c r="E13" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B13,'All runs'!$B:$B,0))</f>
-        <v>1916</v>
+        <v>1913</v>
       </c>
       <c r="F13" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B13,'All runs'!$B:$B,0))</f>
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="G13" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B13,'All runs'!$B:$B,0))</f>
-        <v>0.987496</v>
+        <v>0.985123</v>
       </c>
       <c r="H13" s="16" t="n">
         <f aca="false">D13/$D$5-1</f>
-        <v>3.3944099378882</v>
+        <v>3.753125</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>204</v>
+        <v>331</v>
       </c>
       <c r="B14" s="18" t="s">
         <v>51</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>205</v>
+        <v>332</v>
       </c>
       <c r="D14" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B14,'All runs'!$B:$B,0))</f>
-        <v>1409</v>
+        <v>1481</v>
       </c>
       <c r="E14" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B14,'All runs'!$B:$B,0))</f>
-        <v>1824</v>
+        <v>1816</v>
       </c>
       <c r="F14" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B14,'All runs'!$B:$B,0))</f>
-        <v>1936</v>
+        <v>1961</v>
       </c>
       <c r="G14" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B14,'All runs'!$B:$B,0))</f>
-        <v>0.977653</v>
+        <v>0.979452</v>
       </c>
       <c r="H14" s="21" t="n">
         <f aca="false">D14/$D$5-1</f>
-        <v>3.37577639751553</v>
+        <v>3.628125</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>206</v>
+        <v>333</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>207</v>
+        <v>334</v>
       </c>
       <c r="D15" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B15,'All runs'!$B:$B,0))</f>
-        <v>1415</v>
+        <v>1521</v>
       </c>
       <c r="E15" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B15,'All runs'!$B:$B,0))</f>
-        <v>1911</v>
+        <v>1906</v>
       </c>
       <c r="F15" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B15,'All runs'!$B:$B,0))</f>
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="G15" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B15,'All runs'!$B:$B,0))</f>
-        <v>0.991026</v>
+        <v>0.989135</v>
       </c>
       <c r="H15" s="16" t="n">
         <f aca="false">D15/$D$5-1</f>
-        <v>3.3944099378882</v>
+        <v>3.753125</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>208</v>
+        <v>335</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>209</v>
+        <v>336</v>
       </c>
       <c r="D16" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B16,'All runs'!$B:$B,0))</f>
-        <v>1409</v>
+        <v>1481</v>
       </c>
       <c r="E16" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B16,'All runs'!$B:$B,0))</f>
-        <v>1801</v>
+        <v>1796</v>
       </c>
       <c r="F16" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B16,'All runs'!$B:$B,0))</f>
-        <v>1906</v>
+        <v>1911</v>
       </c>
       <c r="G16" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B16,'All runs'!$B:$B,0))</f>
-        <v>0.989727</v>
+        <v>0.98804</v>
       </c>
       <c r="H16" s="21" t="n">
         <f aca="false">D16/$D$5-1</f>
-        <v>3.37577639751553</v>
+        <v>3.628125</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>210</v>
+        <v>337</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>211</v>
+        <v>338</v>
       </c>
       <c r="D17" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B17,'All runs'!$B:$B,0))</f>
-        <v>1471</v>
+        <v>1466</v>
       </c>
       <c r="E17" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B17,'All runs'!$B:$B,0))</f>
-        <v>1916</v>
+        <v>1896</v>
       </c>
       <c r="F17" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B17,'All runs'!$B:$B,0))</f>
-        <v>2006</v>
+        <v>2011</v>
       </c>
       <c r="G17" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B17,'All runs'!$B:$B,0))</f>
-        <v>0.990728</v>
+        <v>0.990826</v>
       </c>
       <c r="H17" s="16" t="n">
         <f aca="false">D17/$D$5-1</f>
-        <v>3.56832298136646</v>
+        <v>3.58125</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>212</v>
+        <v>339</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>213</v>
+        <v>340</v>
       </c>
       <c r="D18" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B18,'All runs'!$B:$B,0))</f>
-        <v>1421</v>
+        <v>1431</v>
       </c>
       <c r="E18" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B18,'All runs'!$B:$B,0))</f>
-        <v>1991</v>
+        <v>1996</v>
       </c>
       <c r="F18" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B18,'All runs'!$B:$B,0))</f>
-        <v>2193</v>
+        <v>2181</v>
       </c>
       <c r="G18" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B18,'All runs'!$B:$B,0))</f>
-        <v>0.982688</v>
+        <v>0.984303</v>
       </c>
       <c r="H18" s="21" t="n">
         <f aca="false">D18/$D$5-1</f>
-        <v>3.41304347826087</v>
+        <v>3.471875</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>214</v>
+        <v>341</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>56</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>215</v>
+        <v>342</v>
       </c>
       <c r="D19" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B19,'All runs'!$B:$B,0))</f>
-        <v>2501</v>
+        <v>2446</v>
       </c>
       <c r="E19" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B19,'All runs'!$B:$B,0))</f>
-        <v>2589</v>
+        <v>2536</v>
       </c>
       <c r="F19" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B19,'All runs'!$B:$B,0))</f>
-        <v>2636</v>
+        <v>2566</v>
       </c>
       <c r="G19" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B19,'All runs'!$B:$B,0))</f>
-        <v>0.996527</v>
+        <v>0.997208</v>
       </c>
       <c r="H19" s="16" t="n">
         <f aca="false">D19/$D$5-1</f>
-        <v>6.76708074534162</v>
+        <v>6.64375</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>216</v>
+        <v>343</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>209</v>
+        <v>336</v>
       </c>
       <c r="D20" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B20,'All runs'!$B:$B,0))</f>
-        <v>1441</v>
+        <v>1406</v>
       </c>
       <c r="E20" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B20,'All runs'!$B:$B,0))</f>
-        <v>1596</v>
+        <v>1551</v>
       </c>
       <c r="F20" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B20,'All runs'!$B:$B,0))</f>
-        <v>1646</v>
+        <v>1606</v>
       </c>
       <c r="G20" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B20,'All runs'!$B:$B,0))</f>
-        <v>0.994649</v>
+        <v>0.993787</v>
       </c>
       <c r="H20" s="21" t="n">
         <f aca="false">D20/$D$5-1</f>
-        <v>3.47515527950311</v>
+        <v>3.39375</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>217</v>
+        <v>344</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>218</v>
+        <v>345</v>
       </c>
       <c r="D21" s="24" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B21,'All runs'!$B:$B,0))</f>
-        <v>2501</v>
+        <v>2446</v>
       </c>
       <c r="E21" s="24" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B21,'All runs'!$B:$B,0))</f>
-        <v>2589</v>
+        <v>2536</v>
       </c>
       <c r="F21" s="24" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B21,'All runs'!$B:$B,0))</f>
-        <v>2631</v>
+        <v>2566</v>
       </c>
       <c r="G21" s="25" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B21,'All runs'!$B:$B,0))</f>
-        <v>0.996392</v>
+        <v>0.997168</v>
       </c>
       <c r="H21" s="26" t="n">
         <f aca="false">D21/$D$5-1</f>
-        <v>6.76708074534162</v>
+        <v>6.64375</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="s">
-        <v>219</v>
+        <v>346</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>209</v>
+        <v>336</v>
       </c>
       <c r="D22" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B22,'All runs'!$B:$B,0))</f>
-        <v>1671</v>
+        <v>1626</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($B22,'All runs'!$B:$B,0))</f>
-        <v>1851</v>
+        <v>1821</v>
       </c>
       <c r="F22" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($B22,'All runs'!$B:$B,0))</f>
-        <v>1906</v>
+        <v>1881</v>
       </c>
       <c r="G22" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($B22,'All runs'!$B:$B,0))</f>
-        <v>0.993581</v>
+        <v>0.995637</v>
       </c>
       <c r="H22" s="21" t="n">
         <f aca="false">D22/$D$5-1</f>
-        <v>4.18944099378882</v>
+        <v>4.08125</v>
       </c>
     </row>
   </sheetData>
@@ -7479,20 +10340,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>221</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>222</v>
+        <v>349</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>18</v>
@@ -7507,7 +10368,7 @@
         <v>21</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>223</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7515,23 +10376,23 @@
         <v>56</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>224</v>
+        <v>351</v>
       </c>
       <c r="C5" s="24" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A5,'All runs'!$B:$B,0))</f>
-        <v>2501</v>
+        <v>2446</v>
       </c>
       <c r="D5" s="24" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($A5,'All runs'!$B:$B,0))</f>
-        <v>2589</v>
+        <v>2536</v>
       </c>
       <c r="E5" s="24" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($A5,'All runs'!$B:$B,0))</f>
-        <v>2636</v>
+        <v>2566</v>
       </c>
       <c r="F5" s="25" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($A5,'All runs'!$B:$B,0))</f>
-        <v>0.996527</v>
+        <v>0.997208</v>
       </c>
       <c r="G5" s="26" t="n">
         <f aca="false">C5/$C$5-1</f>
@@ -7543,27 +10404,27 @@
         <v>63</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>225</v>
+        <v>352</v>
       </c>
       <c r="C6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A6,'All runs'!$B:$B,0))</f>
-        <v>2501</v>
+        <v>2451</v>
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($A6,'All runs'!$B:$B,0))</f>
-        <v>2589</v>
+        <v>2541</v>
       </c>
       <c r="E6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($A6,'All runs'!$B:$B,0))</f>
-        <v>2636</v>
+        <v>2581</v>
       </c>
       <c r="F6" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($A6,'All runs'!$B:$B,0))</f>
-        <v>0.996527</v>
+        <v>0.997409</v>
       </c>
       <c r="G6" s="21" t="n">
         <f aca="false">C6/$C$5-1</f>
-        <v>0</v>
+        <v>0.00204415372035971</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7571,27 +10432,27 @@
         <v>64</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>226</v>
+        <v>353</v>
       </c>
       <c r="C7" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A7,'All runs'!$B:$B,0))</f>
-        <v>2496</v>
+        <v>2430</v>
       </c>
       <c r="D7" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($A7,'All runs'!$B:$B,0))</f>
-        <v>2581</v>
+        <v>2535</v>
       </c>
       <c r="E7" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($A7,'All runs'!$B:$B,0))</f>
-        <v>2641</v>
+        <v>2581</v>
       </c>
       <c r="F7" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($A7,'All runs'!$B:$B,0))</f>
-        <v>0.996573</v>
+        <v>0.996309</v>
       </c>
       <c r="G7" s="16" t="n">
         <f aca="false">C7/$C$5-1</f>
-        <v>-0.001999200319872</v>
+        <v>-0.00654129190515129</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7599,23 +10460,23 @@
         <v>65</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>227</v>
+        <v>354</v>
       </c>
       <c r="C8" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A8,'All runs'!$B:$B,0))</f>
-        <v>2501</v>
+        <v>2446</v>
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($A8,'All runs'!$B:$B,0))</f>
-        <v>2586</v>
+        <v>2536</v>
       </c>
       <c r="E8" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($A8,'All runs'!$B:$B,0))</f>
-        <v>2626</v>
+        <v>2566</v>
       </c>
       <c r="F8" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($A8,'All runs'!$B:$B,0))</f>
-        <v>0.997107</v>
+        <v>0.997105</v>
       </c>
       <c r="G8" s="21" t="n">
         <f aca="false">C8/$C$5-1</f>
@@ -7627,7 +10488,7 @@
         <v>66</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>228</v>
+        <v>355</v>
       </c>
       <c r="C9" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A9,'All runs'!$B:$B,0))</f>
@@ -7635,19 +10496,19 @@
       </c>
       <c r="D9" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($A9,'All runs'!$B:$B,0))</f>
-        <v>1946</v>
+        <v>1916</v>
       </c>
       <c r="E9" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($A9,'All runs'!$B:$B,0))</f>
-        <v>2021</v>
+        <v>1981</v>
       </c>
       <c r="F9" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($A9,'All runs'!$B:$B,0))</f>
-        <v>0.994142</v>
+        <v>0.995359</v>
       </c>
       <c r="G9" s="16" t="n">
         <f aca="false">C9/$C$5-1</f>
-        <v>-0.293882447021192</v>
+        <v>-0.278004905968929</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7655,27 +10516,27 @@
         <v>67</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>229</v>
+        <v>356</v>
       </c>
       <c r="C10" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A10,'All runs'!$B:$B,0))</f>
-        <v>2106</v>
+        <v>2171</v>
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($A10,'All runs'!$B:$B,0))</f>
-        <v>2516</v>
+        <v>2481</v>
       </c>
       <c r="E10" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($A10,'All runs'!$B:$B,0))</f>
-        <v>2616</v>
+        <v>2551</v>
       </c>
       <c r="F10" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($A10,'All runs'!$B:$B,0))</f>
-        <v>0.997063</v>
+        <v>0.997721</v>
       </c>
       <c r="G10" s="21" t="n">
         <f aca="false">C10/$C$5-1</f>
-        <v>-0.157936825269892</v>
+        <v>-0.112428454619787</v>
       </c>
     </row>
   </sheetData>
@@ -7708,23 +10569,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>230</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>231</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>232</v>
+        <v>359</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>233</v>
+        <v>360</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
@@ -7739,7 +10600,7 @@
         <v>21</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>234</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7747,26 +10608,26 @@
         <v>69</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>235</v>
+        <v>362</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>236</v>
+        <v>363</v>
       </c>
       <c r="D5" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A5,'All runs'!$B:$B,0))</f>
-        <v>2501</v>
+        <v>2446</v>
       </c>
       <c r="E5" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($A5,'All runs'!$B:$B,0))</f>
-        <v>2589</v>
+        <v>2536</v>
       </c>
       <c r="F5" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($A5,'All runs'!$B:$B,0))</f>
-        <v>2636</v>
+        <v>2566</v>
       </c>
       <c r="G5" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($A5,'All runs'!$B:$B,0))</f>
-        <v>0.996527</v>
+        <v>0.997208</v>
       </c>
       <c r="H5" s="16" t="n">
         <f aca="false">D5/$D$5-1</f>
@@ -7778,30 +10639,30 @@
         <v>70</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>235</v>
+        <v>362</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>237</v>
+        <v>364</v>
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A6,'All runs'!$B:$B,0))</f>
-        <v>2436</v>
+        <v>2381</v>
       </c>
       <c r="E6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($A6,'All runs'!$B:$B,0))</f>
-        <v>2531</v>
+        <v>2486</v>
       </c>
       <c r="F6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($A6,'All runs'!$B:$B,0))</f>
-        <v>2561</v>
+        <v>2521</v>
       </c>
       <c r="G6" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($A6,'All runs'!$B:$B,0))</f>
-        <v>0.996404</v>
+        <v>0.996779</v>
       </c>
       <c r="H6" s="21" t="n">
         <f aca="false">D6/$D$5-1</f>
-        <v>-0.0259896041583366</v>
+        <v>-0.026573998364677</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7809,26 +10670,26 @@
         <v>71</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>235</v>
+        <v>362</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>238</v>
+        <v>365</v>
       </c>
       <c r="D7" s="24" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A7,'All runs'!$B:$B,0))</f>
-        <v>2501</v>
+        <v>2446</v>
       </c>
       <c r="E7" s="24" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($A7,'All runs'!$B:$B,0))</f>
-        <v>2589</v>
+        <v>2536</v>
       </c>
       <c r="F7" s="24" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($A7,'All runs'!$B:$B,0))</f>
-        <v>2631</v>
+        <v>2566</v>
       </c>
       <c r="G7" s="25" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($A7,'All runs'!$B:$B,0))</f>
-        <v>0.996392</v>
+        <v>0.997168</v>
       </c>
       <c r="H7" s="26" t="n">
         <f aca="false">D7/$D$5-1</f>
@@ -7840,26 +10701,26 @@
         <v>72</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>239</v>
+        <v>366</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>236</v>
+        <v>363</v>
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A8,'All runs'!$B:$B,0))</f>
-        <v>1441</v>
+        <v>1406</v>
       </c>
       <c r="E8" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($A8,'All runs'!$B:$B,0))</f>
-        <v>1596</v>
+        <v>1551</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($A8,'All runs'!$B:$B,0))</f>
-        <v>1646</v>
+        <v>1606</v>
       </c>
       <c r="G8" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($A8,'All runs'!$B:$B,0))</f>
-        <v>0.994649</v>
+        <v>0.993787</v>
       </c>
       <c r="H8" s="21" t="n">
         <f aca="false">D8/$D$8-1</f>
@@ -7871,30 +10732,30 @@
         <v>73</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>239</v>
+        <v>366</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>237</v>
+        <v>364</v>
       </c>
       <c r="D9" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A9,'All runs'!$B:$B,0))</f>
-        <v>1636</v>
+        <v>1586</v>
       </c>
       <c r="E9" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($A9,'All runs'!$B:$B,0))</f>
-        <v>1846</v>
+        <v>1801</v>
       </c>
       <c r="F9" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($A9,'All runs'!$B:$B,0))</f>
-        <v>1891</v>
+        <v>1866</v>
       </c>
       <c r="G9" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($A9,'All runs'!$B:$B,0))</f>
-        <v>0.994479</v>
+        <v>0.995802</v>
       </c>
       <c r="H9" s="16" t="n">
         <f aca="false">D9/$D$8-1</f>
-        <v>0.135322692574601</v>
+        <v>0.128022759601707</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7902,30 +10763,30 @@
         <v>74</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>239</v>
+        <v>366</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>238</v>
+        <v>365</v>
       </c>
       <c r="D10" s="24" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A10,'All runs'!$B:$B,0))</f>
-        <v>1671</v>
+        <v>1626</v>
       </c>
       <c r="E10" s="24" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($A10,'All runs'!$B:$B,0))</f>
-        <v>1851</v>
+        <v>1821</v>
       </c>
       <c r="F10" s="24" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($A10,'All runs'!$B:$B,0))</f>
-        <v>1906</v>
+        <v>1881</v>
       </c>
       <c r="G10" s="25" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($A10,'All runs'!$B:$B,0))</f>
-        <v>0.993581</v>
+        <v>0.995637</v>
       </c>
       <c r="H10" s="26" t="n">
         <f aca="false">D10/$D$8-1</f>
-        <v>0.159611380985427</v>
+        <v>0.15647226173542</v>
       </c>
     </row>
   </sheetData>
@@ -7957,23 +10818,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>240</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>241</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>118</v>
+        <v>245</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>242</v>
+        <v>369</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
@@ -7990,10 +10851,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>243</v>
+        <v>370</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>244</v>
+        <v>371</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>77</v>
@@ -8004,50 +10865,50 @@
       </c>
       <c r="E5" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C5,'All runs'!$B:$B,0))</f>
-        <v>2011</v>
+        <v>1996</v>
       </c>
       <c r="F5" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C5,'All runs'!$B:$B,0))</f>
-        <v>2106</v>
+        <v>2116</v>
       </c>
       <c r="G5" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C5,'All runs'!$B:$B,0))</f>
-        <v>0.985626</v>
+        <v>0.986194</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>243</v>
+        <v>370</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>245</v>
+        <v>372</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>76</v>
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C6,'All runs'!$B:$B,0))</f>
-        <v>1602</v>
+        <v>1743</v>
       </c>
       <c r="E6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C6,'All runs'!$B:$B,0))</f>
-        <v>2040</v>
+        <v>2031</v>
       </c>
       <c r="F6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C6,'All runs'!$B:$B,0))</f>
-        <v>2126</v>
+        <v>2121</v>
       </c>
       <c r="G6" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C6,'All runs'!$B:$B,0))</f>
-        <v>0.984329</v>
+        <v>0.986778</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>243</v>
+        <v>370</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>246</v>
+        <v>373</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>82</v>
@@ -8062,1203 +10923,1203 @@
       </c>
       <c r="F7" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C7,'All runs'!$B:$B,0))</f>
-        <v>2701</v>
+        <v>2303</v>
       </c>
       <c r="G7" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C7,'All runs'!$B:$B,0))</f>
-        <v>0.973292</v>
+        <v>0.976919</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>243</v>
+        <v>370</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>247</v>
+        <v>374</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>80</v>
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C8,'All runs'!$B:$B,0))</f>
-        <v>1666</v>
+        <v>1551</v>
       </c>
       <c r="E8" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C8,'All runs'!$B:$B,0))</f>
-        <v>2061</v>
+        <v>2051</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C8,'All runs'!$B:$B,0))</f>
-        <v>2302</v>
+        <v>2401</v>
       </c>
       <c r="G8" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C8,'All runs'!$B:$B,0))</f>
-        <v>0.980665</v>
+        <v>0.982669</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>243</v>
+        <v>370</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>248</v>
+        <v>375</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>83</v>
       </c>
       <c r="D9" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C9,'All runs'!$B:$B,0))</f>
-        <v>1639</v>
+        <v>1681</v>
       </c>
       <c r="E9" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C9,'All runs'!$B:$B,0))</f>
-        <v>2045</v>
+        <v>2051</v>
       </c>
       <c r="F9" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C9,'All runs'!$B:$B,0))</f>
-        <v>2146</v>
+        <v>2201</v>
       </c>
       <c r="G9" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C9,'All runs'!$B:$B,0))</f>
-        <v>0.979466</v>
+        <v>0.981511</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>243</v>
+        <v>370</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>249</v>
+        <v>376</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>78</v>
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C10,'All runs'!$B:$B,0))</f>
-        <v>1611</v>
+        <v>1606</v>
       </c>
       <c r="E10" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C10,'All runs'!$B:$B,0))</f>
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="F10" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C10,'All runs'!$B:$B,0))</f>
-        <v>2201</v>
+        <v>2116</v>
       </c>
       <c r="G10" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C10,'All runs'!$B:$B,0))</f>
-        <v>0.980777</v>
+        <v>0.98646</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>243</v>
+        <v>370</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>250</v>
+        <v>377</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>79</v>
       </c>
       <c r="D11" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C11,'All runs'!$B:$B,0))</f>
-        <v>1431</v>
+        <v>1410</v>
       </c>
       <c r="E11" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C11,'All runs'!$B:$B,0))</f>
-        <v>2046</v>
+        <v>2041</v>
       </c>
       <c r="F11" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C11,'All runs'!$B:$B,0))</f>
-        <v>2211</v>
+        <v>2141</v>
       </c>
       <c r="G11" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C11,'All runs'!$B:$B,0))</f>
-        <v>0.983414</v>
+        <v>0.987119</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>243</v>
+        <v>370</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>251</v>
+        <v>378</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>81</v>
       </c>
       <c r="D12" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C12,'All runs'!$B:$B,0))</f>
-        <v>1625</v>
+        <v>1486</v>
       </c>
       <c r="E12" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C12,'All runs'!$B:$B,0))</f>
-        <v>2036</v>
+        <v>2041</v>
       </c>
       <c r="F12" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C12,'All runs'!$B:$B,0))</f>
-        <v>2121</v>
+        <v>2502</v>
       </c>
       <c r="G12" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C12,'All runs'!$B:$B,0))</f>
-        <v>0.981109</v>
+        <v>0.982345</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>214</v>
+        <v>341</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>244</v>
+        <v>371</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>85</v>
       </c>
       <c r="D13" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C13,'All runs'!$B:$B,0))</f>
-        <v>2501</v>
+        <v>2446</v>
       </c>
       <c r="E13" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C13,'All runs'!$B:$B,0))</f>
-        <v>2589</v>
+        <v>2536</v>
       </c>
       <c r="F13" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C13,'All runs'!$B:$B,0))</f>
-        <v>2636</v>
+        <v>2566</v>
       </c>
       <c r="G13" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C13,'All runs'!$B:$B,0))</f>
-        <v>0.996527</v>
+        <v>0.997208</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>214</v>
+        <v>341</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>245</v>
+        <v>372</v>
       </c>
       <c r="C14" s="18" t="s">
         <v>84</v>
       </c>
       <c r="D14" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C14,'All runs'!$B:$B,0))</f>
-        <v>2511</v>
+        <v>2481</v>
       </c>
       <c r="E14" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C14,'All runs'!$B:$B,0))</f>
-        <v>2601</v>
+        <v>2551</v>
       </c>
       <c r="F14" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C14,'All runs'!$B:$B,0))</f>
-        <v>2646</v>
+        <v>2596</v>
       </c>
       <c r="G14" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C14,'All runs'!$B:$B,0))</f>
-        <v>0.996431</v>
+        <v>0.99752</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>214</v>
+        <v>341</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>246</v>
+        <v>373</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>90</v>
       </c>
       <c r="D15" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C15,'All runs'!$B:$B,0))</f>
-        <v>2531</v>
+        <v>2476</v>
       </c>
       <c r="E15" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C15,'All runs'!$B:$B,0))</f>
-        <v>2634</v>
+        <v>2581</v>
       </c>
       <c r="F15" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C15,'All runs'!$B:$B,0))</f>
-        <v>2671</v>
+        <v>2621</v>
       </c>
       <c r="G15" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C15,'All runs'!$B:$B,0))</f>
-        <v>0.996847</v>
+        <v>0.997118</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>214</v>
+        <v>341</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>247</v>
+        <v>374</v>
       </c>
       <c r="C16" s="18" t="s">
         <v>88</v>
       </c>
       <c r="D16" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C16,'All runs'!$B:$B,0))</f>
-        <v>2496</v>
+        <v>2416</v>
       </c>
       <c r="E16" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C16,'All runs'!$B:$B,0))</f>
-        <v>2578</v>
+        <v>2546</v>
       </c>
       <c r="F16" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C16,'All runs'!$B:$B,0))</f>
-        <v>2621</v>
+        <v>2581</v>
       </c>
       <c r="G16" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C16,'All runs'!$B:$B,0))</f>
-        <v>0.996601</v>
+        <v>0.997119</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>214</v>
+        <v>341</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>248</v>
+        <v>375</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>91</v>
       </c>
       <c r="D17" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C17,'All runs'!$B:$B,0))</f>
-        <v>2471</v>
+        <v>2446</v>
       </c>
       <c r="E17" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C17,'All runs'!$B:$B,0))</f>
-        <v>2606</v>
+        <v>2541</v>
       </c>
       <c r="F17" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C17,'All runs'!$B:$B,0))</f>
-        <v>2636</v>
+        <v>2571</v>
       </c>
       <c r="G17" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C17,'All runs'!$B:$B,0))</f>
-        <v>0.996435</v>
+        <v>0.996922</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>214</v>
+        <v>341</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>249</v>
+        <v>376</v>
       </c>
       <c r="C18" s="18" t="s">
         <v>86</v>
       </c>
       <c r="D18" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C18,'All runs'!$B:$B,0))</f>
-        <v>2491</v>
+        <v>2401</v>
       </c>
       <c r="E18" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C18,'All runs'!$B:$B,0))</f>
-        <v>2568</v>
+        <v>2507</v>
       </c>
       <c r="F18" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C18,'All runs'!$B:$B,0))</f>
-        <v>2606</v>
+        <v>2541</v>
       </c>
       <c r="G18" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C18,'All runs'!$B:$B,0))</f>
-        <v>0.996691</v>
+        <v>0.997033</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>214</v>
+        <v>341</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>250</v>
+        <v>377</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>87</v>
       </c>
       <c r="D19" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C19,'All runs'!$B:$B,0))</f>
-        <v>2506</v>
+        <v>2466</v>
       </c>
       <c r="E19" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C19,'All runs'!$B:$B,0))</f>
-        <v>2603</v>
+        <v>2567</v>
       </c>
       <c r="F19" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C19,'All runs'!$B:$B,0))</f>
-        <v>2651</v>
+        <v>2611</v>
       </c>
       <c r="G19" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C19,'All runs'!$B:$B,0))</f>
-        <v>0.996986</v>
+        <v>0.997024</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>214</v>
+        <v>341</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>251</v>
+        <v>378</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>89</v>
       </c>
       <c r="D20" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C20,'All runs'!$B:$B,0))</f>
-        <v>2491</v>
+        <v>2451</v>
       </c>
       <c r="E20" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C20,'All runs'!$B:$B,0))</f>
-        <v>2581</v>
+        <v>2526</v>
       </c>
       <c r="F20" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C20,'All runs'!$B:$B,0))</f>
-        <v>2621</v>
+        <v>2561</v>
       </c>
       <c r="G20" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C20,'All runs'!$B:$B,0))</f>
-        <v>0.995811</v>
+        <v>0.997042</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>217</v>
+        <v>344</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>244</v>
+        <v>371</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>93</v>
       </c>
       <c r="D21" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C21,'All runs'!$B:$B,0))</f>
-        <v>2501</v>
+        <v>2446</v>
       </c>
       <c r="E21" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C21,'All runs'!$B:$B,0))</f>
-        <v>2589</v>
+        <v>2536</v>
       </c>
       <c r="F21" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C21,'All runs'!$B:$B,0))</f>
-        <v>2631</v>
+        <v>2566</v>
       </c>
       <c r="G21" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C21,'All runs'!$B:$B,0))</f>
-        <v>0.996392</v>
+        <v>0.997168</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="s">
-        <v>217</v>
+        <v>344</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>245</v>
+        <v>372</v>
       </c>
       <c r="C22" s="18" t="s">
         <v>92</v>
       </c>
       <c r="D22" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C22,'All runs'!$B:$B,0))</f>
-        <v>2511</v>
+        <v>2481</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C22,'All runs'!$B:$B,0))</f>
-        <v>2601</v>
+        <v>2551</v>
       </c>
       <c r="F22" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C22,'All runs'!$B:$B,0))</f>
-        <v>2646</v>
+        <v>2596</v>
       </c>
       <c r="G22" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C22,'All runs'!$B:$B,0))</f>
-        <v>0.996428</v>
+        <v>0.997438</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>217</v>
+        <v>344</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>246</v>
+        <v>373</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>98</v>
       </c>
       <c r="D23" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C23,'All runs'!$B:$B,0))</f>
-        <v>2531</v>
+        <v>2476</v>
       </c>
       <c r="E23" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C23,'All runs'!$B:$B,0))</f>
-        <v>2634</v>
+        <v>2581</v>
       </c>
       <c r="F23" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C23,'All runs'!$B:$B,0))</f>
-        <v>2676</v>
+        <v>2621</v>
       </c>
       <c r="G23" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C23,'All runs'!$B:$B,0))</f>
-        <v>0.996544</v>
+        <v>0.996897</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="18" t="s">
-        <v>217</v>
+        <v>344</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>247</v>
+        <v>374</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>96</v>
       </c>
       <c r="D24" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C24,'All runs'!$B:$B,0))</f>
-        <v>2496</v>
+        <v>2416</v>
       </c>
       <c r="E24" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C24,'All runs'!$B:$B,0))</f>
-        <v>2578</v>
+        <v>2546</v>
       </c>
       <c r="F24" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C24,'All runs'!$B:$B,0))</f>
-        <v>2626</v>
+        <v>2581</v>
       </c>
       <c r="G24" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C24,'All runs'!$B:$B,0))</f>
-        <v>0.996407</v>
+        <v>0.99721</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>217</v>
+        <v>344</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>248</v>
+        <v>375</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>99</v>
       </c>
       <c r="D25" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C25,'All runs'!$B:$B,0))</f>
-        <v>2471</v>
+        <v>2446</v>
       </c>
       <c r="E25" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C25,'All runs'!$B:$B,0))</f>
-        <v>2606</v>
+        <v>2541</v>
       </c>
       <c r="F25" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C25,'All runs'!$B:$B,0))</f>
-        <v>2641</v>
+        <v>2571</v>
       </c>
       <c r="G25" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C25,'All runs'!$B:$B,0))</f>
-        <v>0.996132</v>
+        <v>0.997079</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="s">
-        <v>217</v>
+        <v>344</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>249</v>
+        <v>376</v>
       </c>
       <c r="C26" s="18" t="s">
         <v>94</v>
       </c>
       <c r="D26" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C26,'All runs'!$B:$B,0))</f>
-        <v>2491</v>
+        <v>2401</v>
       </c>
       <c r="E26" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C26,'All runs'!$B:$B,0))</f>
-        <v>2568</v>
+        <v>2507</v>
       </c>
       <c r="F26" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C26,'All runs'!$B:$B,0))</f>
-        <v>2601</v>
+        <v>2541</v>
       </c>
       <c r="G26" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C26,'All runs'!$B:$B,0))</f>
-        <v>0.996703</v>
+        <v>0.997081</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>217</v>
+        <v>344</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>250</v>
+        <v>377</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>95</v>
       </c>
       <c r="D27" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C27,'All runs'!$B:$B,0))</f>
-        <v>2506</v>
+        <v>2466</v>
       </c>
       <c r="E27" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C27,'All runs'!$B:$B,0))</f>
-        <v>2603</v>
+        <v>2567</v>
       </c>
       <c r="F27" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C27,'All runs'!$B:$B,0))</f>
-        <v>2646</v>
+        <v>2611</v>
       </c>
       <c r="G27" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C27,'All runs'!$B:$B,0))</f>
-        <v>0.997105</v>
+        <v>0.997048</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>217</v>
+        <v>344</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>251</v>
+        <v>378</v>
       </c>
       <c r="C28" s="18" t="s">
         <v>97</v>
       </c>
       <c r="D28" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C28,'All runs'!$B:$B,0))</f>
-        <v>2491</v>
+        <v>2451</v>
       </c>
       <c r="E28" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C28,'All runs'!$B:$B,0))</f>
-        <v>2581</v>
+        <v>2526</v>
       </c>
       <c r="F28" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C28,'All runs'!$B:$B,0))</f>
-        <v>2641</v>
+        <v>2566</v>
       </c>
       <c r="G28" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C28,'All runs'!$B:$B,0))</f>
-        <v>0.995049</v>
+        <v>0.996856</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>216</v>
+        <v>343</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>244</v>
+        <v>371</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D29" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C29,'All runs'!$B:$B,0))</f>
-        <v>1441</v>
+        <v>1406</v>
       </c>
       <c r="E29" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C29,'All runs'!$B:$B,0))</f>
-        <v>1596</v>
+        <v>1551</v>
       </c>
       <c r="F29" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C29,'All runs'!$B:$B,0))</f>
-        <v>1646</v>
+        <v>1606</v>
       </c>
       <c r="G29" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C29,'All runs'!$B:$B,0))</f>
-        <v>0.994649</v>
+        <v>0.993787</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="s">
-        <v>216</v>
+        <v>343</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>245</v>
+        <v>372</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D30" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C30,'All runs'!$B:$B,0))</f>
-        <v>1466</v>
+        <v>1386</v>
       </c>
       <c r="E30" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C30,'All runs'!$B:$B,0))</f>
-        <v>1651</v>
+        <v>1636</v>
       </c>
       <c r="F30" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C30,'All runs'!$B:$B,0))</f>
-        <v>1696</v>
+        <v>1671</v>
       </c>
       <c r="G30" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C30,'All runs'!$B:$B,0))</f>
-        <v>0.993332</v>
+        <v>0.993522</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>216</v>
+        <v>343</v>
       </c>
       <c r="B31" s="37" t="s">
-        <v>246</v>
+        <v>373</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D31" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C31,'All runs'!$B:$B,0))</f>
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="E31" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C31,'All runs'!$B:$B,0))</f>
-        <v>1646</v>
+        <v>1621</v>
       </c>
       <c r="F31" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C31,'All runs'!$B:$B,0))</f>
-        <v>1701</v>
+        <v>1671</v>
       </c>
       <c r="G31" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C31,'All runs'!$B:$B,0))</f>
-        <v>0.992082</v>
+        <v>0.994442</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="18" t="s">
-        <v>216</v>
+        <v>343</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>247</v>
+        <v>374</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D32" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C32,'All runs'!$B:$B,0))</f>
-        <v>1451</v>
+        <v>1436</v>
       </c>
       <c r="E32" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C32,'All runs'!$B:$B,0))</f>
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="F32" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C32,'All runs'!$B:$B,0))</f>
-        <v>1696</v>
+        <v>1666</v>
       </c>
       <c r="G32" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C32,'All runs'!$B:$B,0))</f>
-        <v>0.992346</v>
+        <v>0.993628</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>216</v>
+        <v>343</v>
       </c>
       <c r="B33" s="37" t="s">
-        <v>248</v>
+        <v>375</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D33" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C33,'All runs'!$B:$B,0))</f>
-        <v>1446</v>
+        <v>1416</v>
       </c>
       <c r="E33" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C33,'All runs'!$B:$B,0))</f>
-        <v>1646</v>
+        <v>1626</v>
       </c>
       <c r="F33" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C33,'All runs'!$B:$B,0))</f>
-        <v>1701</v>
+        <v>1666</v>
       </c>
       <c r="G33" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C33,'All runs'!$B:$B,0))</f>
-        <v>0.99434</v>
+        <v>0.993002</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="18" t="s">
-        <v>216</v>
+        <v>343</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>249</v>
+        <v>376</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D34" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C34,'All runs'!$B:$B,0))</f>
-        <v>1421</v>
+        <v>1346</v>
       </c>
       <c r="E34" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C34,'All runs'!$B:$B,0))</f>
-        <v>1606</v>
+        <v>1571</v>
       </c>
       <c r="F34" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C34,'All runs'!$B:$B,0))</f>
-        <v>1651</v>
+        <v>1631</v>
       </c>
       <c r="G34" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C34,'All runs'!$B:$B,0))</f>
-        <v>0.994033</v>
+        <v>0.994742</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>216</v>
+        <v>343</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>250</v>
+        <v>377</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D35" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C35,'All runs'!$B:$B,0))</f>
-        <v>1446</v>
+        <v>1436</v>
       </c>
       <c r="E35" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C35,'All runs'!$B:$B,0))</f>
-        <v>1641</v>
+        <v>1626</v>
       </c>
       <c r="F35" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C35,'All runs'!$B:$B,0))</f>
-        <v>1691</v>
+        <v>1676</v>
       </c>
       <c r="G35" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C35,'All runs'!$B:$B,0))</f>
-        <v>0.994139</v>
+        <v>0.992915</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="18" t="s">
-        <v>216</v>
+        <v>343</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>251</v>
+        <v>378</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D36" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C36,'All runs'!$B:$B,0))</f>
-        <v>1391</v>
+        <v>1396</v>
       </c>
       <c r="E36" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C36,'All runs'!$B:$B,0))</f>
-        <v>1596</v>
+        <v>1566</v>
       </c>
       <c r="F36" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C36,'All runs'!$B:$B,0))</f>
-        <v>1651</v>
+        <v>1616</v>
       </c>
       <c r="G36" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C36,'All runs'!$B:$B,0))</f>
-        <v>0.993827</v>
+        <v>0.993724</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>219</v>
+        <v>346</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>244</v>
+        <v>371</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D37" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C37,'All runs'!$B:$B,0))</f>
-        <v>1671</v>
+        <v>1626</v>
       </c>
       <c r="E37" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C37,'All runs'!$B:$B,0))</f>
-        <v>1851</v>
+        <v>1821</v>
       </c>
       <c r="F37" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C37,'All runs'!$B:$B,0))</f>
-        <v>1906</v>
+        <v>1881</v>
       </c>
       <c r="G37" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C37,'All runs'!$B:$B,0))</f>
-        <v>0.993581</v>
+        <v>0.995637</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="18" t="s">
-        <v>219</v>
+        <v>346</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>245</v>
+        <v>372</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D38" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C38,'All runs'!$B:$B,0))</f>
-        <v>1661</v>
+        <v>1636</v>
       </c>
       <c r="E38" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C38,'All runs'!$B:$B,0))</f>
-        <v>1891</v>
+        <v>1866</v>
       </c>
       <c r="F38" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C38,'All runs'!$B:$B,0))</f>
-        <v>1951</v>
+        <v>1911</v>
       </c>
       <c r="G38" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C38,'All runs'!$B:$B,0))</f>
-        <v>0.994434</v>
+        <v>0.994081</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>219</v>
+        <v>346</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>246</v>
+        <v>373</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D39" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C39,'All runs'!$B:$B,0))</f>
-        <v>1681</v>
+        <v>1646</v>
       </c>
       <c r="E39" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C39,'All runs'!$B:$B,0))</f>
-        <v>1881</v>
+        <v>1871</v>
       </c>
       <c r="F39" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C39,'All runs'!$B:$B,0))</f>
-        <v>1956</v>
+        <v>1916</v>
       </c>
       <c r="G39" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C39,'All runs'!$B:$B,0))</f>
-        <v>0.993912</v>
+        <v>0.994856</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="s">
-        <v>219</v>
+        <v>346</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>247</v>
+        <v>374</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D40" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C40,'All runs'!$B:$B,0))</f>
-        <v>1716</v>
+        <v>1681</v>
       </c>
       <c r="E40" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C40,'All runs'!$B:$B,0))</f>
-        <v>1891</v>
+        <v>1871</v>
       </c>
       <c r="F40" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C40,'All runs'!$B:$B,0))</f>
-        <v>1951</v>
+        <v>1921</v>
       </c>
       <c r="G40" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C40,'All runs'!$B:$B,0))</f>
-        <v>0.993293</v>
+        <v>0.993602</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>219</v>
+        <v>346</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>248</v>
+        <v>375</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D41" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C41,'All runs'!$B:$B,0))</f>
-        <v>1721</v>
+        <v>1676</v>
       </c>
       <c r="E41" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C41,'All runs'!$B:$B,0))</f>
-        <v>1876</v>
+        <v>1851</v>
       </c>
       <c r="F41" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C41,'All runs'!$B:$B,0))</f>
-        <v>1926</v>
+        <v>1901</v>
       </c>
       <c r="G41" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C41,'All runs'!$B:$B,0))</f>
-        <v>0.995348</v>
+        <v>0.994335</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="18" t="s">
-        <v>219</v>
+        <v>346</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>249</v>
+        <v>376</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D42" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C42,'All runs'!$B:$B,0))</f>
-        <v>1646</v>
+        <v>1596</v>
       </c>
       <c r="E42" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C42,'All runs'!$B:$B,0))</f>
-        <v>1851</v>
+        <v>1826</v>
       </c>
       <c r="F42" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C42,'All runs'!$B:$B,0))</f>
-        <v>1921</v>
+        <v>1876</v>
       </c>
       <c r="G42" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C42,'All runs'!$B:$B,0))</f>
-        <v>0.994472</v>
+        <v>0.995765</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>219</v>
+        <v>346</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>250</v>
+        <v>377</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D43" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C43,'All runs'!$B:$B,0))</f>
-        <v>1716</v>
+        <v>1681</v>
       </c>
       <c r="E43" s="14" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C43,'All runs'!$B:$B,0))</f>
-        <v>1881</v>
+        <v>1861</v>
       </c>
       <c r="F43" s="14" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C43,'All runs'!$B:$B,0))</f>
-        <v>1941</v>
+        <v>1901</v>
       </c>
       <c r="G43" s="15" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C43,'All runs'!$B:$B,0))</f>
-        <v>0.993319</v>
+        <v>0.992752</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="18" t="s">
-        <v>219</v>
+        <v>346</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>251</v>
+        <v>378</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D44" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($C44,'All runs'!$B:$B,0))</f>
-        <v>1641</v>
+        <v>1671</v>
       </c>
       <c r="E44" s="19" t="n">
         <f aca="false">INDEX('All runs'!$D:$D,MATCH($C44,'All runs'!$B:$B,0))</f>
-        <v>1856</v>
+        <v>1831</v>
       </c>
       <c r="F44" s="19" t="n">
         <f aca="false">INDEX('All runs'!$E:$E,MATCH($C44,'All runs'!$B:$B,0))</f>
-        <v>1916</v>
+        <v>1876</v>
       </c>
       <c r="G44" s="20" t="n">
         <f aca="false">INDEX('All runs'!$F:$F,MATCH($C44,'All runs'!$B:$B,0))</f>
-        <v>0.994133</v>
+        <v>0.995833</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>118</v>
+        <v>245</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6" t="s">
-        <v>252</v>
+        <v>379</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>253</v>
+        <v>380</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>254</v>
+        <v>381</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>255</v>
+        <v>382</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>256</v>
+        <v>383</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>257</v>
+        <v>384</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>258</v>
+        <v>385</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>243</v>
+        <v>370</v>
       </c>
       <c r="D47" s="39" t="n">
         <f aca="false">AVERAGE(D5:D12)</f>
-        <v>1618</v>
+        <v>1605.875</v>
       </c>
       <c r="E47" s="39" t="n">
         <f aca="false">AVERAGE(E5:E12)</f>
-        <v>2040.625</v>
+        <v>2036</v>
       </c>
       <c r="F47" s="39" t="n">
         <f aca="false">AVERAGE(F5:F12)</f>
-        <v>2239.25</v>
+        <v>2237.625</v>
       </c>
       <c r="G47" s="40" t="n">
         <f aca="false">AVERAGE(G5:G12)</f>
-        <v>0.98108475</v>
+        <v>0.983749375</v>
       </c>
       <c r="H47" s="39" t="n">
         <f aca="false">MIN(D5:D12)</f>
-        <v>1431</v>
+        <v>1410</v>
       </c>
       <c r="I47" s="39" t="n">
         <f aca="false">MAX(D5:D12)</f>
-        <v>1725</v>
+        <v>1743</v>
       </c>
       <c r="J47" s="41" t="n">
         <f aca="false">(I47-H47)/2/D47</f>
-        <v>0.0908529048207664</v>
+        <v>0.103681793414805</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="18" t="s">
-        <v>214</v>
+        <v>341</v>
       </c>
       <c r="D48" s="42" t="n">
         <f aca="false">AVERAGE(D13:D20)</f>
-        <v>2499.75</v>
+        <v>2447.875</v>
       </c>
       <c r="E48" s="42" t="n">
         <f aca="false">AVERAGE(E13:E20)</f>
-        <v>2595</v>
+        <v>2544.375</v>
       </c>
       <c r="F48" s="42" t="n">
         <f aca="false">AVERAGE(F13:F20)</f>
-        <v>2636</v>
+        <v>2581</v>
       </c>
       <c r="G48" s="43" t="n">
         <f aca="false">AVERAGE(G13:G20)</f>
-        <v>0.996541125</v>
+        <v>0.99712325</v>
       </c>
       <c r="H48" s="42" t="n">
         <f aca="false">MIN(D13:D20)</f>
-        <v>2471</v>
+        <v>2401</v>
       </c>
       <c r="I48" s="42" t="n">
         <f aca="false">MAX(D13:D20)</f>
-        <v>2531</v>
+        <v>2481</v>
       </c>
       <c r="J48" s="44" t="n">
         <f aca="false">(I48-H48)/2/D48</f>
-        <v>0.012001200120012</v>
+        <v>0.0163407036715519</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="23" t="s">
-        <v>217</v>
+        <v>344</v>
       </c>
       <c r="D49" s="45" t="n">
         <f aca="false">AVERAGE(D21:D28)</f>
-        <v>2499.75</v>
+        <v>2447.875</v>
       </c>
       <c r="E49" s="45" t="n">
         <f aca="false">AVERAGE(E21:E28)</f>
-        <v>2595</v>
+        <v>2544.375</v>
       </c>
       <c r="F49" s="45" t="n">
         <f aca="false">AVERAGE(F21:F28)</f>
-        <v>2638.5</v>
+        <v>2581.625</v>
       </c>
       <c r="G49" s="46" t="n">
         <f aca="false">AVERAGE(G21:G28)</f>
-        <v>0.996345</v>
+        <v>0.997097125</v>
       </c>
       <c r="H49" s="45" t="n">
         <f aca="false">MIN(D21:D28)</f>
-        <v>2471</v>
+        <v>2401</v>
       </c>
       <c r="I49" s="45" t="n">
         <f aca="false">MAX(D21:D28)</f>
-        <v>2531</v>
+        <v>2481</v>
       </c>
       <c r="J49" s="47" t="n">
         <f aca="false">(I49-H49)/2/D49</f>
-        <v>0.012001200120012</v>
+        <v>0.0163407036715519</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="18" t="s">
-        <v>216</v>
+        <v>343</v>
       </c>
       <c r="D50" s="42" t="n">
         <f aca="false">AVERAGE(D29:D36)</f>
-        <v>1442.875</v>
+        <v>1412.25</v>
       </c>
       <c r="E50" s="42" t="n">
         <f aca="false">AVERAGE(E29:E36)</f>
-        <v>1627.25</v>
+        <v>1603.5</v>
       </c>
       <c r="F50" s="42" t="n">
         <f aca="false">AVERAGE(F29:F36)</f>
-        <v>1679.125</v>
+        <v>1650.375</v>
       </c>
       <c r="G50" s="43" t="n">
         <f aca="false">AVERAGE(G29:G36)</f>
-        <v>0.9935935</v>
+        <v>0.99372025</v>
       </c>
       <c r="H50" s="42" t="n">
         <f aca="false">MIN(D29:D36)</f>
-        <v>1391</v>
+        <v>1346</v>
       </c>
       <c r="I50" s="42" t="n">
         <f aca="false">MAX(D29:D36)</f>
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="J50" s="44" t="n">
         <f aca="false">(I50-H50)/2/D50</f>
-        <v>0.0311877328250888</v>
+        <v>0.0460258452823509</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="13" t="s">
-        <v>219</v>
+        <v>346</v>
       </c>
       <c r="D51" s="39" t="n">
         <f aca="false">AVERAGE(D37:D44)</f>
-        <v>1681.625</v>
+        <v>1651.625</v>
       </c>
       <c r="E51" s="39" t="n">
         <f aca="false">AVERAGE(E37:E44)</f>
-        <v>1872.25</v>
+        <v>1849.75</v>
       </c>
       <c r="F51" s="39" t="n">
         <f aca="false">AVERAGE(F37:F44)</f>
-        <v>1933.5</v>
+        <v>1897.875</v>
       </c>
       <c r="G51" s="40" t="n">
         <f aca="false">AVERAGE(G37:G44)</f>
-        <v>0.9940615</v>
+        <v>0.994607625</v>
       </c>
       <c r="H51" s="39" t="n">
         <f aca="false">MIN(D37:D44)</f>
-        <v>1641</v>
+        <v>1596</v>
       </c>
       <c r="I51" s="39" t="n">
         <f aca="false">MAX(D37:D44)</f>
-        <v>1721</v>
+        <v>1681</v>
       </c>
       <c r="J51" s="41" t="n">
         <f aca="false">(I51-H51)/2/D51</f>
-        <v>0.0237865160187319</v>
+        <v>0.0257322334064936</v>
       </c>
     </row>
   </sheetData>

--- a/thesis-final/Results_Comparison.xlsx
+++ b/thesis-final/Results_Comparison.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="411">
   <si>
     <t xml:space="preserve">Results comparison — v8-Chain thesis</t>
   </si>
@@ -377,39 +377,6 @@
   </si>
   <si>
     <t xml:space="preserve">v8_farBS_seed99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v8_chain_mic104_aes5nJ_center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v8_chain_mic104_aes5nJ_ecc20mJ_center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v8_chain_mic104_aes5nJ_ecc20mJ_far</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v8_chain_mic104_aes5nJ_far</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v8_chain_mic104_center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v8_chain_mic104_ecc20mJ_center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v8_chain_mic104_ecc20mJ_far</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v8_chain_mic104_far</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v8_chain_none_center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v8_chain_none_far</t>
   </si>
   <si>
     <t xml:space="preserve">far_bs</t>
@@ -2217,11 +2184,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="32135223"/>
-        <c:axId val="33015798"/>
+        <c:axId val="8187278"/>
+        <c:axId val="18269281"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="32135223"/>
+        <c:axId val="8187278"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2253,7 +2220,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33015798"/>
+        <c:crossAx val="18269281"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2261,7 +2228,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="33015798"/>
+        <c:axId val="18269281"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2337,7 +2304,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32135223"/>
+        <c:crossAx val="8187278"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2964,11 +2931,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="6505993"/>
-        <c:axId val="39638910"/>
+        <c:axId val="90524230"/>
+        <c:axId val="42581885"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="6505993"/>
+        <c:axId val="90524230"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3000,7 +2967,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39638910"/>
+        <c:crossAx val="42581885"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3008,7 +2975,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="39638910"/>
+        <c:axId val="42581885"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3084,7 +3051,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6505993"/>
+        <c:crossAx val="90524230"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3495,11 +3462,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="89937507"/>
-        <c:axId val="29399870"/>
+        <c:axId val="77799052"/>
+        <c:axId val="28736539"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="89937507"/>
+        <c:axId val="77799052"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3531,7 +3498,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29399870"/>
+        <c:crossAx val="28736539"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3539,7 +3506,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="29399870"/>
+        <c:axId val="28736539"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3615,7 +3582,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89937507"/>
+        <c:crossAx val="77799052"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4053,151 +4020,151 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -4216,7 +4183,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F214"/>
+  <dimension ref="A1:F204"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -5982,16 +5949,16 @@
         <v>117</v>
       </c>
       <c r="C91" s="8" t="n">
-        <v>2061</v>
+        <v>970</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>2141</v>
+        <v>1377</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>2176</v>
+        <v>1400</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>0.997941</v>
+        <v>0.99521</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6002,16 +5969,16 @@
         <v>118</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>1971</v>
+        <v>1410</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>2062</v>
+        <v>1437</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>2091</v>
+        <v>1457</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>0.997036</v>
+        <v>0.991819</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6022,16 +5989,16 @@
         <v>119</v>
       </c>
       <c r="C93" s="8" t="n">
-        <v>1336</v>
+        <v>350</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>1506</v>
+        <v>765</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>1546</v>
+        <v>1375</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>0.99502</v>
+        <v>0.995336</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6042,16 +6009,16 @@
         <v>120</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>1361</v>
+        <v>407</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>1566</v>
+        <v>756</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>1616</v>
+        <v>1386</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>0.99394</v>
+        <v>0.994919</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6062,16 +6029,16 @@
         <v>121</v>
       </c>
       <c r="C95" s="8" t="n">
-        <v>2246</v>
+        <v>1121</v>
       </c>
       <c r="D95" s="8" t="n">
-        <v>2321</v>
+        <v>1156</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>2351</v>
+        <v>1174</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>0.997584</v>
+        <v>0.980272</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6082,16 +6049,16 @@
         <v>122</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>2156</v>
+        <v>1219</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>2231</v>
+        <v>1262</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>2261</v>
+        <v>1278</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>0.997196</v>
+        <v>0.991184</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6102,16 +6069,16 @@
         <v>123</v>
       </c>
       <c r="C97" s="8" t="n">
-        <v>1426</v>
+        <v>988</v>
       </c>
       <c r="D97" s="8" t="n">
-        <v>1611</v>
+        <v>1230</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>1661</v>
+        <v>1652</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>0.995774</v>
+        <v>0.994295</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6122,16 +6089,16 @@
         <v>124</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>1491</v>
+        <v>1374</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>1686</v>
+        <v>2176</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>1721</v>
+        <v>2713</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>0.99558</v>
+        <v>0.990811</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6142,16 +6109,16 @@
         <v>125</v>
       </c>
       <c r="C99" s="8" t="n">
-        <v>2446</v>
+        <v>390</v>
       </c>
       <c r="D99" s="8" t="n">
-        <v>2536</v>
+        <v>601</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>2566</v>
+        <v>861</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>0.997168</v>
+        <v>0.996734</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6162,413 +6129,413 @@
         <v>126</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>1626</v>
+        <v>1388</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>1821</v>
+        <v>1435</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>1881</v>
+        <v>1455</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>0.995637</v>
+        <v>0.988878</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B101" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B101" s="7" t="s">
-        <v>128</v>
-      </c>
       <c r="C101" s="8" t="n">
-        <v>970</v>
+        <v>1161</v>
       </c>
       <c r="D101" s="8" t="n">
-        <v>1377</v>
+        <v>1546</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>1400</v>
+        <v>2902</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>0.99521</v>
+        <v>0.980928</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="10" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C102" s="11" t="n">
-        <v>1410</v>
+        <v>1161</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>1437</v>
+        <v>1536</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>1457</v>
+        <v>1905</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>0.991819</v>
+        <v>0.987968</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B103" s="7" t="s">
         <v>130</v>
       </c>
       <c r="C103" s="8" t="n">
-        <v>350</v>
+        <v>1383</v>
       </c>
       <c r="D103" s="8" t="n">
-        <v>765</v>
+        <v>1586</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>1375</v>
+        <v>1842</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>0.995336</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B104" s="10" t="s">
         <v>131</v>
       </c>
       <c r="C104" s="11" t="n">
-        <v>407</v>
+        <v>971</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>756</v>
+        <v>1141</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>1386</v>
+        <v>1300</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>0.994919</v>
+        <v>0.9931</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>132</v>
       </c>
       <c r="C105" s="8" t="n">
-        <v>1121</v>
+        <v>845</v>
       </c>
       <c r="D105" s="8" t="n">
-        <v>1156</v>
+        <v>986</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>1174</v>
+        <v>1118</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>0.980272</v>
+        <v>0.9887</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B106" s="10" t="s">
         <v>133</v>
       </c>
       <c r="C106" s="11" t="n">
-        <v>1219</v>
+        <v>281</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>1262</v>
+        <v>306</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>1278</v>
+        <v>320</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>0.991184</v>
+        <v>0.9887</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>134</v>
       </c>
       <c r="C107" s="8" t="n">
-        <v>988</v>
+        <v>557</v>
       </c>
       <c r="D107" s="8" t="n">
-        <v>1230</v>
+        <v>666</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>1652</v>
+        <v>779</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>0.994295</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B108" s="10" t="s">
         <v>135</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>1374</v>
+        <v>932</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>2176</v>
+        <v>1080</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>2713</v>
+        <v>1250</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>0.990811</v>
+        <v>0.9896</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>136</v>
       </c>
       <c r="C109" s="8" t="n">
-        <v>390</v>
+        <v>728</v>
       </c>
       <c r="D109" s="8" t="n">
-        <v>601</v>
+        <v>870</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>861</v>
+        <v>1029</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>0.996734</v>
+        <v>0.9879</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B110" s="10" t="s">
         <v>137</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>1388</v>
+        <v>990</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>1435</v>
+        <v>1158</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>1455</v>
+        <v>1321</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>0.988878</v>
+        <v>0.9943</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>138</v>
       </c>
       <c r="C111" s="8" t="n">
-        <v>1161</v>
+        <v>1037</v>
       </c>
       <c r="D111" s="8" t="n">
-        <v>1546</v>
+        <v>1240</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>2902</v>
+        <v>1435</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>0.980928</v>
+        <v>0.9913</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B112" s="10" t="s">
         <v>139</v>
       </c>
       <c r="C112" s="11" t="n">
-        <v>1161</v>
+        <v>395</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>1536</v>
+        <v>429</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>1905</v>
+        <v>450</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>0.987968</v>
+        <v>0.9908</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B113" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B113" s="7" t="s">
-        <v>141</v>
-      </c>
       <c r="C113" s="8" t="n">
-        <v>1383</v>
+        <v>302</v>
       </c>
       <c r="D113" s="8" t="n">
-        <v>1586</v>
+        <v>328</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>1842</v>
+        <v>347</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>0.994</v>
+        <v>0.9806</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B114" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C114" s="11" t="n">
-        <v>971</v>
+        <v>1</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>1141</v>
+        <v>23</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>1300</v>
+        <v>39</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>0.9931</v>
+        <v>0.2382</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C115" s="8" t="n">
-        <v>845</v>
+        <v>182</v>
       </c>
       <c r="D115" s="8" t="n">
-        <v>986</v>
+        <v>194</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>1118</v>
+        <v>201</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>0.9887</v>
+        <v>0.0547</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B116" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>281</v>
+        <v>1019</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>306</v>
+        <v>1210</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>320</v>
+        <v>1410</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>0.9887</v>
+        <v>0.992</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C117" s="8" t="n">
-        <v>557</v>
+        <v>1017</v>
       </c>
       <c r="D117" s="8" t="n">
-        <v>666</v>
+        <v>1194</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>779</v>
+        <v>1365</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>0.987</v>
+        <v>0.9912</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>932</v>
+        <v>284</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>1080</v>
+        <v>314</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>1250</v>
+        <v>321</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>0.9896</v>
+        <v>0.9698</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C119" s="8" t="n">
-        <v>728</v>
+        <v>201</v>
       </c>
       <c r="D119" s="8" t="n">
-        <v>870</v>
+        <v>209</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>1029</v>
+        <v>220</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>0.9879</v>
+        <v>0.9532</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B120" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>1158</v>
+        <v>1230</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>1321</v>
+        <v>1652</v>
       </c>
       <c r="F120" s="12" t="n">
         <v>0.9943</v>
@@ -6576,1881 +6543,1681 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C121" s="8" t="n">
-        <v>1037</v>
+        <v>764</v>
       </c>
       <c r="D121" s="8" t="n">
-        <v>1240</v>
+        <v>913</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>1435</v>
+        <v>1207</v>
       </c>
       <c r="F121" s="9" t="n">
-        <v>0.9913</v>
+        <v>0.9917</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>395</v>
+        <v>648</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>429</v>
+        <v>771</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>450</v>
+        <v>1046</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>0.9908</v>
+        <v>0.9894</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C123" s="8" t="n">
-        <v>302</v>
+        <v>262</v>
       </c>
       <c r="D123" s="8" t="n">
-        <v>328</v>
+        <v>285</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>347</v>
+        <v>311</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>0.9806</v>
+        <v>0.9926</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1</v>
+        <v>504</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>23</v>
+        <v>566</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>39</v>
+        <v>752</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>0.2382</v>
+        <v>0.9841</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C125" s="8" t="n">
-        <v>182</v>
+        <v>720</v>
       </c>
       <c r="D125" s="8" t="n">
-        <v>194</v>
+        <v>867</v>
       </c>
       <c r="E125" s="8" t="n">
-        <v>201</v>
+        <v>1158</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>0.0547</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>1019</v>
+        <v>572</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>1210</v>
+        <v>675</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>1410</v>
+        <v>913</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>0.992</v>
+        <v>0.9901</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C127" s="8" t="n">
-        <v>1017</v>
+        <v>765</v>
       </c>
       <c r="D127" s="8" t="n">
-        <v>1194</v>
+        <v>920</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>1365</v>
+        <v>1252</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>0.9912</v>
+        <v>0.9896</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>284</v>
+        <v>821</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>314</v>
+        <v>986</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>321</v>
+        <v>1334</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>0.9698</v>
+        <v>0.9884</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C129" s="8" t="n">
-        <v>201</v>
+        <v>351</v>
       </c>
       <c r="D129" s="8" t="n">
-        <v>209</v>
+        <v>390</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>220</v>
+        <v>434</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>0.9532</v>
+        <v>0.9884</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>988</v>
+        <v>281</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>1230</v>
+        <v>304</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>1652</v>
+        <v>336</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>0.9943</v>
+        <v>0.9883</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C131" s="8" t="n">
-        <v>764</v>
+        <v>1</v>
       </c>
       <c r="D131" s="8" t="n">
-        <v>913</v>
+        <v>20</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>1207</v>
+        <v>47</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>0.9917</v>
+        <v>0.2185</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>648</v>
+        <v>161</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>771</v>
+        <v>186</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>1046</v>
+        <v>200</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>0.9894</v>
+        <v>0.0528</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C133" s="8" t="n">
-        <v>262</v>
+        <v>798</v>
       </c>
       <c r="D133" s="8" t="n">
-        <v>285</v>
+        <v>954</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>311</v>
+        <v>1283</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>0.9926</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>504</v>
+        <v>786</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>566</v>
+        <v>930</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>752</v>
+        <v>1266</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>0.9841</v>
+        <v>0.9916</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C135" s="8" t="n">
-        <v>720</v>
+        <v>264</v>
       </c>
       <c r="D135" s="8" t="n">
-        <v>867</v>
+        <v>295</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>1158</v>
+        <v>320</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>0.99</v>
+        <v>0.9584</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>572</v>
+        <v>181</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>675</v>
+        <v>203</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>913</v>
+        <v>220</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>0.9901</v>
+        <v>0.9415</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C137" s="8" t="n">
-        <v>765</v>
+        <v>1324</v>
       </c>
       <c r="D137" s="8" t="n">
-        <v>920</v>
+        <v>2352</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>1252</v>
+        <v>3504</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>0.9896</v>
+        <v>0.9942</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>821</v>
+        <v>1141</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>986</v>
+        <v>1953</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>1334</v>
+        <v>2938</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>0.9884</v>
+        <v>0.9932</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C139" s="8" t="n">
-        <v>351</v>
+        <v>981</v>
       </c>
       <c r="D139" s="8" t="n">
-        <v>390</v>
+        <v>1676</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>434</v>
+        <v>2514</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>0.9884</v>
+        <v>0.992</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>281</v>
+        <v>760</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>304</v>
+        <v>1016</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>336</v>
+        <v>1665</v>
       </c>
       <c r="F140" s="12" t="n">
-        <v>0.9883</v>
+        <v>0.9801</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C141" s="8" t="n">
-        <v>1</v>
+        <v>785</v>
       </c>
       <c r="D141" s="8" t="n">
-        <v>20</v>
+        <v>1099</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>47</v>
+        <v>1682</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>0.2185</v>
+        <v>0.9919</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>161</v>
+        <v>1081</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>186</v>
+        <v>1847</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>200</v>
+        <v>2776</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>0.0528</v>
+        <v>0.9937</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C143" s="8" t="n">
-        <v>798</v>
+        <v>863</v>
       </c>
       <c r="D143" s="8" t="n">
-        <v>954</v>
+        <v>1475</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>1283</v>
+        <v>2226</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>0.991</v>
+        <v>0.9926</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B144" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>786</v>
+        <v>1158</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>930</v>
+        <v>1980</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>1266</v>
+        <v>2982</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>0.9916</v>
+        <v>0.9935</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C145" s="8" t="n">
-        <v>264</v>
+        <v>1196</v>
       </c>
       <c r="D145" s="8" t="n">
-        <v>295</v>
+        <v>2043</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>320</v>
+        <v>3077</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>0.9584</v>
+        <v>0.9942</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>181</v>
+        <v>874</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>203</v>
+        <v>1245</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>220</v>
+        <v>2008</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>0.9415</v>
+        <v>0.9772</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C147" s="8" t="n">
-        <v>1324</v>
+        <v>774</v>
       </c>
       <c r="D147" s="8" t="n">
-        <v>2352</v>
+        <v>1047</v>
       </c>
       <c r="E147" s="8" t="n">
-        <v>3504</v>
+        <v>1705</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>0.9942</v>
+        <v>0.9768</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C148" s="11" t="n">
-        <v>1141</v>
+        <v>11</v>
       </c>
       <c r="D148" s="11" t="n">
-        <v>1953</v>
+        <v>12</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>2938</v>
+        <v>23</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>0.9932</v>
+        <v>0.8329</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C149" s="8" t="n">
-        <v>981</v>
+        <v>1</v>
       </c>
       <c r="D149" s="8" t="n">
-        <v>1676</v>
+        <v>1</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>2514</v>
+        <v>14</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>0.992</v>
+        <v>0.0288</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C150" s="11" t="n">
-        <v>760</v>
+        <v>1158</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>1016</v>
+        <v>1980</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>1665</v>
+        <v>2982</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>0.9801</v>
+        <v>0.9935</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C151" s="8" t="n">
-        <v>785</v>
+        <v>1141</v>
       </c>
       <c r="D151" s="8" t="n">
-        <v>1099</v>
+        <v>1953</v>
       </c>
       <c r="E151" s="8" t="n">
-        <v>1682</v>
+        <v>2938</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>0.9919</v>
+        <v>0.9932</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>1081</v>
+        <v>774</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>1847</v>
+        <v>1047</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>2776</v>
+        <v>1700</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>0.9937</v>
+        <v>0.9768</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C153" s="8" t="n">
-        <v>863</v>
+        <v>674</v>
       </c>
       <c r="D153" s="8" t="n">
-        <v>1475</v>
+        <v>848</v>
       </c>
       <c r="E153" s="8" t="n">
-        <v>2226</v>
+        <v>1229</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>0.9926</v>
+        <v>0.9446</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>1158</v>
+        <v>1374</v>
       </c>
       <c r="D154" s="11" t="n">
-        <v>1980</v>
+        <v>2176</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>2982</v>
+        <v>2713</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>0.9935</v>
+        <v>0.9908</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C155" s="8" t="n">
-        <v>1196</v>
+        <v>1182</v>
       </c>
       <c r="D155" s="8" t="n">
-        <v>2043</v>
+        <v>1814</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>3077</v>
+        <v>2272</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>0.9942</v>
+        <v>0.9911</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B156" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>874</v>
+        <v>1014</v>
       </c>
       <c r="D156" s="11" t="n">
-        <v>1245</v>
+        <v>1560</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>2008</v>
+        <v>1952</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>0.9772</v>
+        <v>0.9884</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C157" s="8" t="n">
         <v>774</v>
       </c>
       <c r="D157" s="8" t="n">
-        <v>1047</v>
+        <v>974</v>
       </c>
       <c r="E157" s="8" t="n">
-        <v>1705</v>
+        <v>1016</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>0.9768</v>
+        <v>0.9649</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>11</v>
+        <v>804</v>
       </c>
       <c r="D158" s="11" t="n">
-        <v>12</v>
+        <v>1057</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>23</v>
+        <v>1397</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>0.8329</v>
+        <v>0.9858</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C159" s="8" t="n">
-        <v>1</v>
+        <v>1118</v>
       </c>
       <c r="D159" s="8" t="n">
-        <v>1</v>
+        <v>1716</v>
       </c>
       <c r="E159" s="8" t="n">
-        <v>14</v>
+        <v>2149</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>0.0288</v>
+        <v>0.9887</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B160" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>1158</v>
+        <v>893</v>
       </c>
       <c r="D160" s="11" t="n">
-        <v>1980</v>
+        <v>1374</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>2982</v>
+        <v>1721</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>0.9935</v>
+        <v>0.9886</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C161" s="8" t="n">
-        <v>1141</v>
+        <v>1199</v>
       </c>
       <c r="D161" s="8" t="n">
-        <v>1953</v>
+        <v>1843</v>
       </c>
       <c r="E161" s="8" t="n">
-        <v>2938</v>
+        <v>2302</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>0.9932</v>
+        <v>0.9897</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B162" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>774</v>
+        <v>1237</v>
       </c>
       <c r="D162" s="11" t="n">
-        <v>1047</v>
+        <v>1900</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>1700</v>
+        <v>2384</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>0.9768</v>
+        <v>0.9911</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C163" s="8" t="n">
-        <v>674</v>
+        <v>894</v>
       </c>
       <c r="D163" s="8" t="n">
-        <v>848</v>
+        <v>1195</v>
       </c>
       <c r="E163" s="8" t="n">
-        <v>1229</v>
+        <v>1259</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>0.9446</v>
+        <v>0.9735</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B164" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C164" s="11" t="n">
-        <v>1374</v>
+        <v>796</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>2176</v>
+        <v>1021</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>2713</v>
+        <v>1076</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>0.9908</v>
+        <v>0.9681</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C165" s="8" t="n">
-        <v>1182</v>
+        <v>11</v>
       </c>
       <c r="D165" s="8" t="n">
-        <v>1814</v>
+        <v>12</v>
       </c>
       <c r="E165" s="8" t="n">
-        <v>2272</v>
+        <v>22</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>0.9911</v>
+        <v>0.8314</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B166" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C166" s="11" t="n">
-        <v>1014</v>
+        <v>1</v>
       </c>
       <c r="D166" s="11" t="n">
-        <v>1560</v>
+        <v>1</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>1952</v>
+        <v>13</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>0.9884</v>
+        <v>0.0338</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C167" s="8" t="n">
-        <v>774</v>
+        <v>1199</v>
       </c>
       <c r="D167" s="8" t="n">
-        <v>974</v>
+        <v>1843</v>
       </c>
       <c r="E167" s="8" t="n">
-        <v>1016</v>
+        <v>2302</v>
       </c>
       <c r="F167" s="9" t="n">
-        <v>0.9649</v>
+        <v>0.9897</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B168" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C168" s="11" t="n">
-        <v>804</v>
+        <v>1182</v>
       </c>
       <c r="D168" s="11" t="n">
-        <v>1057</v>
+        <v>1814</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>1397</v>
+        <v>2272</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>0.9858</v>
+        <v>0.9911</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C169" s="8" t="n">
-        <v>1118</v>
+        <v>796</v>
       </c>
       <c r="D169" s="8" t="n">
-        <v>1716</v>
+        <v>1021</v>
       </c>
       <c r="E169" s="8" t="n">
-        <v>2149</v>
+        <v>1075</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>0.9887</v>
+        <v>0.9681</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C170" s="11" t="n">
-        <v>893</v>
+        <v>674</v>
       </c>
       <c r="D170" s="11" t="n">
-        <v>1374</v>
+        <v>806</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>1721</v>
+        <v>855</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>0.9886</v>
+        <v>0.9594</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C171" s="8" t="n">
-        <v>1199</v>
+        <v>2446</v>
       </c>
       <c r="D171" s="8" t="n">
-        <v>1843</v>
+        <v>2536</v>
       </c>
       <c r="E171" s="8" t="n">
-        <v>2302</v>
+        <v>2566</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>0.9897</v>
+        <v>0.9972</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B172" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>1237</v>
+        <v>1931</v>
       </c>
       <c r="D172" s="11" t="n">
-        <v>1900</v>
+        <v>2016</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>2384</v>
+        <v>2046</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>0.9911</v>
+        <v>0.9975</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C173" s="8" t="n">
-        <v>894</v>
+        <v>1651</v>
       </c>
       <c r="D173" s="8" t="n">
-        <v>1195</v>
+        <v>1741</v>
       </c>
       <c r="E173" s="8" t="n">
-        <v>1259</v>
+        <v>1771</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>0.9735</v>
+        <v>0.9974</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>796</v>
+        <v>991</v>
       </c>
       <c r="D174" s="11" t="n">
-        <v>1021</v>
+        <v>1096</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>1076</v>
+        <v>1136</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>0.9681</v>
+        <v>0.9937</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C175" s="8" t="n">
-        <v>11</v>
+        <v>1061</v>
       </c>
       <c r="D175" s="8" t="n">
-        <v>12</v>
+        <v>1181</v>
       </c>
       <c r="E175" s="8" t="n">
-        <v>22</v>
+        <v>1211</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>0.8314</v>
+        <v>0.996</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B176" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>1</v>
+        <v>1831</v>
       </c>
       <c r="D176" s="11" t="n">
-        <v>1</v>
+        <v>1916</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>13</v>
+        <v>1941</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>0.0338</v>
+        <v>0.9971</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C177" s="8" t="n">
-        <v>1199</v>
+        <v>1481</v>
       </c>
       <c r="D177" s="8" t="n">
-        <v>1843</v>
+        <v>1551</v>
       </c>
       <c r="E177" s="8" t="n">
-        <v>2302</v>
+        <v>1591</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>0.9897</v>
+        <v>0.9971</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>1182</v>
+        <v>1961</v>
       </c>
       <c r="D178" s="11" t="n">
-        <v>1814</v>
+        <v>2046</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>2272</v>
+        <v>2081</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>0.9911</v>
+        <v>0.9976</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C179" s="8" t="n">
-        <v>796</v>
+        <v>2061</v>
       </c>
       <c r="D179" s="8" t="n">
-        <v>1021</v>
+        <v>2141</v>
       </c>
       <c r="E179" s="8" t="n">
-        <v>1075</v>
+        <v>2176</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>0.9681</v>
+        <v>0.9979</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B180" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>674</v>
+        <v>1286</v>
       </c>
       <c r="D180" s="11" t="n">
-        <v>806</v>
+        <v>1351</v>
       </c>
       <c r="E180" s="11" t="n">
-        <v>855</v>
+        <v>1391</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>0.9594</v>
+        <v>0.9906</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C181" s="8" t="n">
-        <v>2446</v>
+        <v>1101</v>
       </c>
       <c r="D181" s="8" t="n">
-        <v>2536</v>
+        <v>1191</v>
       </c>
       <c r="E181" s="8" t="n">
-        <v>2566</v>
+        <v>1241</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>0.9972</v>
+        <v>0.9903</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B182" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C182" s="11" t="n">
-        <v>1931</v>
+        <v>2</v>
       </c>
       <c r="D182" s="11" t="n">
-        <v>2016</v>
+        <v>96</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>2046</v>
+        <v>201</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>0.9975</v>
+        <v>0.1687</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C183" s="8" t="n">
-        <v>1651</v>
+        <v>44</v>
       </c>
       <c r="D183" s="8" t="n">
-        <v>1741</v>
+        <v>216</v>
       </c>
       <c r="E183" s="8" t="n">
-        <v>1771</v>
+        <v>331</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>0.9974</v>
+        <v>0.0591</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>991</v>
+        <v>2016</v>
       </c>
       <c r="D184" s="11" t="n">
-        <v>1096</v>
+        <v>2086</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>1136</v>
+        <v>2116</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>0.9937</v>
+        <v>0.9975</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C185" s="8" t="n">
-        <v>1061</v>
+        <v>1966</v>
       </c>
       <c r="D185" s="8" t="n">
-        <v>1181</v>
+        <v>2050</v>
       </c>
       <c r="E185" s="8" t="n">
-        <v>1211</v>
+        <v>2076</v>
       </c>
       <c r="F185" s="9" t="n">
-        <v>0.996</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>1831</v>
+        <v>706</v>
       </c>
       <c r="D186" s="11" t="n">
-        <v>1916</v>
+        <v>936</v>
       </c>
       <c r="E186" s="11" t="n">
-        <v>1941</v>
+        <v>1026</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>0.9971</v>
+        <v>0.9666</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C187" s="8" t="n">
-        <v>1481</v>
+        <v>411</v>
       </c>
       <c r="D187" s="8" t="n">
-        <v>1551</v>
+        <v>746</v>
       </c>
       <c r="E187" s="8" t="n">
-        <v>1591</v>
+        <v>851</v>
       </c>
       <c r="F187" s="9" t="n">
-        <v>0.9971</v>
+        <v>0.9535</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>1961</v>
+        <v>1626</v>
       </c>
       <c r="D188" s="11" t="n">
-        <v>2046</v>
+        <v>1821</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>2081</v>
+        <v>1881</v>
       </c>
       <c r="F188" s="12" t="n">
-        <v>0.9976</v>
+        <v>0.9956</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C189" s="8" t="n">
-        <v>2061</v>
+        <v>1281</v>
       </c>
       <c r="D189" s="8" t="n">
-        <v>2141</v>
+        <v>1481</v>
       </c>
       <c r="E189" s="8" t="n">
-        <v>2176</v>
+        <v>1536</v>
       </c>
       <c r="F189" s="9" t="n">
-        <v>0.9979</v>
+        <v>0.9944</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>1286</v>
+        <v>1051</v>
       </c>
       <c r="D190" s="11" t="n">
-        <v>1351</v>
+        <v>1276</v>
       </c>
       <c r="E190" s="11" t="n">
-        <v>1391</v>
+        <v>1316</v>
       </c>
       <c r="F190" s="12" t="n">
-        <v>0.9906</v>
+        <v>0.9946</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C191" s="8" t="n">
-        <v>1101</v>
+        <v>796</v>
       </c>
       <c r="D191" s="8" t="n">
-        <v>1191</v>
+        <v>911</v>
       </c>
       <c r="E191" s="8" t="n">
-        <v>1241</v>
+        <v>986</v>
       </c>
       <c r="F191" s="9" t="n">
-        <v>0.9903</v>
+        <v>0.972</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C192" s="11" t="n">
-        <v>2</v>
+        <v>661</v>
       </c>
       <c r="D192" s="11" t="n">
-        <v>96</v>
+        <v>901</v>
       </c>
       <c r="E192" s="11" t="n">
-        <v>201</v>
+        <v>936</v>
       </c>
       <c r="F192" s="12" t="n">
-        <v>0.1687</v>
+        <v>0.9932</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C193" s="8" t="n">
-        <v>44</v>
+        <v>1226</v>
       </c>
       <c r="D193" s="8" t="n">
-        <v>216</v>
+        <v>1386</v>
       </c>
       <c r="E193" s="8" t="n">
-        <v>331</v>
+        <v>1436</v>
       </c>
       <c r="F193" s="9" t="n">
-        <v>0.0591</v>
+        <v>0.9958</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B194" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>2016</v>
+        <v>911</v>
       </c>
       <c r="D194" s="11" t="n">
-        <v>2086</v>
+        <v>1111</v>
       </c>
       <c r="E194" s="11" t="n">
-        <v>2116</v>
+        <v>1171</v>
       </c>
       <c r="F194" s="12" t="n">
-        <v>0.9975</v>
+        <v>0.9935</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C195" s="8" t="n">
-        <v>1966</v>
+        <v>1336</v>
       </c>
       <c r="D195" s="8" t="n">
-        <v>2050</v>
+        <v>1491</v>
       </c>
       <c r="E195" s="8" t="n">
-        <v>2076</v>
+        <v>1551</v>
       </c>
       <c r="F195" s="9" t="n">
-        <v>0.997</v>
+        <v>0.9952</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B196" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C196" s="11" t="n">
-        <v>706</v>
+        <v>1361</v>
       </c>
       <c r="D196" s="11" t="n">
-        <v>936</v>
+        <v>1566</v>
       </c>
       <c r="E196" s="11" t="n">
-        <v>1026</v>
+        <v>1616</v>
       </c>
       <c r="F196" s="12" t="n">
-        <v>0.9666</v>
+        <v>0.9939</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C197" s="8" t="n">
-        <v>411</v>
+        <v>946</v>
       </c>
       <c r="D197" s="8" t="n">
-        <v>746</v>
+        <v>1100</v>
       </c>
       <c r="E197" s="8" t="n">
-        <v>851</v>
+        <v>1186</v>
       </c>
       <c r="F197" s="9" t="n">
-        <v>0.9535</v>
+        <v>0.9802</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B198" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>1626</v>
+        <v>841</v>
       </c>
       <c r="D198" s="11" t="n">
-        <v>1821</v>
+        <v>981</v>
       </c>
       <c r="E198" s="11" t="n">
-        <v>1881</v>
+        <v>1061</v>
       </c>
       <c r="F198" s="12" t="n">
-        <v>0.9956</v>
+        <v>0.9606</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C199" s="8" t="n">
-        <v>1281</v>
+        <v>1</v>
       </c>
       <c r="D199" s="8" t="n">
-        <v>1481</v>
+        <v>71</v>
       </c>
       <c r="E199" s="8" t="n">
-        <v>1536</v>
+        <v>181</v>
       </c>
       <c r="F199" s="9" t="n">
-        <v>0.9944</v>
+        <v>0.1491</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B200" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C200" s="11" t="n">
-        <v>1051</v>
+        <v>199</v>
       </c>
       <c r="D200" s="11" t="n">
-        <v>1276</v>
+        <v>281</v>
       </c>
       <c r="E200" s="11" t="n">
-        <v>1316</v>
+        <v>386</v>
       </c>
       <c r="F200" s="12" t="n">
-        <v>0.9946</v>
+        <v>0.0405</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C201" s="8" t="n">
-        <v>796</v>
+        <v>1316</v>
       </c>
       <c r="D201" s="8" t="n">
-        <v>911</v>
+        <v>1521</v>
       </c>
       <c r="E201" s="8" t="n">
-        <v>986</v>
+        <v>1561</v>
       </c>
       <c r="F201" s="9" t="n">
-        <v>0.972</v>
+        <v>0.9955</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B202" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>661</v>
+        <v>1286</v>
       </c>
       <c r="D202" s="11" t="n">
-        <v>901</v>
+        <v>1496</v>
       </c>
       <c r="E202" s="11" t="n">
-        <v>936</v>
+        <v>1551</v>
       </c>
       <c r="F202" s="12" t="n">
-        <v>0.9932</v>
+        <v>0.9957</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C203" s="8" t="n">
-        <v>1226</v>
+        <v>661</v>
       </c>
       <c r="D203" s="8" t="n">
-        <v>1386</v>
+        <v>921</v>
       </c>
       <c r="E203" s="8" t="n">
-        <v>1436</v>
+        <v>996</v>
       </c>
       <c r="F203" s="9" t="n">
-        <v>0.9958</v>
+        <v>0.9606</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="10" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B204" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C204" s="11" t="n">
-        <v>911</v>
+        <v>346</v>
       </c>
       <c r="D204" s="11" t="n">
-        <v>1111</v>
+        <v>746</v>
       </c>
       <c r="E204" s="11" t="n">
-        <v>1171</v>
+        <v>846</v>
       </c>
       <c r="F204" s="12" t="n">
-        <v>0.9935</v>
-      </c>
-    </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="B205" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="C205" s="8" t="n">
-        <v>1336</v>
-      </c>
-      <c r="D205" s="8" t="n">
-        <v>1491</v>
-      </c>
-      <c r="E205" s="8" t="n">
-        <v>1551</v>
-      </c>
-      <c r="F205" s="9" t="n">
-        <v>0.9952</v>
-      </c>
-    </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B206" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="C206" s="11" t="n">
-        <v>1361</v>
-      </c>
-      <c r="D206" s="11" t="n">
-        <v>1566</v>
-      </c>
-      <c r="E206" s="11" t="n">
-        <v>1616</v>
-      </c>
-      <c r="F206" s="12" t="n">
-        <v>0.9939</v>
-      </c>
-    </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="B207" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="C207" s="8" t="n">
-        <v>946</v>
-      </c>
-      <c r="D207" s="8" t="n">
-        <v>1100</v>
-      </c>
-      <c r="E207" s="8" t="n">
-        <v>1186</v>
-      </c>
-      <c r="F207" s="9" t="n">
-        <v>0.9802</v>
-      </c>
-    </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B208" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="C208" s="11" t="n">
-        <v>841</v>
-      </c>
-      <c r="D208" s="11" t="n">
-        <v>981</v>
-      </c>
-      <c r="E208" s="11" t="n">
-        <v>1061</v>
-      </c>
-      <c r="F208" s="12" t="n">
-        <v>0.9606</v>
-      </c>
-    </row>
-    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="B209" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="C209" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D209" s="8" t="n">
-        <v>71</v>
-      </c>
-      <c r="E209" s="8" t="n">
-        <v>181</v>
-      </c>
-      <c r="F209" s="9" t="n">
-        <v>0.1491</v>
-      </c>
-    </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B210" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="C210" s="11" t="n">
-        <v>199</v>
-      </c>
-      <c r="D210" s="11" t="n">
-        <v>281</v>
-      </c>
-      <c r="E210" s="11" t="n">
-        <v>386</v>
-      </c>
-      <c r="F210" s="12" t="n">
-        <v>0.0405</v>
-      </c>
-    </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="B211" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C211" s="8" t="n">
-        <v>1316</v>
-      </c>
-      <c r="D211" s="8" t="n">
-        <v>1521</v>
-      </c>
-      <c r="E211" s="8" t="n">
-        <v>1561</v>
-      </c>
-      <c r="F211" s="9" t="n">
-        <v>0.9955</v>
-      </c>
-    </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B212" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="C212" s="11" t="n">
-        <v>1286</v>
-      </c>
-      <c r="D212" s="11" t="n">
-        <v>1496</v>
-      </c>
-      <c r="E212" s="11" t="n">
-        <v>1551</v>
-      </c>
-      <c r="F212" s="12" t="n">
-        <v>0.9957</v>
-      </c>
-    </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="B213" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="C213" s="8" t="n">
-        <v>661</v>
-      </c>
-      <c r="D213" s="8" t="n">
-        <v>921</v>
-      </c>
-      <c r="E213" s="8" t="n">
-        <v>996</v>
-      </c>
-      <c r="F213" s="9" t="n">
-        <v>0.9606</v>
-      </c>
-    </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B214" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="C214" s="11" t="n">
-        <v>346</v>
-      </c>
-      <c r="D214" s="11" t="n">
-        <v>746</v>
-      </c>
-      <c r="E214" s="11" t="n">
-        <v>846</v>
-      </c>
-      <c r="F214" s="12" t="n">
         <v>0.9488</v>
       </c>
     </row>
@@ -8483,23 +8250,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
@@ -8514,21 +8281,21 @@
         <v>21</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>34</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="D5" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B5,'All runs'!$B:$B,0))</f>
@@ -8557,13 +8324,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>31</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B6,'All runs'!$B:$B,0))</f>
@@ -8592,13 +8359,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="D7" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B7,'All runs'!$B:$B,0))</f>
@@ -8627,13 +8394,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>35</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B8,'All runs'!$B:$B,0))</f>
@@ -8662,13 +8429,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="D9" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B9,'All runs'!$B:$B,0))</f>
@@ -8697,13 +8464,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>40</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B10,'All runs'!$B:$B,0))</f>
@@ -8732,13 +8499,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="D11" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B11,'All runs'!$B:$B,0))</f>
@@ -8767,13 +8534,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>39</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="D12" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B12,'All runs'!$B:$B,0))</f>
@@ -8802,13 +8569,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D13" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B13,'All runs'!$B:$B,0))</f>
@@ -8837,13 +8604,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="B14" s="18" t="s">
         <v>38</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="D14" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B14,'All runs'!$B:$B,0))</f>
@@ -8872,13 +8639,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="B15" s="23" t="s">
         <v>57</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="D15" s="24" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B15,'All runs'!$B:$B,0))</f>
@@ -8933,67 +8700,67 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>1312</v>
@@ -9027,24 +8794,24 @@
         <v>0.0114329268292683</v>
       </c>
       <c r="M5" s="30" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="F6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B6,'All runs'!$B:$B,0))</f>
@@ -9075,12 +8842,12 @@
         <v/>
       </c>
       <c r="M6" s="33" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>27</v>
@@ -9123,24 +8890,24 @@
         <v>0.00273722627737226</v>
       </c>
       <c r="M7" s="30" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B8,'All runs'!$B:$B,0))</f>
@@ -9171,21 +8938,21 @@
         <v/>
       </c>
       <c r="M8" s="33" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>4312</v>
@@ -9219,12 +8986,12 @@
         <v>0.720083487940631</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>23</v>
@@ -9267,12 +9034,12 @@
         <v>0.719545454545455</v>
       </c>
       <c r="M10" s="33" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="34" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -9304,23 +9071,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
@@ -9335,15 +9102,15 @@
         <v>21</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>28</v>
@@ -9365,15 +9132,15 @@
         <v>0.996585</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>36</v>
@@ -9395,15 +9162,15 @@
         <v>0.985844</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>40</v>
@@ -9425,15 +9192,15 @@
         <v>0.992063</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>25</v>
@@ -9455,15 +9222,15 @@
         <v>0.950353</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>33</v>
@@ -9485,15 +9252,15 @@
         <v>0.992968</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="C10" s="23" t="s">
         <v>39</v>
@@ -9515,15 +9282,15 @@
         <v>0.993617</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>23</v>
@@ -9545,15 +9312,15 @@
         <v>0.997831</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>30</v>
@@ -9575,15 +9342,15 @@
         <v>0.994936</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="C13" s="23" t="s">
         <v>38</v>
@@ -9605,31 +9372,31 @@
         <v>0.996207</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D16" s="21" t="n">
         <f aca="false">D7/D6-1</f>
@@ -9650,7 +9417,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="D17" s="16" t="n">
         <f aca="false">D10/D9-1</f>
@@ -9671,7 +9438,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="D18" s="21" t="n">
         <f aca="false">D13/D12-1</f>
@@ -9719,23 +9486,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
@@ -9750,18 +9517,18 @@
         <v>21</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>42</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="D5" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B5,'All runs'!$B:$B,0))</f>
@@ -9786,13 +9553,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>43</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B6,'All runs'!$B:$B,0))</f>
@@ -9817,13 +9584,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>44</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="D7" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B7,'All runs'!$B:$B,0))</f>
@@ -9848,13 +9615,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>45</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B8,'All runs'!$B:$B,0))</f>
@@ -9879,13 +9646,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>46</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="D9" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B9,'All runs'!$B:$B,0))</f>
@@ -9910,13 +9677,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B10,'All runs'!$B:$B,0))</f>
@@ -9941,13 +9708,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="D11" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B11,'All runs'!$B:$B,0))</f>
@@ -9972,13 +9739,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>47</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="D12" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B12,'All runs'!$B:$B,0))</f>
@@ -10003,13 +9770,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>50</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="D13" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B13,'All runs'!$B:$B,0))</f>
@@ -10034,13 +9801,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="B14" s="18" t="s">
         <v>51</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="D14" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B14,'All runs'!$B:$B,0))</f>
@@ -10065,13 +9832,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>54</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="D15" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B15,'All runs'!$B:$B,0))</f>
@@ -10096,13 +9863,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="B16" s="18" t="s">
         <v>55</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="D16" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B16,'All runs'!$B:$B,0))</f>
@@ -10127,13 +9894,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>52</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="D17" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B17,'All runs'!$B:$B,0))</f>
@@ -10158,13 +9925,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="B18" s="18" t="s">
         <v>53</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="D18" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B18,'All runs'!$B:$B,0))</f>
@@ -10189,13 +9956,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>56</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="D19" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B19,'All runs'!$B:$B,0))</f>
@@ -10220,13 +9987,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>59</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="D20" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B20,'All runs'!$B:$B,0))</f>
@@ -10251,13 +10018,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="B21" s="23" t="s">
         <v>57</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="D21" s="24" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B21,'All runs'!$B:$B,0))</f>
@@ -10282,13 +10049,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="B22" s="18" t="s">
         <v>58</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="D22" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($B22,'All runs'!$B:$B,0))</f>
@@ -10340,20 +10107,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>18</v>
@@ -10368,7 +10135,7 @@
         <v>21</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10376,7 +10143,7 @@
         <v>56</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="C5" s="24" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A5,'All runs'!$B:$B,0))</f>
@@ -10404,7 +10171,7 @@
         <v>63</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="C6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A6,'All runs'!$B:$B,0))</f>
@@ -10432,7 +10199,7 @@
         <v>64</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="C7" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A7,'All runs'!$B:$B,0))</f>
@@ -10460,7 +10227,7 @@
         <v>65</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="C8" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A8,'All runs'!$B:$B,0))</f>
@@ -10488,7 +10255,7 @@
         <v>66</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="C9" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A9,'All runs'!$B:$B,0))</f>
@@ -10516,7 +10283,7 @@
         <v>67</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="C10" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A10,'All runs'!$B:$B,0))</f>
@@ -10569,23 +10336,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
@@ -10600,7 +10367,7 @@
         <v>21</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10608,10 +10375,10 @@
         <v>69</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="D5" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A5,'All runs'!$B:$B,0))</f>
@@ -10639,10 +10406,10 @@
         <v>70</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A6,'All runs'!$B:$B,0))</f>
@@ -10670,10 +10437,10 @@
         <v>71</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="D7" s="24" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A7,'All runs'!$B:$B,0))</f>
@@ -10701,10 +10468,10 @@
         <v>72</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A8,'All runs'!$B:$B,0))</f>
@@ -10732,10 +10499,10 @@
         <v>73</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="D9" s="14" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A9,'All runs'!$B:$B,0))</f>
@@ -10763,10 +10530,10 @@
         <v>74</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="D10" s="24" t="n">
         <f aca="false">INDEX('All runs'!$C:$C,MATCH($A10,'All runs'!$B:$B,0))</f>
@@ -10818,23 +10585,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
@@ -10851,10 +10618,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>77</v>
@@ -10878,10 +10645,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>76</v>
@@ -10905,10 +10672,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>82</v>
@@ -10932,10 +10699,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>80</v>
@@ -10959,10 +10726,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>83</v>
@@ -10986,10 +10753,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>78</v>
@@ -11013,10 +10780,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>79</v>
@@ -11040,10 +10807,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>81</v>
@@ -11067,10 +10834,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>85</v>
@@ -11094,10 +10861,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C14" s="18" t="s">
         <v>84</v>
@@ -11121,10 +10888,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>90</v>
@@ -11148,10 +10915,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="C16" s="18" t="s">
         <v>88</v>
@@ -11175,10 +10942,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>91</v>
@@ -11202,10 +10969,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="C18" s="18" t="s">
         <v>86</v>
@@ -11229,10 +10996,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>87</v>
@@ -11256,10 +11023,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>89</v>
@@ -11283,10 +11050,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>93</v>
@@ -11310,10 +11077,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C22" s="18" t="s">
         <v>92</v>
@@ -11337,10 +11104,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>98</v>
@@ -11364,10 +11131,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="18" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>96</v>
@@ -11391,10 +11158,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>99</v>
@@ -11418,10 +11185,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="C26" s="18" t="s">
         <v>94</v>
@@ -11445,10 +11212,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>95</v>
@@ -11472,10 +11239,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="C28" s="18" t="s">
         <v>97</v>
@@ -11499,10 +11266,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>109</v>
@@ -11526,10 +11293,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C30" s="18" t="s">
         <v>108</v>
@@ -11553,10 +11320,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="B31" s="37" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="C31" s="13" t="s">
         <v>114</v>
@@ -11580,10 +11347,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="18" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="C32" s="18" t="s">
         <v>112</v>
@@ -11607,10 +11374,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="B33" s="37" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>115</v>
@@ -11634,10 +11401,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="18" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="C34" s="18" t="s">
         <v>110</v>
@@ -11661,10 +11428,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>111</v>
@@ -11688,10 +11455,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="18" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="C36" s="18" t="s">
         <v>113</v>
@@ -11715,10 +11482,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>101</v>
@@ -11742,10 +11509,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="18" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C38" s="18" t="s">
         <v>100</v>
@@ -11769,10 +11536,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>106</v>
@@ -11796,10 +11563,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="C40" s="18" t="s">
         <v>104</v>
@@ -11823,10 +11590,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="C41" s="13" t="s">
         <v>107</v>
@@ -11850,10 +11617,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="18" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="C42" s="18" t="s">
         <v>102</v>
@@ -11877,10 +11644,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="C43" s="13" t="s">
         <v>103</v>
@@ -11904,10 +11671,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="18" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="C44" s="18" t="s">
         <v>105</v>
@@ -11931,35 +11698,35 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="D47" s="39" t="n">
         <f aca="false">AVERAGE(D5:D12)</f>
@@ -11992,7 +11759,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="18" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="D48" s="42" t="n">
         <f aca="false">AVERAGE(D13:D20)</f>
@@ -12025,7 +11792,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="23" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="D49" s="45" t="n">
         <f aca="false">AVERAGE(D21:D28)</f>
@@ -12058,7 +11825,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="18" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="D50" s="42" t="n">
         <f aca="false">AVERAGE(D29:D36)</f>
@@ -12091,7 +11858,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="13" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="D51" s="39" t="n">
         <f aca="false">AVERAGE(D37:D44)</f>

--- a/thesis-final/Results_Comparison.xlsx
+++ b/thesis-final/Results_Comparison.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="+0%;-0%"/>
     <numFmt numFmtId="165" formatCode="+0.0%;-0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,6 +60,12 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="005F5E5A"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -132,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -153,7 +159,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -168,7 +174,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -180,27 +186,28 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -714,17 +721,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -790,7 +797,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="31" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>LEACH</t>
@@ -820,7 +827,7 @@
         <v>0.7686189443239335</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="31" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>HEED</t>
@@ -850,7 +857,7 @@
         <v>2.717325227963526</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="31" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>PEGASIS</t>
@@ -880,7 +887,7 @@
         <v>0.8474320241691844</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="31" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
           <t>SH-LEACH+</t>
@@ -910,7 +917,7 @@
         <v>0.6527027027027028</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="31" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>H-LEACH+</t>
@@ -940,7 +947,7 @@
         <v>0.6605566870332655</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="31" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
           <t>EECH-HEED+</t>
@@ -970,7 +977,7 @@
         <v>0.8322097378277153</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="31" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
           <t>v8 (main)</t>
@@ -1002,7 +1009,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="31" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
           <t>v8-Chain (far BS)</t>
@@ -1037,7 +1044,7 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2. The three hybrids — before and after our fix (FND)</t>
+          <t>2. Classic protocols — paper → our code → unified environment → far BS</t>
         </is>
       </c>
     </row>
@@ -1049,736 +1056,1543 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Problem we found</t>
+          <t>Version</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Paper settings</t>
+          <t>FND</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Same env. (as published)</t>
+          <t>HND</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>After our fix</t>
+          <t>LND</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Change</t>
+          <t>PDR</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Far BS after fix</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
+          <t>Change (FND*)</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>What changed and why</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
+          <t>LEACH</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Paper (published)</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>932</v>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Table 2 of the paper (0.5 J)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="31" customHeight="1">
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Our ORIGINAL code (paper settings)</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>1152</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>1327</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0.9862109999999999</v>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>+11.1% vs paper</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Paper settings: 50 × 50 m, BS far at (25, −100), one amplifier (100 pJ). Close to the paper → our code is correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44.5" customHeight="1">
+      <c r="A20" s="10" t="inlineStr"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Our EDITED code (unified environment)</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>1383</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>1586</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>1842</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0.9939519999999999</v>
+      </c>
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>+33.6% vs ORIGINAL</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Same algorithm, unified environment: amplifier 10× cheaper (two-slope, 10 pJ) and BS at the centre (≤ 70 m instead of 100–150 m); set-up messages are now charged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="31" customHeight="1">
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Far BS (50, −100)</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>988</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>1230</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>1652</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0.994295</v>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>-28.6% vs centre</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>BS at (50, −100): every CH sends far (cost d⁴).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>HEED</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Paper (published)</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>graphs only</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="31" customHeight="1">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Our ORIGINAL code (paper settings)</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>734</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>1384</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>2259</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>0.997956</v>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Paper settings: 500 nodes, 2 J, one election then 5 data frames. The paper gives graphs only; the behaviour matches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="31" customHeight="1">
+      <c r="A24" s="10" t="inlineStr"/>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Our EDITED code (unified environment)</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>658</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>1197</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>1875</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>0.996512</v>
+      </c>
+      <c r="G24" s="19" t="inlineStr">
+        <is>
+          <t>-10.4% vs ORIGINAL</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Unified: one election per data packet; the election messages are heard by ~20 neighbours every round; 0.5 J instead of 2 J.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="31" customHeight="1">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Far BS (50, −100)</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>350</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>765</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>1375</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>0.995336</v>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>-46.8% vs centre</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>BS far: every CH sends far (cost d⁴).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>PEGASIS</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Paper (published)</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>1578</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>2082</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>2192</v>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>Table 1 of the paper (50 × 50 m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="31" customHeight="1">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Our ORIGINAL code (paper settings)</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>1616</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>2186</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>0.988595</v>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>+2.4% vs paper</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Paper settings: 50 × 50 m, BS at (25, 150). All values within 3.5 % of the paper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="44.5" customHeight="1">
+      <c r="A28" s="10" t="inlineStr"/>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Our EDITED code (unified environment)</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>1324</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>2352</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>3504</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>0.994186</v>
+      </c>
+      <c r="G28" s="19" t="inlineStr">
+        <is>
+          <t>-18.1% vs ORIGINAL</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>Unified: field 4× bigger → one chain link of 91.5 m (&gt; d0, cost d⁴) kills node 73 first (FND ↓); cheap radio + central BS → the last nodes live long (LND ↑).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="31" customHeight="1">
+      <c r="A29" s="5" t="inlineStr"/>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Far BS (50, −100)</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>1374</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>2176</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>2713</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>0.990811</v>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>+3.8% vs centre</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>BS far: only the leader talks to the BS, so the first death hardly changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>3. The three hybrids — paper → our code → unified → OUR FIX → far BS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>FND</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>HND</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>LND</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>PDR</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Change (FND*)</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>What changed / what we improved</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
           <t>SH-LEACH</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>round counter never resets → too many CHs</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="n">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Paper (published)</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>graphs only</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="31" customHeight="1">
+      <c r="A34" s="10" t="inlineStr"/>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>Our ORIGINAL code (paper settings)</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="n">
         <v>484</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D34" s="12" t="n">
+        <v>583</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>689</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>0.9965850000000001</v>
+      </c>
+      <c r="G34" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>Paper settings: 100 × 100 m, one amplifier (100 pJ), packet size not given (2000 bits assumed). Paper: graphs only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="31" customHeight="1">
+      <c r="A35" s="5" t="inlineStr"/>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Our EDITED code (unified environment)</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n">
         <v>647</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="D35" s="7" t="n">
+        <v>702</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>721</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>0.9858440000000001</v>
+      </c>
+      <c r="G35" s="20" t="inlineStr">
+        <is>
+          <t>+33.7% vs ORIGINAL</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Unified: cheaper radio (10 vs 100 pJ). The paper's flaw remains: the round counter r never resets → up to 100 CHs per round.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="31" customHeight="1">
+      <c r="A36" s="15" t="inlineStr"/>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>IMPROVED (our fix)</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="n">
         <v>1480</v>
       </c>
-      <c r="F18" s="19" t="n">
-        <v>1.287480680061824</v>
-      </c>
-      <c r="G18" s="12" t="n">
+      <c r="D36" s="16" t="n">
+        <v>1542</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>1558</v>
+      </c>
+      <c r="F36" s="17" t="n">
+        <v>0.992063</v>
+      </c>
+      <c r="G36" s="21" t="inlineStr">
+        <is>
+          <t>+128.7% vs EDITED</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="inlineStr">
+        <is>
+          <t>OUR FIX: the counter restarts every 1/C_prob = 10 rounds (r → ((r − 1) mod 10) + 1) → CHs stay few instead of reaching 100.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="31" customHeight="1">
+      <c r="A37" s="5" t="inlineStr"/>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Far BS (50, −100)</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="n">
         <v>1388</v>
       </c>
-      <c r="H18" s="20" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="D37" s="7" t="n">
+        <v>1435</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>1455</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>0.988878</v>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>-6.2% vs centre</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>BS far, after the fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>H-LEACH</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>deadlock (E &gt; average) + no G-set</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="n">
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Paper (published)</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>4312</v>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>Fig. 2 of the paper (≈ 4312)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="44.5" customHeight="1">
+      <c r="A39" s="5" t="inlineStr"/>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Our ORIGINAL code (paper settings)</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n">
         <v>1078</v>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D39" s="7" t="n">
+        <v>1157</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>1207</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>0.950353</v>
+      </c>
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t>-72.0% vs paper</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>Paper settings: 4000-bit packets. The paper's LND ≈ 4312 is not reachable (the 50 J are used up before round 2500). A fallback CH was added for the deadlock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="31" customHeight="1">
+      <c r="A40" s="10" t="inlineStr"/>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>Our EDITED code (unified environment)</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="n">
         <v>1384</v>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="D40" s="12" t="n">
+        <v>1419</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>1434</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>0.992968</v>
+      </c>
+      <c r="G40" s="19" t="inlineStr">
+        <is>
+          <t>+28.4% vs ORIGINAL</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>Unified: 2000-bit packets. The paper's flaws remain: "E &gt; average" → no CH in round 1 (deadlock); no G-set → bursts of up to 59 CHs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="31" customHeight="1">
+      <c r="A41" s="15" t="inlineStr"/>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>IMPROVED (our fix)</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="n">
         <v>1473</v>
       </c>
-      <c r="F19" s="21" t="n">
-        <v>0.06430635838150289</v>
-      </c>
-      <c r="G19" s="7" t="n">
+      <c r="D41" s="16" t="n">
+        <v>1509</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>1525</v>
+      </c>
+      <c r="F41" s="17" t="n">
+        <v>0.993617</v>
+      </c>
+      <c r="G41" s="21" t="inlineStr">
+        <is>
+          <t>+6.4% vs EDITED</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="inlineStr">
+        <is>
+          <t>OUR FIX: "E &gt; average" → "E ≥ average" + LEACH G-set restored → no deadlock, no CH bursts (8.6 → 5.3 CHs per round).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="31" customHeight="1">
+      <c r="A42" s="10" t="inlineStr"/>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Far BS (50, −100)</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="n">
         <v>1219</v>
       </c>
-      <c r="H19" s="22" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="D42" s="12" t="n">
+        <v>1262</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>1278</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>0.991184</v>
+      </c>
+      <c r="G42" s="19" t="inlineStr">
+        <is>
+          <t>-17.2% vs centre</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>BS far, after the fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>EECH-HEED</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>rotation of 1 round in zone 2</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="n">
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Paper (published)</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>1650</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Table 7 of the paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="31" customHeight="1">
+      <c r="A44" s="10" t="inlineStr"/>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>Our ORIGINAL code (paper settings)</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="n">
         <v>1121</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D44" s="12" t="n">
+        <v>1954</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>3783</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>0.997831</v>
+      </c>
+      <c r="G44" s="19" t="inlineStr">
+        <is>
+          <t>-10.3% vs paper</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>Paper scenario: adaptive sensing ON, heterogeneous energy (≈ 56 J), 4000-bit packets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="44.5" customHeight="1">
+      <c r="A45" s="5" t="inlineStr"/>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Our EDITED code (unified environment)</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="n">
         <v>1277</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="D45" s="7" t="n">
+        <v>1384</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>1543</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>0.994936</v>
+      </c>
+      <c r="G45" s="20" t="inlineStr">
+        <is>
+          <t>+13.9% vs ORIGINAL</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Unified: sensing OFF (every node sends every round), 50 J. The paper's flaw remains: zone 2 P ≈ 1 → the same border nodes are CH every other round.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="31" customHeight="1">
+      <c r="A46" s="15" t="inlineStr"/>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>IMPROVED (our fix)</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="n">
         <v>1335</v>
       </c>
-      <c r="F20" s="19" t="n">
-        <v>0.04541895066562263</v>
-      </c>
-      <c r="G20" s="12" t="n">
+      <c r="D46" s="16" t="n">
+        <v>1384</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>1766</v>
+      </c>
+      <c r="F46" s="17" t="n">
+        <v>0.996207</v>
+      </c>
+      <c r="G46" s="21" t="inlineStr">
+        <is>
+          <t>+4.5% vs EDITED</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="inlineStr">
+        <is>
+          <t>OUR FIX: zone-2 rotation fixed at the paper's 10 % + G-set; energy × degree kept as a weight (7.6 → 2.9 CHs per round).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="31" customHeight="1">
+      <c r="A47" s="5" t="inlineStr"/>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Far BS (50, −100)</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="n">
         <v>1410</v>
       </c>
-      <c r="H20" s="20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>LEACH (reference)</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="D47" s="7" t="n">
+        <v>1437</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>1457</v>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>0.991819</v>
+      </c>
+      <c r="G47" s="20" t="inlineStr">
+        <is>
+          <t>+5.6% vs centre</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>BS far, after the fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>* When the paper gives no FND, the ORIGINAL row compares LND. ORIGINAL → EDITED = environment only; EDITED → IMPROVED = our one fix only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>4. Our protocol — one change per version (BS at the centre)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>What changed</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>FND</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>HND</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>LND</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>PDR</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>FND change</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52" ht="31" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>HEED election + LEACH join</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="D52" s="12" t="n">
+        <v>529</v>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>1218</v>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>0.997623</v>
+      </c>
+      <c r="G52" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n">
-        <v>1035</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>1383</v>
-      </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="H52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53" ht="31" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>+ fairness penalty</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>334</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>528</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>1285</v>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>0.997665</v>
+      </c>
+      <c r="G53" s="24" t="n">
+        <v>0.04374999999999996</v>
+      </c>
+      <c r="H53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54" ht="31" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>single-pass score + 5-round reuse</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="n">
+        <v>1645</v>
+      </c>
+      <c r="D54" s="12" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>2203</v>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>0.983494</v>
+      </c>
+      <c r="G54" s="23" t="n">
+        <v>3.925149700598802</v>
+      </c>
+      <c r="H54" s="11" t="inlineStr"/>
+    </row>
+    <row r="55" ht="31" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>reuse 15 rounds</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>1513</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>2158</v>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>2416</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>0.970722</v>
+      </c>
+      <c r="G55" s="24" t="n">
+        <v>-0.08024316109422491</v>
+      </c>
+      <c r="H55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56" ht="31" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>v5</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>+ backup CH (interval 15)</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="n">
+        <v>1513</v>
+      </c>
+      <c r="D56" s="12" t="n">
+        <v>2116</v>
+      </c>
+      <c r="E56" s="12" t="n">
+        <v>2356</v>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>0.984351</v>
+      </c>
+      <c r="G56" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="11" t="inlineStr"/>
+    </row>
+    <row r="57" ht="31" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>v5b</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>backup + repair, interval 5, energy check</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>1645</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>1996</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>2116</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>0.986194</v>
+      </c>
+      <c r="G57" s="24" t="n">
+        <v>0.08724388631857227</v>
+      </c>
+      <c r="H57" s="6" t="inlineStr"/>
+    </row>
+    <row r="58" ht="31" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>v6</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>ordered CH chain</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="n">
+        <v>1521</v>
+      </c>
+      <c r="D58" s="12" t="n">
+        <v>1913</v>
+      </c>
+      <c r="E58" s="12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>0.985123</v>
+      </c>
+      <c r="G58" s="23" t="n">
+        <v>-0.07537993920972641</v>
+      </c>
+      <c r="H58" s="11" t="inlineStr"/>
+    </row>
+    <row r="59" ht="31" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>chain + backup + repair</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>1521</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>1906</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>2011</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>0.989135</v>
+      </c>
+      <c r="G59" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60" ht="31" customHeight="1">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>v7.1</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>greedy multi-hop tree</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="n">
+        <v>1466</v>
+      </c>
+      <c r="D60" s="12" t="n">
+        <v>1896</v>
+      </c>
+      <c r="E60" s="12" t="n">
+        <v>2011</v>
+      </c>
+      <c r="F60" s="13" t="n">
+        <v>0.990826</v>
+      </c>
+      <c r="G60" s="23" t="n">
+        <v>-0.03616042077580539</v>
+      </c>
+      <c r="H60" s="11" t="inlineStr"/>
+    </row>
+    <row r="61" ht="31" customHeight="1">
+      <c r="A61" s="15" t="inlineStr">
+        <is>
+          <t>v8</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>v5b + I1–I5</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="n">
+        <v>2446</v>
+      </c>
+      <c r="D61" s="16" t="n">
+        <v>2536</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>2566</v>
+      </c>
+      <c r="F61" s="17" t="n">
+        <v>0.997208</v>
+      </c>
+      <c r="G61" s="25" t="n">
+        <v>0.6684856753069577</v>
+      </c>
+      <c r="H61" s="15" t="inlineStr"/>
+    </row>
+    <row r="62" ht="31" customHeight="1">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>v8-Chain</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>v8 + energy-aware relay</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="n">
+        <v>2446</v>
+      </c>
+      <c r="D62" s="16" t="n">
+        <v>2536</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>2566</v>
+      </c>
+      <c r="F62" s="17" t="n">
+        <v>0.9971680000000001</v>
+      </c>
+      <c r="G62" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="15" t="inlineStr"/>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>5. Which part of v8 matters? (v8 with one improvement switched off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Switched off</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>FND</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>HND</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>LND</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>PDR</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>FND change</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66" ht="31" customHeight="1">
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t>v8 (full)</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="C66" s="16" t="n">
+        <v>2446</v>
+      </c>
+      <c r="D66" s="16" t="n">
+        <v>2536</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>2566</v>
+      </c>
+      <c r="F66" s="17" t="n">
+        <v>0.997208</v>
+      </c>
+      <c r="G66" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="7" t="n">
-        <v>988</v>
-      </c>
-      <c r="H21" s="22" t="inlineStr"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>3. Our protocol — one change per version (BS at the centre)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>What changed</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>FND</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>HND</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>LND</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>PDR</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>FND change</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>HEED election + LEACH join</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="n">
-        <v>320</v>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>529</v>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>1218</v>
-      </c>
-      <c r="F25" s="8" t="n">
-        <v>0.997623</v>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H25" s="22" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>+ fairness penalty</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="n">
-        <v>334</v>
-      </c>
-      <c r="D26" s="12" t="n">
-        <v>528</v>
-      </c>
-      <c r="E26" s="12" t="n">
-        <v>1285</v>
-      </c>
-      <c r="F26" s="13" t="n">
-        <v>0.997665</v>
-      </c>
-      <c r="G26" s="19" t="n">
-        <v>0.04374999999999996</v>
-      </c>
-      <c r="H26" s="20" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>single-pass score + 5-round reuse</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="n">
-        <v>1645</v>
-      </c>
-      <c r="D27" s="7" t="n">
-        <v>2001</v>
-      </c>
-      <c r="E27" s="7" t="n">
-        <v>2203</v>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>0.983494</v>
-      </c>
-      <c r="G27" s="21" t="n">
-        <v>3.925149700598802</v>
-      </c>
-      <c r="H27" s="22" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>v4</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>reuse 15 rounds</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="n">
-        <v>1513</v>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>2158</v>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>2416</v>
-      </c>
-      <c r="F28" s="13" t="n">
-        <v>0.970722</v>
-      </c>
-      <c r="G28" s="19" t="n">
-        <v>-0.08024316109422491</v>
-      </c>
-      <c r="H28" s="20" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>v5</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>+ backup CH (interval 15)</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="n">
-        <v>1513</v>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>2116</v>
-      </c>
-      <c r="E29" s="7" t="n">
-        <v>2356</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>0.984351</v>
-      </c>
-      <c r="G29" s="21" t="n">
+      <c r="H66" s="15" t="inlineStr"/>
+    </row>
+    <row r="67" ht="31" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>v8 − I1</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>I1 epoch fix</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>2451</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>2541</v>
+      </c>
+      <c r="E67" s="7" t="n">
+        <v>2581</v>
+      </c>
+      <c r="F67" s="8" t="n">
+        <v>0.997409</v>
+      </c>
+      <c r="G67" s="24" t="n">
+        <v>0.002044153720359709</v>
+      </c>
+      <c r="H67" s="6" t="inlineStr"/>
+    </row>
+    <row r="68" ht="31" customHeight="1">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>v8 − I2</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>I2 handover</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="n">
+        <v>2430</v>
+      </c>
+      <c r="D68" s="12" t="n">
+        <v>2535</v>
+      </c>
+      <c r="E68" s="12" t="n">
+        <v>2581</v>
+      </c>
+      <c r="F68" s="13" t="n">
+        <v>0.996309</v>
+      </c>
+      <c r="G68" s="23" t="n">
+        <v>-0.006541291905151292</v>
+      </c>
+      <c r="H68" s="11" t="inlineStr"/>
+    </row>
+    <row r="69" ht="31" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>v8 − I3</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>I3 re-join</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>2446</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>2536</v>
+      </c>
+      <c r="E69" s="7" t="n">
+        <v>2566</v>
+      </c>
+      <c r="F69" s="8" t="n">
+        <v>0.997105</v>
+      </c>
+      <c r="G69" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="22" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>v5b</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>backup + repair, interval 5, energy check</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="n">
-        <v>1645</v>
-      </c>
-      <c r="D30" s="12" t="n">
-        <v>1996</v>
-      </c>
-      <c r="E30" s="12" t="n">
-        <v>2116</v>
-      </c>
-      <c r="F30" s="13" t="n">
-        <v>0.986194</v>
-      </c>
-      <c r="G30" s="19" t="n">
-        <v>0.08724388631857227</v>
-      </c>
-      <c r="H30" s="20" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>v6</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>ordered CH chain</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="n">
-        <v>1521</v>
-      </c>
-      <c r="D31" s="7" t="n">
-        <v>1913</v>
-      </c>
-      <c r="E31" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>0.985123</v>
-      </c>
-      <c r="G31" s="21" t="n">
-        <v>-0.07537993920972641</v>
-      </c>
-      <c r="H31" s="22" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>v7</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>chain + backup + repair</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="n">
-        <v>1521</v>
-      </c>
-      <c r="D32" s="12" t="n">
-        <v>1906</v>
-      </c>
-      <c r="E32" s="12" t="n">
-        <v>2011</v>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>0.989135</v>
-      </c>
-      <c r="G32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="20" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>v7.1</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>greedy multi-hop tree</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="n">
-        <v>1466</v>
-      </c>
-      <c r="D33" s="7" t="n">
-        <v>1896</v>
-      </c>
-      <c r="E33" s="7" t="n">
-        <v>2011</v>
-      </c>
-      <c r="F33" s="8" t="n">
-        <v>0.990826</v>
-      </c>
-      <c r="G33" s="21" t="n">
-        <v>-0.03616042077580539</v>
-      </c>
-      <c r="H33" s="22" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>v8</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>v5b + I1–I5</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="n">
-        <v>2446</v>
-      </c>
-      <c r="D34" s="16" t="n">
-        <v>2536</v>
-      </c>
-      <c r="E34" s="16" t="n">
-        <v>2566</v>
-      </c>
-      <c r="F34" s="17" t="n">
-        <v>0.997208</v>
-      </c>
-      <c r="G34" s="23" t="n">
-        <v>0.6684856753069577</v>
-      </c>
-      <c r="H34" s="24" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>v8-Chain</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>v8 + energy-aware relay</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="n">
-        <v>2446</v>
-      </c>
-      <c r="D35" s="16" t="n">
-        <v>2536</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>2566</v>
-      </c>
-      <c r="F35" s="17" t="n">
-        <v>0.9971680000000001</v>
-      </c>
-      <c r="G35" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="24" t="inlineStr"/>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>4. Which part of v8 matters? (v8 with one improvement switched off)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Switched off</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>FND</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>HND</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>LND</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>PDR</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>FND change</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>v8 (full)</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="n">
-        <v>2446</v>
-      </c>
-      <c r="D39" s="16" t="n">
-        <v>2536</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>2566</v>
-      </c>
-      <c r="F39" s="17" t="n">
-        <v>0.997208</v>
-      </c>
-      <c r="G39" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H39" s="24" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>v8 − I1</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>I1 epoch fix</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="n">
-        <v>2451</v>
-      </c>
-      <c r="D40" s="12" t="n">
-        <v>2541</v>
-      </c>
-      <c r="E40" s="12" t="n">
-        <v>2581</v>
-      </c>
-      <c r="F40" s="13" t="n">
-        <v>0.997409</v>
-      </c>
-      <c r="G40" s="19" t="n">
-        <v>0.002044153720359709</v>
-      </c>
-      <c r="H40" s="20" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>v8 − I2</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>I2 handover</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="n">
-        <v>2430</v>
-      </c>
-      <c r="D41" s="7" t="n">
-        <v>2535</v>
-      </c>
-      <c r="E41" s="7" t="n">
-        <v>2581</v>
-      </c>
-      <c r="F41" s="8" t="n">
-        <v>0.996309</v>
-      </c>
-      <c r="G41" s="21" t="n">
-        <v>-0.006541291905151292</v>
-      </c>
-      <c r="H41" s="22" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>v8 − I3</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>I3 re-join</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="n">
-        <v>2446</v>
-      </c>
-      <c r="D42" s="12" t="n">
-        <v>2536</v>
-      </c>
-      <c r="E42" s="12" t="n">
-        <v>2566</v>
-      </c>
-      <c r="F42" s="13" t="n">
-        <v>0.997105</v>
-      </c>
-      <c r="G42" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="20" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="H69" s="6" t="inlineStr"/>
+    </row>
+    <row r="70" ht="31" customHeight="1">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>v8 − I4</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>I4 direct-to-BS</t>
         </is>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C70" s="12" t="n">
         <v>1766</v>
       </c>
-      <c r="D43" s="7" t="n">
+      <c r="D70" s="12" t="n">
         <v>1916</v>
       </c>
-      <c r="E43" s="7" t="n">
+      <c r="E70" s="12" t="n">
         <v>1981</v>
       </c>
-      <c r="F43" s="8" t="n">
+      <c r="F70" s="13" t="n">
         <v>0.995359</v>
       </c>
-      <c r="G43" s="21" t="n">
+      <c r="G70" s="23" t="n">
         <v>-0.2780049059689289</v>
       </c>
-      <c r="H43" s="22" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="H70" s="11" t="inlineStr"/>
+    </row>
+    <row r="71" ht="31" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>v8 − I5</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>I5 energy gate</t>
         </is>
       </c>
-      <c r="C44" s="12" t="n">
+      <c r="C71" s="7" t="n">
         <v>2171</v>
       </c>
-      <c r="D44" s="12" t="n">
+      <c r="D71" s="7" t="n">
         <v>2481</v>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E71" s="7" t="n">
         <v>2551</v>
       </c>
-      <c r="F44" s="13" t="n">
+      <c r="F71" s="8" t="n">
         <v>0.997721</v>
       </c>
-      <c r="G44" s="19" t="n">
+      <c r="G71" s="24" t="n">
         <v>-0.1124284546197875</v>
       </c>
-      <c r="H44" s="20" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="25" t="inlineStr">
+      <c r="H71" s="6" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="26" t="inlineStr">
         <is>
           <t>Robustness: v8 on 8 random topologies → FND 2401 – 2481 (mean 2448).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A46:H46"/>
+  <mergeCells count="6">
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A73:H73"/>
     <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A64:H64"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A31:H31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
